--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -9,11 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internships" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company watchlist" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$W$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Y$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Company watchlist'!$A$1:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -471,6 +473,8 @@
     <col width="27" customWidth="1" min="21" max="21"/>
     <col width="27" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="27" customWidth="1" min="24" max="24"/>
+    <col width="27" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="29" customHeight="1">
@@ -486,105 +490,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Role type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Work mode</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Minimum INR/month</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Maximum INR/month</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Pay confirmed in original</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Next action</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Interview time</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Applied date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Original source</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Application link</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Application email</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Application route</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Evidence / caveats</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Application instructions</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Posted</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>First discovered</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Last checked</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Personal notes</t>
         </is>
@@ -603,83 +617,93 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>30000</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="G2" s="2" t="b">
+      <c r="G2" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>discovered</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn job</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>mailto:info@shramiksathi.com</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>info@shramiksathi.com</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Email application; draft can be prepared</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Employer-authored LinkedIn description explicitly states Remote (India) and ₹30,000/month. The job header says Bengaluru; the description confirms remote work. One opening listed.</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Figma, reusable components, design tokens, responsive and accessible interfaces, research and Hindi/English communication. Work includes worker-facing mobile flows and administrative dashboards. Internship: 3–6 months.</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Email a portfolio with 2–3 case studies and a response of up to 150 words: how should a worker confirm yesterday’s attendance on a small Android phone with an intermittent connection? No cover letter requested. Selection mentions a portfolio discussion, then a paid exercise.</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>3 weeks ago when checked</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="95" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -694,79 +718,89 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>On-site</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>25000</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="G3" s="2" t="b">
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>discovered</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>https://www.menstrupedia.com/careers/ux-intern</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>https://forms.gle/fWuuGCFJwACS7uVa9</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Company application form</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>Company career page states internship, Ahmedabad office and ₹25,000–₹30,000/month. Meets the Gujarat minimum. Original posting date is not stated; confirm the opening is still available.</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Design web/mobile interfaces, test with users, collaborate with developers and measure outcomes. Visual design, typography, colour and English communication required. Past UX experience is desirable.</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Use the company’s Apply link. The page also asks for a résumé and a paragraph explaining suitability, with subject Application for UX Design Intern.</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="95" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -781,75 +815,85 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>Bengaluru, Karnataka</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>On-site</t>
         </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>35000</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>35000</v>
       </c>
-      <c r="G4" s="2" t="b">
+      <c r="G4" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>discovered</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn job</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>LinkedIn application</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Employer-authored LinkedIn description states ₹35,000/month and Bengaluru. Remote work is not confirmed. Third-party ₹40,000 claims were not used.</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Portfolio showing design decisions and process, Figma, user research and design systems. Pursuing or recently completed a relevant design/HCI degree. Internship duration: 3–6 months.</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>1 week ago when checked</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="95" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -864,83 +908,93 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>Remote / hybrid, India</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Unconfirmed</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>20000</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>25000</v>
       </c>
-      <c r="G5" s="2" t="b">
+      <c r="H5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>discovered</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn job</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/product-design-intern-at-bthree-design-agency-4473077505</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>mailto:contact@bthreedesigns.com</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>contact@bthreedesigns.com</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Email application; draft can be prepared</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Original listing gives ₹20,000–₹25,000/month and Remote / Hybrid. Conditional only if ₹25,000 is agreed and fully remote work is confirmed; the advertised minimum falls below your general threshold.</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Original listing gives ₹20,000–₹25,000/month and Remote / Hybrid. Conditional only if ₹25,000 is agreed and fully remote work is confirmed; the advertised minimum falls below your general threshold. An X mirror of the company post claims remote anywhere in India; original X access was blocked, so confirm with the employer.</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>Strong Framer implementation, Figma auto-layout/components, design systems and motion tools such as Jitter or Lottie. Three-month internship, immediate start, eight hours/day.</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Send portfolio/work samples, 2–3 lines on work you enjoy and 2–3 lines on what you want to learn. Framer/motion examples are useful.</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>3 weeks ago when checked</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="95" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -955,71 +1009,81 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>Bengaluru, Karnataka</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>On-site</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="b">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn post</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/posts/sruthisivakumar_product-design-intern-wint-wealth-activity-7515659430051426304-tqUQ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>https://binary.so/P01RayN</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Recruiter-linked application form</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>A current post by the company’s co-founder/design leader confirms the internship and Bangalore office attendance. ₹30k–₹35k appears only in third-party listings; employer pay is unconfirmed.</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>Figma, product thinking, collaboration with product and engineering. Portfolio work on design systems is specifically encouraged.</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>1 week ago when checked</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="95" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1034,71 +1098,81 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>Bengaluru, Karnataka</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>On-site</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="b">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/hevodata/433ffdef-3125-48ed-a131-52c697c321ee</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/hevodata/433ffdef-3125-48ed-a131-52c697c321ee/apply</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Lever application form</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Official employer Lever role and application page are accessible. On-site Bangalore; stipend and original publication date are not disclosed.</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>Figma components and tokens, SaaS/dashboard interfaces, prototyping and developer handoff. AI-assisted design workflows are relevant.</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="95" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1113,71 +1187,81 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>Bengaluru, Karnataka</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>On-site</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="b">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>https://www.revrag.ai/careers/product-design-intern</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>https://www.revrag.ai/careers/product-design-intern</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Employer-linked Google Form</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Original company role is accessible and lists Bengaluru on-site. Third-party ₹40k claims are not confirmed by this page.</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>Strong portfolio, Figma variables/components, AI prototyping, interaction states and fintech workflows. Six-month internship.</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="95" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1192,79 +1276,89 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>Remote, India; Bengaluru preferred</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="b">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>mailto:apply@chiblu.com</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>apply@chiblu.com</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Email or Wellfound</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Company still exposes the role page and links it from careers. It is an older May posting; current hiring and stipend require confirmation.</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>At least three portfolio projects, including end-to-end thinking and a mobile flow; Figma, visual craft, research and communication. Two months with possible extension.</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Share portfolio, a short reason for your interest, one project you would discuss and earliest start date.</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>5 May 2026 · older posting</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="95" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1279,71 +1373,81 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="b">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>https://www.neuralpath.app/careers/</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>https://www.neuralpath.app/careers/</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Email application via company page</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Company careers page explicitly lists a remote Product Design Intern opportunity and year-round applications. Duration and stipend are discussed individually.</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>Figma, UI, prototypes and a portfolio. Students/recent graduates welcome; internships can fit around classes.</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="95" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1358,71 +1462,81 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="b">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>https://krmrsolutions.com/careers/design-intern</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>https://krmrsolutions.com/careers/design-intern</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>LinkedIn link from employer page</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Original company career page confirms Remote (India) and internship. No stipend or publication date stated.</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>Portfolio showing layout, typography and colour; Figma auto-layout and prototypes; component documentation and development handoff.</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="95" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1437,71 +1551,81 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Remote, India</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="b">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>https://www.gozavio.com/careers</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>https://www.gozavio.com/careers</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Company application link</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Company careers page lists this as an open internship, remote anywhere in India. Stipend and posting date are not stated.</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Research, wireframes, user flows and high-fidelity interfaces for financial education products.</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="95" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1516,71 +1640,81 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Remote, India (reported)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="b">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Job board</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>https://www.jobleads.com/in/job/product-design-intern--india--e24abd61a6654a91f9a3af3bab3db8da5</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>https://www.gnixar.in/careers</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Confirm on employer careers first</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Job-board description reports remote India and ₹25k–₹40k/month, but its header conflicts on location and compensation. The company careers page dynamically loads roles; this role/pay remains unverified.</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>Visual and interaction design portfolio, Figma, prototyping and design-system contributions.</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>13 days ago on job board when checked</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="95" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1595,106 +1729,781 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Bengaluru, Karnataka</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Unconfirmed</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="b">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>discovered</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Job board</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>https://www.studentsmart.co.in/student/internships/glance-ux-design-intern</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>https://www.studentsmart.co.in/student/internships/glance-ux-design-intern</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Job-board sign-in; find original employer listing</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>StudentSmart reports ₹30k–₹40k/month and Bengaluru; original employer confirmation and work arrangement are still needed.</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>UX/visual design for TV shopping interfaces, design systems, interaction states, engineering handoff and interest in AI/ambient computing.</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>15 October 2026 on job board</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="95" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Techolution</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad / remote claim requires confirmation</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Confirm current vacancy, India remote eligibility and at least ₹25–30k/month before submitting.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>https://hire.techolution.com/careers</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Indeed application or locate UX Designer–Intern on employer careers portal; form and account requirements untested</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Indeed detail accessible; official careers index also lists UX Designer–Intern in Hyderabad. Remote statement in Indeed conflicts with Hyderabad in current company index. Official careers site is dynamic; indexed role corroboration is stronger than its text-only rendering.</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio and Figma; Interaction/UX/graphic design or related degree; Research, wireframes, prototypes and developer specifications.</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>No reliable original posting date displayed</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="95" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Ask stipend, Bengaluru attendance requirements and six-month availability before applying.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Indeed; official careers page provides careers@f1studioz.com as company hiring channel.</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Original Indeed detail accessible without an expiry banner; official careers page corroborates employer and application channel, not a unique role detail. Actual application submission flow not tested. General company hybrid policy does not establish this role's work mode.</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Practice projects accepted in portfolio; Final-semester B.Des/M.Des or engineering student/graduate with UX skills; AI tools and enterprise UX interest; possible full-time availability.</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="95" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Green Ping Solutions</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Confirm stipend of at least ₹20k/month and internship duration.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=157d2635900933e2</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=157d2635900933e2</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Indeed SmartApply</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Original Indeed detail accessible without an expiry banner. Login and application fields not inspected through submission.</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Web and mobile UI; User research, flows and prototypes; Components/design systems and developer collaboration.</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="95" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Trainee UI/UX Designer</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Confirm starting monthly salary ≥₹20k and graduate eligibility.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moontechnolabs.com/career-with-us/</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Official careers Apply Now / career@moontechnolabs.com, or Indeed</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Indeed detail accessible; official careers page lists Trainee UI/UX Designer with experience Fresher. Submission not tested; this is a junior job alternative, not an internship.</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Figma or Adobe XD; Wireframes, prototypes, research and design systems; Bachelor's graduate and developer handoff skills.</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="95" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Remote India (confirm eligibility)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Verify active Naukri route and paid stipend ≥₹25–30k before investing in application.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Naukri</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Employer page directs applicants to Naukri; no WhatsApp applications.</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>Current accessible employer role page explicitly links this Naukri application. Original Naukri page is robots-blocked, so activity of that particular Naukri listing is unverified. Employer says remote; Naukri slug says Gurgaon. Confirm remote India eligibility and current application link.</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>B.Des/M.Des or relevant design qualification; Figma and Illustrator; Research/usability, web/mobile design, components and brand styles.</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>No reliable posting date. Naukri identifier appears historical; do not infer freshness.</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="95" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Pune; remote for now</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Remote for now</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Confirm paid stipend and whether eventual Pune attendance is required.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Employer form with resume, education, experience, notice period, location, expected salary and privacy consent.</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>Official role and application form accessible. Employer prefers candidates in or near Pune. Remote arrangement is temporary; no promise of permanent remote. Application form not submitted.</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Figma basics; Few college, personal or professional design projects; Layout, wireframes, simple prototypes and checking developed screens.</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Careers index shows a relative age of 2 days; original absolute publication date not independently available.</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="95" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer (Fresher)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Pune; remote for now</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Remote for now</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Confirm salary ≥₹25–30k/month and future office expectations.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Employer application form; resume, location, expected annual salary and privacy consent required.</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Official role and application form accessible; Indeed discovery was a search result, not a uniquely verified job-detail URL. Employer prefers Pune or nearby candidates; current remote arrangement may change.</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Figma and portfolio; personal/college/freelance work accepted; Flows, prototypes, accessible UI and design systems; Developer collaboration and usability reviews.</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Careers index shows a relative age of 2 days; original absolute publication date not independently available.</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W14"/>
+  <autoFilter ref="A1:Y21"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"discovered,shortlisted,applied,assessment,interview,offer,closed"</formula1>
+    <dataValidation sqref="I2:I10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1706,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2229,8 +3038,600 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Techolution</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Green Ping Solutions</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=157d2635900933e2</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.microsoft.com/v2/global/en/students</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/university</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/earlycareers</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Tekion</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://tekion.com/careers</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Scaler Academy</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Lenskart</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.lenskart.com/</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://shramiksathi.com/</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rapido</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rapido.bike/Careers</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SatSure</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.satsure.co/careers/</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>BThree Design Agency</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bthreedesigns.com/</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.parallelhq.com/careers</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://f1studioz.com/careers</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moontechnolabs.com/career-with-us/</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.keyideasinfotech.com/careers/ui-ux-design-internship/</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Wint Wealth</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/beatsbyshaz/status/2112981756571983955</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Original X URL returned 403; content checked through third-party mirror. Evidence: https://workingww.twstalker.com/beatsbyshaz/status/2112981756571983955</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>BThree Designs</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BThreeAgency/status/2108934891069161479</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Original X URL returned 403; content checked through third-party mirror. Evidence: https://workingww.twstalker.com/BThreeAgency/status/2108934891069161479</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2241,7 +3642,1170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
+    <col width="75" customWidth="1" min="5" max="5"/>
+    <col width="75" customWidth="1" min="6" max="6"/>
+    <col width="75" customWidth="1" min="7" max="7"/>
+    <col width="75" customWidth="1" min="8" max="8"/>
+    <col width="75" customWidth="1" min="9" max="9"/>
+    <col width="75" customWidth="1" min="10" max="10"/>
+    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="75" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="29" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Why this target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pay evidence type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Reported role</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Range minimum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Range maximum</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Original period</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Limitations</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Careers URL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Pay source</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Observed date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Product-design teams across enterprise and consumer software. Keep India student and early-career openings on your radar.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Older, low-confidence UX intern reports with inconsistent geography. Current India stipend and eligibility need confirmation.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.microsoft.com/v2/global/en/students</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/Microsoft-UX-Design-intern-Bangalore-EJI_IE1651.0%2C9_KO10%2C26_IL.27%2C36_IM1091.htm?filter.payPeriod=MONTHLY</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Creative tools and digital experience products. Watch India university and early-career design roles.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Modeled salary estimate</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>A related-designation salary model gives an annual intern estimate; exact India internship pay is not established. No monthly stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/university</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ambitionbox.com/salaries/adobe-salaries/ui-ux-architect</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Collaboration products and design systems. Watch for India-eligible early-career opportunities.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Only two annualized intern reports, with unclear geography. The current US internship found in research is not an India opportunity.</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/earlycareers</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>https://static.glassdoor.co.in/Salary/Atlassian-Salaries-E115699_P10.htm</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Tekion</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Suggested practical product-company target with direct design-intern salary history, not a hiring probability.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Historical small sample; source labels low confidence. Current stipend, role availability and remote eligibility need employer confirmation.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://tekion.com/careers</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/Tekion-Product-Design-Intern-Bangalore-Salaries-EJI_IE1501014.0%2C6_KO7%2C28_IL.29%2C38_IM1091.htm?payPeriod=MONTHLY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Scaler Academy</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Suggested product-design target with reported internship compensation near the requested ballpark.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Old employee reports, not a current offer. Careers page currently exposes other roles; no matching internship confirmed.</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/Scaler-Academy-Product-Design-Intern-Bengaluru-Salaries-EJI_IE3340290.0%2C14_KO15%2C36_IL.37%2C46_IC2940587.htm?payPeriod=MONTHLY</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Lenskart</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Suggested consumer-product employer with a design-intern salary signal.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>39000</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>One report, location/date of report not shown. Official careers redirects to a company job board displaying0 jobs on24 Oct2026; watchlist only.</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.lenskart.com/</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>https://static.glassdoor.co.in/Salary/Lenskart-Solutions-Salaries-E742328_P56.htm</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Suggested practical target because its employer-stated internship range meets the Gujarat minimum.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed stipend</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Listing publication date absent; an accessible page does not guarantee recruitment is still open.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Suggested practical target with explicit remote internship pay and concrete product-design responsibilities.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed stipend</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed snapshot</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Employer website is verified, but no separate careers page was located. Listing freshness should be reconfirmed; source is an employer-authored LinkedIn job, not a current employee pay report.</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://shramiksathi.com/</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Rapido</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Suggested exploratory product-design target; reported pay spans below and above the requested minimum.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Small sample with substantial variation; not enough to assume all internships meet INR30k. Source labels low confidence.</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rapido.bike/Careers</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/Rapido-Product-Design-Intern-Bangalore-Salaries-EJI_IE1150759.0%2C6_KO7%2C28_IL.29%2C38_IM1091.htm?payPeriod=MONTHLY</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SatSure</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Suggested exploratory B2B/geospatial-product target with design-intern salary history near the conditional band.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Annualized salary display is not a confirmed internship-term payment. INR25k/month is only arithmetic annual/12 equivalence; current amount and duration must be checked.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.satsure.co/careers/</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>https://www2.glassdoor.co.in/Salary/SatSure-Salaries-E4629454_P2.htm</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BThree Design Agency</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Suggested exploratory studio target; advertised maximum reaches the user’s conditional INR25k band.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed stipend</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed snapshot</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Below general minimum unless INR25k is agreed. Verify work mode and whether the role remains open. Company website verified; separate careers page not found.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bthreedesigns.com/</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-bthree-design-agency-4473077505</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Suggested exploratory specialist-studio target with remote design work; pay range overlaps the conditional band.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Third-party listing</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Treat as historical/unverified rather than a live job. Official careers page is accessible but did not independently confirm this internship or stipend.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.parallelhq.com/careers</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>https://jobgether.com/offer/6a88dfb41de6f4542a4decc5-product-design-intern</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise UX studio with a current intern listing, but historical internship pay is below your target. Confirm the current budget before applying.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Low-confidence page displays about ₹10k/month and5 submissions, updated4 June2025. Historical report is below your target; verify whether this current role has a different budget.</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://f1studioz.com/careers</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Monthly-Pay/f1Studioz-UX-Intern-Remote-India-Monthly-Pay-EJI_IE1588351.0%2C9_KO10%2C19_IL.20%2C32_IS12563.htm</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Employer careers lists a fresher UI/UX trainee role in Gujarat. Confirm starting pay and graduate requirements.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Current posting does not disclose pay. No reliable role-specific salary estimate was established in this research pass.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moontechnolabs.com/career-with-us/</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Official intern and fresher roles accept personal or college projects. Confirm stipend and eventual Pune attendance.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Current posting does not disclose pay. No reliable role-specific salary estimate was established in this research pass.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Employer page lists a remote UI/UX internship and links to Naukri. Check whether the historical application route is still active.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Cross-company salary page reports ₹19k–₹21k/month for Keyideas in New Delhi. Sample/date unavailable and location differs from the remote posting. This is below the general target and does not establish current pay.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.keyideasinfotech.com/careers/ui-ux-design-internship/</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Salaries/ui-ux-design-intern-salary-SRCH_IM1083_KO0%2C19_P4.htm</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Techolution</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>UX internship listings and historical pay near the conditional range. Confirm remote eligibility and the current stipend first.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Reported salary</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Historical reports</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Visible reports range from ₹15k in May2024 to ₹25k–₹29k in2025. The page also models ₹18k–₹30k/month across10 submissions. Reports are not the current role’s offer; confirm ₹25k–₹30k and remote terms.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://hire.techolution.com/careers</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/Techolution-UX-Design-intern-India-Salaries-EJI_IE1397522.0%2C11_KO12%2C28_IL.29%2C34_IN115.htm?payPeriod=MONTHLY</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M18"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Dream,Workable,Possible"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2256,7 +4820,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Research snapshot: 2026-10-23</t>
+          <t>Research snapshot: 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -2292,151 +4856,247 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Only employer-stated minimums count as confirmed. Undisclosed and third-party pay must be checked.</t>
+          <t>Only employer-stated minimums count as confirmed. Undisclosed-pay roles stay on hold. Glassdoor and other company reports are historical context, never a current offer. Annual figures stay annual.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Freshness</t>
+          <t>Company groups</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Discovery date is not posting date. An accessible listing does not guarantee current hiring.</t>
+          <t>Dream / Workable / Possible are editable suggestions, not hiring probabilities. The company watchlist does not assert current vacancies or offers.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Freshness</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No applications have been submitted. Status and application fields are for you to update.</t>
+          <t>Discovery date is not posting date. An accessible listing does not guarantee current hiring.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Board vs Excel</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>This workbook contains the research snapshot. Browser board changes are exported separately using CSV or JSON backup.</t>
+          <t>No applications have been submitted. Status and application fields are for you to update.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Board vs Excel</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Initial workbook contains no résumé or personal contact data. Employer application contacts are public listing details.</t>
+          <t>This workbook contains the research snapshot. Browser board changes are exported separately using CSV or JSON backup.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Excluded roles</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>See the exclusion list below.</t>
+          <t>Initial workbook contains no résumé or personal contact data. Employer application contacts are public listing details.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Appbrew</t>
+          <t>Excluded roles</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Previously indexed Wellfound role returned HTTP 410 Gone; excluded as an active opening.</t>
+          <t>See the exclusion list below.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Parallel</t>
+          <t>Appbrew</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Third-party role returned HTTP 410 Gone. General careers page alone does not confirm an internship or stipend.</t>
+          <t>Previously indexed Wellfound role returned HTTP 410 Gone; excluded as an active opening.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CrossBo</t>
+          <t>Parallel</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Remote recruiter post is approximately seven months old; stipend and current hiring not confirmed.</t>
+          <t>Third-party role returned HTTP 410 Gone. General careers page alone does not confirm an internship or stipend.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Ourora</t>
+          <t>CrossBo</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Remote internship is explicitly unpaid and falls below your stipend requirements.</t>
+          <t>Remote recruiter post is approximately seven months old; stipend and current hiring not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Trinance</t>
+          <t>Ourora</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad on-site internship lists ₹20,000/month, below your non-Gujarat minimum.</t>
+          <t>Remote internship is explicitly unpaid and falls below your stipend requirements.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>hussh Pune</t>
+          <t>Trinance</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Stale snippet advertises ₹40k, but the current page gives no stipend and describes a campus challenge/probation process; keep outside confirmed matches.</t>
+          <t>Hyderabad on-site internship lists ₹20,000/month, below your non-Gujarat minimum.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>hussh Pune</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Searched public indexed hiring posts; no independently verified qualifying original post found in this pass.</t>
+          <t>Stale snippet advertises ₹40k, but the current page gives no stipend and describes a campus challenge/probation process; keep outside confirmed matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DronaHQ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Original Indeed detail explicitly says expired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>iVoyant</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Original Indeed result explicitly says expired; another listing 0d6b9d4b3f8986b1 also expired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Zuntra Digital</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Official employer description explicitly says unpaid 3-month internship; old Naukri-associated salary snippets must not override this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SurveySparrow</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Indeed lists ₹10,000–20,000 a year, not a month. Below threshold as written; do not silently change unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>FX31Labs</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Naukri-associated identifier appears old; aggregator result is unrelated head role with another-card snippet. Official career page did not verify active internship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Kevit.io</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Indexed Naukri-associated lead is historical and current original Naukri/employer vacancy could not be established. Avoid presenting as newly active Naukri role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Indeed detail remains accessible, but original company role returns HTTP 410 Gone. Company-side deletion conflicts with accessible Indeed listing; do not label verified active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CartGeek</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Indeed and employer page accessible. Another employer posting on LinkedIn categorizes the same title as Volunteer; paid status is not established. Possible volunteer/unpaid classification; do not recommend as a qualifying paid role until clarified.</t>
         </is>
       </c>
     </row>

--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$225</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -4020,8 +4020,290 @@
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
     </row>
+    <row r="38" ht="95" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX &amp; Product Design Internship (Web, Mobile &amp; AI Systems)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Confirm paid six-month terms at INR20,000/month or more, final-year eligibility and whether the immediate-joining intake allows a later start.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/apply/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Published employer application route; no submission made</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>UI hierarchy, typography, contrast and responsive layouts; Component libraries, auto-layout, tokens and interaction states; Client discovery, end-to-end flows and engineering collaboration; Interest in generative visuals; motion and frontend knowledge are bonuses; Final-year design/technical students, recent graduates or self-taught designers; six- or twelve-month options</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>No reliable absolute original posting date verified; discovery date is not publication date.</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="95" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Intern</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Bengaluru-based employer description</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Confirm current paid employment intake, no applicant fees, India eligibility, duration/start window and remote stipend around INR30,000/month; INR25,000 only considered individually.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Published employer application route; no submission made</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Enrolled in design, HCI or a related degree; Basic interface-design tools and principles; Research, wireframes, prototypes and usability testing; Team communication; portfolio and edtech familiarity are helpful</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>No reliable absolute original posting date verified; discovery date is not publication date.</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="95" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Internship</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Remote (India), full-time</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>First confirm the employer is still recruiting; then confirm paid terms, India remote eligibility, duration and start window. Target INR30,000/month; INR25,000 requires individual review.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Published employer application route; no submission made</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Employer Dover ATS search index contains role and application fields; direct opening returned a JavaScript shell. Indexed employer copy was crawled about five months before review, not a posting date. Remotive mirror returned403; its relative age does not prove freshness. Pay and duration undisclosed.</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Listed experience band zero to two years; Figma and Adobe visual/motion tools; Design systems, user research, testing and prototypes</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>No reliable absolute original posting date verified; discovery date is not publication date.</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z37"/>
+  <autoFilter ref="A1:Z40"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
@@ -4100,6 +4382,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4111,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5060,11 +5348,19 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page publishes hr@parallelhq.com; no new internship verified.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -11146,8 +11442,552 @@
         </is>
       </c>
     </row>
+    <row r="226" ht="42" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="42" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="42" customHeight="1">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Employer Dover ATS search index contains role and application fields; direct opening returned a JavaScript shell. Indexed employer copy was crawled about five months before review, not a posting date. Remotive mirror returned403; its relative age does not prove freshness. Pay and duration undisclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="42" customHeight="1">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Mixed enterprise software/client engineering; no current qualifying stipend confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="42" customHeight="1">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>careers</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>ATS describes an edtech platform powered by Intellihire Staffing Solutions. Paid terms, no-fee status and current intake remain unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="42" customHeight="1">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in221?src=28</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Indexed copy crawled about five months before review. Below remote target and not the current in295 offer. Original publication date unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="42" customHeight="1">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote/jobs/design/ui-ux-internship-5888092</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Indexed crosspost; direct403. Employer ATS indexed evidence retained with current-intake caveat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="42" customHeight="1">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote/jobs/design/ui-ux-intern-6141465</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Indexed mirror returned404. Use employer-hosted in295 detail; mirror age is not employer posting date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="42" customHeight="1">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/jobs/ux-designer-job/</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="42" customHeight="1">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=bcc3ef8b70c9e52f</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Accessible; no stipend stated; Official role page has an application form but metadata originally dates to 11 October2022, modified8 April2025. Corresponding LinkedIn crosspost explicitly closed. Watchlist only; no active job card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="42" customHeight="1">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-and-ux-designer-fresher-at-bicsom-4439044957</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly no longer accepting applications; Official role page has an application form but metadata originally dates to 11 October2022, modified8 April2025. Corresponding LinkedIn crosspost explicitly closed. Watchlist only; no active job card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="42" customHeight="1">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>https://peerlist.io/company/parallelhq/careers/product-design-intern/jobhr86gnmbgaeadm2agkoddjro97e</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Historical advertisements only: archived Peerlist body INR25–30k/month versus INR30k header; earlier Jobgether INR20–30k/month and remote claim differ. No current offer or qualifying vacancy verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="42" customHeight="1">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Kixar</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/job-listing/ui-ux-designer-kixar-private-limited-JV_IC2939242_KO0%2C14_KE15%2C36.htm?jl=1010127226858</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="42" customHeight="1">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Melento</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=833d06c53f7e612d</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="42" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>BetterStory</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4722763-visual-design-intern</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="42" customHeight="1">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Redliner</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/q-ui-ux-internship-l-india-remote-jobs.html?vjk=68ca8d800a96d7da</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="42" customHeight="1">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Veril Studio</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.verilstudio.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Official design internship explicitly unpaid.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F225"/>
+  <autoFilter ref="A1:F242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11158,7 +11998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11230,7 +12070,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Reviewed public design search and selected company job details. Two eligible-region conditional leads retained with older dates and pay caveats. No newly confirmed qualifying monthly stipend.</t>
+          <t>Reviewed public design search and selected company job details. Two eligible-region conditional leads retained with older dates and pay caveats. No newly confirmed qualifying monthly stipend. Additional pass: Additional targeted public design/intern search produced no new verified eligible role. Older SuperKalam/Coulomb records remain older listings, not new postings.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -11263,7 +12103,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Direct filtered route was not accessible in the research tool; public YC employer pages provide overlapping job content.</t>
+          <t>Direct filtered route was not accessible in the research tool; public YC employer pages provide overlapping job content. Additional pass: Additional targeted public design/intern search produced no new verified eligible role. Older SuperKalam/Coulomb records remain older listings, not new postings.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -11296,7 +12136,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fetched the actual October2026 thread via Algolia API:266 top-level posts,25 mentioning designer/UX/design-engineer terms. No verified India-eligible UX/product internship or junior role from this pass. Cardog and Sundream retained as conditional company targets.</t>
+          <t>Fetched the actual October2026 thread via Algolia API:266 top-level posts,25 mentioning designer/UX/design-engineer terms. No verified India-eligible UX/product internship or junior role from this pass. Cardog and Sundream retained as conditional company targets. Additional pass: Additional Algolia API scan of266 top-level comments: strict designer/UX/UI/product-design terms matched20 (different methodology from prior25-term count). No additional paid India-eligible junior design internship verified.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -11362,11 +12202,19 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expanded targeted searches beyond four earlier listings. Four new relevant details retained with undisclosed stipend (Icogz, VictorFlow, Balusen, Gunadhya), plus genuine cross-post enrichments. Numerous other interns are below pay floor, unpaid, wrong discipline or expired; no inference that search counts equal relevant vacancies.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>Expanded targeted searches beyond four earlier listings. Four new relevant details retained with undisclosed stipend (Icogz, VictorFlow, Balusen, Gunadhya), plus genuine cross-post enrichments. Numerous other interns are below pay floor, unpaid, wrong discipline or expired; no inference that search counts equal relevant vacancies. Additional pass: Additional targeted check: BiCSoM fresher detail opened, but old original/closed LinkedIn makes it watchlist-only; Melento minimum INR11k is below target; Kixar and Redliner copies expired. No new qualifying Indeed vacancy added.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Kixar: INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.; Melento: Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.; Redliner: Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.; BiCSoM: Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -11391,10 +12239,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Direct/domain public queries again reported robots restrictions. No newly verified original Naukri role; existing employer-linked route retained. Account connection was not tested or required for these public-source checks; do not imply signed-in access.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>Direct/domain public queries again reported robots restrictions. No newly verified original Naukri role; existing employer-linked route retained. Account connection was not tested or required for these public-source checks; do not imply signed-in access. Additional pass: Targeted public queries again blocked by robots; no original or signed-in access verified and no new role invented.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
@@ -11420,10 +12272,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Qoruz junior product UX alternative found with annual pay preserved; Ungrammary matching internship adds below-target advertised pay context. Monsoonfish/Integra/AMPM below target and unrelated Product Management roles excluded. Current public examples were mostly below target: Integra Magna INR 3–5k/month, AMPM INR 10–15k/month, SDS INR 7–15k/month. BigThinkCode has an annual INR 1–3 lakh header and restrictive cohort/certification requirements, retained as company research. Ungrammary cross-post adds an annual range and inactive-recruiter caveat to an existing role.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>Qoruz junior product UX alternative found with annual pay preserved; Ungrammary matching internship adds below-target advertised pay context. Monsoonfish/Integra/AMPM below target and unrelated Product Management roles excluded. Current public examples were mostly below target: Integra Magna INR 3–5k/month, AMPM INR 10–15k/month, SDS INR 7–15k/month. BigThinkCode has an annual INR 1–3 lakh header and restrictive cohort/certification requirements, retained as company research. Ungrammary cross-post adds an annual range and inactive-recruiter caveat to an existing role. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>AMPM Network: ₹10–15k/mo, belowtarget; recruiterinactive; SDS softwares: ₹7–15k/mo; no current full-time students; immediatejoiners</t>
@@ -11453,10 +12309,14 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Targeted design searches found BigThinkCode deadline14 Oct 2026 and Virtual Tech2024closed; neither added as active. Competition/hackathon results are not jobs. Targeted search returned competitions with INR 30k prize pools rather than monthly internship pay. No competition prize was treated as an employer stipend.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t>Targeted design searches found BigThinkCode deadline14 Oct 2026 and Virtual Tech2024closed; neither added as active. Competition/hackathon results are not jobs. Targeted search returned competitions with INR 30k prize pools rather than monthly internship pay. No competition prize was treated as an employer stipend. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Pixel Paranoia UI/UX hackathon: Competitionprize30k, notinternstipend</t>
@@ -11486,10 +12346,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Public domain search reported robots restriction. No new original role verified; no CAPTCHA bypass or signed-in session attempted.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>Public domain search reported robots restriction. No new original role verified; no CAPTCHA bypass or signed-in session attempted. Additional pass: Additional public domain queries again robots-blocked; no original session or access-control bypass attempted.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
@@ -11515,10 +12379,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Targeted indexed design-intern/0–1 year queries produced no independently verified eligible detail in this pass. This is a coverage limitation, not proof of no jobs; authenticated matching workflow not inspected.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+          <t>Targeted indexed design-intern/0–1 year queries produced no independently verified eligible detail in this pass. This is a coverage limitation, not proof of no jobs; authenticated matching workflow not inspected. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
@@ -11544,13 +12412,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Several indexed internships were expired on direct check; accessible ads often unpaid or below target. Attira preserved as company/conditional research, no proven qualifying stipend. Accounts may be needed to apply/save, not to research these public detail pages.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>Several indexed internships were expired on direct check; accessible ads often unpaid or below target. Attira preserved as company/conditional research, no proven qualifying stipend. Accounts may be needed to apply/save, not to research these public detail pages. Additional pass: BetterStory remote INR25k visual internship detail opened; employer explicitly excludes product/UX scope, so not shortlisted.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid</t>
+          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid; BetterStory: INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.</t>
         </is>
       </c>
     </row>
@@ -11577,10 +12449,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Documented public API checks: India product-designer internships returned 0; UX internships returned 6, including five developer/graphic roles and GWEN fee-based training. Entry-level UI/UX search returned 6 records: one plausible junior opening at Energise.pro, an experienced Cloud Counselage role, a GitLab talent pool, adjacent QA and graphic roles. Category counts alone do not establish suitable vacancies.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>Documented public API checks: India product-designer internships returned 0; UX internships returned 6, including five developer/graphic roles and GWEN fee-based training. Entry-level UI/UX search returned 6 records: one plausible junior opening at Energise.pro, an experienced Cloud Counselage role, a GitLab talent pool, adjacent QA and graphic roles. Category counts alone do not establish suitable vacancies. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>GWEN: Applicant-paid training, no salary or job offer; Cloud Counselage: 2+years andKerala/TamilNadu residency; not a fresher role; GitLab: Explicit future talent pool, not current vacancy</t>
@@ -11610,10 +12486,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>No suitable India-eligible UX/product internship or fresher role verified in the examined public sample. Visible roles were predominantly senior/principal/manager or geographically restricted. Category-level Anywhere in the World labels are insufficient evidence of country eligibility.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>No suitable India-eligible UX/product internship or fresher role verified in the examined public sample. Visible roles were predominantly senior/principal/manager or geographically restricted. Category-level Anywhere in the World labels are insufficient evidence of country eligibility. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Workiva: Principal designer, UnitedStates; Cribl: Senior UX, UnitedStates</t>
@@ -11643,10 +12523,14 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>No suitable India-eligible UX/product internship or junior role verified from examined categories and junior filters. A junior brand-design example was Canada-only; a worldwide junior graphic role was outside the requested discipline.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>No suitable India-eligible UX/product internship or junior role verified from examined categories and junior filters. A junior brand-design example was Canada-only; a worldwide junior graphic role was outside the requested discipline. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Twine: Canada-only brand role; Twine: Graphic brand work; outside requested UX/product roles</t>
@@ -11671,15 +12555,19 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Limited public sample; full feed marketed behind paid access</t>
+          <t>Indexed leads with employer corroboration; mirror details403/404</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Opened design, India andinternpublicpages. No suitable UX/product internship or junior role verified; visible examples were geographic restrictions, senior, graphic/video or other disciplines. Did not bypass paid access or promise comprehensive coverage.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>Opened design, India andinternpublicpages. No suitable UX/product internship or junior role verified; visible examples were geographic restrictions, senior, graphic/video or other disciplines. Did not bypass paid access or promise comprehensive coverage. Additional pass: Unitedover mirror403 and Innovexis mirror404. Innovexis employer-hosted in295 detail accessible with undisclosed amount; Unitedover employer Dover index only, direct JS shell. Both kept on hold with separate verification limits; mirror relative dates are not original posting dates.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Blueprint Technologies: UX/CX roleArgentina; seniorexamplePhilippines; HOPn UG: GraphicinternGermany</t>
@@ -11709,10 +12597,14 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Examined public designcategory. Product/visual roles predominantly US-national orUSlocal/hybrid; no suitable Indiaeligibleintern/junior verified.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
+          <t>Examined public designcategory. Product/visual roles predominantly US-national orUSlocal/hybrid; no suitable Indiaeligibleintern/junior verified. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Databento: VisualDesignerUSnational; Discovery Education: ProductDesignerUSnational</t>
@@ -11737,15 +12629,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Page inaccessible through research tool; no verified leads</t>
+          <t>Alternate public category opened; no eligible detail verified</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Design URL could not be accessed and targetedpublicsearch yielded no independently verifiable matching detail. This is an access/coverage gap, not evidence of no jobs.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t>Design URL could not be accessed and targetedpublicsearch yielded no independently verifiable matching detail. This is an access/coverage gap, not evidence of no jobs. Additional pass: Alternate /remote-entry-level-product-design-jobs page opened. No new India-eligible internship/junior employer detail verified; index/category labels alone do not establish experience or geography.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
@@ -11771,10 +12667,14 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Public landing page and eligible-city links inspected. Useful for finding potential employers by city/sector; a hiring filter is not proof of a UX internship. Follow individual company sites to verify roles.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>Public landing page and eligible-city links inspected. Useful for finding potential employers by city/sector; a hiring filter is not proof of a UX internship. Follow individual company sites to verify roles. Additional pass: Public discovery page reopened; no vacancy inferred from map membership or funding/rank. Role acceptance still requires employer/job-detail evidence.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
@@ -11800,10 +12700,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Accessible India startup directory includes existing targets such as Swiggy, Meesho, Groww and Juspay. Rankings/funding do not establish an active business, stipend or design vacancy; verify official careers.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>Accessible India startup directory includes existing targets such as Swiggy, Meesho, Groww and Juspay. Rankings/funding do not establish an active business, stipend or design vacancy; verify official careers. Additional pass: Public discovery page reopened; no vacancy inferred from map membership or funding/rank. Role acceptance still requires employer/job-detail evidence.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
@@ -11829,10 +12733,14 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Public map and methodology explain registered companies and coordinate limits. Registration, scheme membership and funding signals do not establish current hiring; no vacancy inferred.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>Public map and methodology explain registered companies and coordinate limits. Registration, scheme membership and funding signals do not establish current hiring; no vacancy inferred. Additional pass: Public discovery page reopened; no vacancy inferred from map membership or funding/rank. Role acceptance still requires employer/job-detail evidence.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
@@ -11861,11 +12769,114 @@
           <t>Indexed directory discovered, but direct page timed out. No new role or employer contact was verified from this source.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Targeted public checks</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>New Arihant AI and Innovexis employer-hosted internships have undisclosed pay; Unitedover indexed employer ATS remains current-intake unverified. Parallel internship archived; BiCSoM historical fresher page is watchlist-only.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Public sample only; no exhaustive or authenticated access claim.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/search?q=product%20design%20intern%20India</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Targeted public checks</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Targeted indexed UX/product/interaction internship searches produced no newly independently verified original X hiring post. Existing Wint/BThree crossposts retained; no claim of original authenticated access.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Public sample only; no exhaustive or authenticated access claim.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Targeted public checks</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Targeted early-career searches used as corroboration. BiCSoM crosspost explicitly closed; no new LinkedIn-primary role added. Relative ages are not verified original posting dates.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Public sample only; no exhaustive or authenticated access claim.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11876,7 +12887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12655,7 +13666,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Suggested exploratory specialist-studio target with remote design work; pay range overlaps the conditional band.</t>
+          <t>Specialist product-design studio to monitor; internship pay evidence is historical and arrangements conflict across old copies.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -12686,7 +13697,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Treat as historical/unverified rather than a live job. Official careers page is accessible but did not independently confirm this internship or stipend.</t>
+          <t>Historical advertisements only: archived Peerlist body INR25–30k/month versus INR30k header; earlier Jobgether INR20–30k/month and remote claim differ. No current offer or qualifying vacancy verified.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -17246,8 +18257,212 @@
         </is>
       </c>
     </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Eligible-region enterprise-interface work; scope is relevant but compensation and intake are unresolved.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current monthly stipend established.</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Exploratory remote edtech-product target; separate employment from course/training activity.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Historical separate employer-hosted advertisement</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Intern — separate older ATS listing in221</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Indexed copy crawled about five months before review. Below remote target and not the current in295 offer. Original publication date unknown.</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in221?src=28</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Exploratory remote-India design lead; employer identity, current intake and pay need confirmation.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current monthly stipend established.</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Eligible-city studio with a published fresher role family; an old form is insufficient evidence of a current vacancy.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current monthly stipend established.</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/job-openings/</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M112"/>
+  <autoFilter ref="A1:M116"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Dream,Workable,Possible"</formula1>
@@ -17382,6 +18597,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17393,7 +18613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18062,12 +19282,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Remote India reported in third-party internship description</t>
+          <t>Archived Peerlist internship: Bengaluru office; older Jobgether mirror said remote. Confirm each new intake.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Company watchlist; not a verified current vacancy</t>
+          <t>Watchlist; Peerlist internship archived, new intake unverified</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -18080,9 +19300,21 @@
           <t>https://www.parallelhq.com/careers</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>hr@parallelhq.com</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.parallelhq.com/careers</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Published recruitment enquiries; not an open-role guarantee</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -24359,8 +25591,264 @@
         </is>
       </c>
     </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise ERP and AI software engineering</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Advertised internship; pay and intake require confirmation</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>careers@arihantai.com</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Candidate enquiries / recruitment, explicitly published on careers page</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Mixed enterprise software/client engineering; no current qualifying stipend confirmed.</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Education technology and training</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Bengaluru-based employer description</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Advertised internship; pay and intake require confirmation</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>ATS describes an edtech platform powered by Intellihire Staffing Solutions. Paid terms, no-fee status and current intake remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Digital products; ownership/business model unverified</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Remote (India), full-time</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Indexed internship; live intake unverified</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Directory target based on indexed employer ATS; no independent company-wide hiring or product-business claim.</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Design studio</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Digital product design and development</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; office role with six-day week</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Historical fresher page; current intake unverified, LinkedIn crosspost closed</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/job-openings/</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/job-openings/</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Official role page has an application form but metadata originally dates to 11 October2022, modified8 April2025. Corresponding LinkedIn crosspost explicitly closed. Watchlist only; no active job card.</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M112"/>
+  <autoFilter ref="A1:M116"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -24374,200 +25862,209 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId215"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24579,7 +26076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -24772,37 +26269,37 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>F1studioz</t>
+          <t>Parallel</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UX Intern</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Internship — archived</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru; in-office</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+          <t>https://peerlist.io/company/parallelhq/careers/product-design-intern/jobhr86gnmbgaeadm2agkoddjro97e</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Original Indeed detail accessible without an expiry banner; official careers page corroborates employer and application channel, not a unique role detail. Actual application submission flow not tested. General company hybrid policy does not establish this role's work mode.</t>
+          <t>Archived advertisement; not current intake</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Practice projects accepted in portfolio; Final-semester B.Des/M.Des or engineering student/graduate with UX skills; AI tools and enterprise UX interest; possible full-time availability.</t>
+          <t>Portfolio and Figma-based product design</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -24815,37 +26312,37 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Moon Technolabs</t>
+          <t>Parallel</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Trainee UI/UX Designer</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship — archived</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat</t>
+          <t>Bengaluru; in-office</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
+          <t>https://peerlist.io/company/parallelhq/careers/product-design-intern/jobhr86gnmbgaeadm2agkoddjro97e</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail accessible; official careers page lists Trainee UI/UX Designer with experience Fresher. Submission not tested; this is a junior job alternative, not an internship.</t>
+          <t>Archived advertisement; not current intake</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Figma or Adobe XD; Wireframes, prototypes, research and design systems; Bachelor's graduate and developer handoff skills.</t>
+          <t>Research, systems, prototyping and engineering collaboration</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -24858,37 +26355,37 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Zunderdog</t>
+          <t>Parallel</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Design Intern</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Internship — archived</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Pune; remote for now</t>
+          <t>Bengaluru; in-office</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+          <t>https://peerlist.io/company/parallelhq/careers/product-design-intern/jobhr86gnmbgaeadm2agkoddjro97e</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Official role and application form accessible. Employer prefers candidates in or near Pune. Remote arrangement is temporary; no promise of permanent remote. Application form not submitted.</t>
+          <t>Archived advertisement; not current intake</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Figma basics; Few college, personal or professional design projects; Layout, wireframes, simple prototypes and checking developed screens.</t>
+          <t>Duration wording varies between four-month minimum and six months</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -24901,37 +26398,37 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Zunderdog</t>
+          <t>F1studioz</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Designer (Fresher)</t>
+          <t>UX Intern</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Pune; remote for now</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Official role and application form accessible; Indeed discovery was a search result, not a uniquely verified job-detail URL. Employer prefers Pune or nearby candidates; current remote arrangement may change.</t>
+          <t>Original Indeed detail accessible without an expiry banner; official careers page corroborates employer and application channel, not a unique role detail. Actual application submission flow not tested. General company hybrid policy does not establish this role's work mode.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Figma and portfolio; personal/college/freelance work accepted; Flows, prototypes, accessible UI and design systems; Developer collaboration and usability reviews.</t>
+          <t>Practice projects accepted in portfolio; Final-semester B.Des/M.Des or engineering student/graduate with UX skills; AI tools and enterprise UX interest; possible full-time availability.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -24944,37 +26441,37 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Keyideas Infotech</t>
+          <t>Moon Technolabs</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Design Intern</t>
+          <t>Trainee UI/UX Designer</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Remote India (confirm eligibility)</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Current accessible employer role page explicitly links this Naukri application. Original Naukri page is robots-blocked, so activity of that particular Naukri listing is unverified. Employer says remote; Naukri slug says Gurgaon. Confirm remote India eligibility and current application link.</t>
+          <t>Indeed detail accessible; official careers page lists Trainee UI/UX Designer with experience Fresher. Submission not tested; this is a junior job alternative, not an internship.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>B.Des/M.Des or relevant design qualification; Figma and Illustrator; Research/usability, web/mobile design, components and brand styles.</t>
+          <t>Figma or Adobe XD; Wireframes, prototypes, research and design systems; Bachelor's graduate and developer handoff skills.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -24987,12 +26484,12 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Techolution</t>
+          <t>Zunderdog</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UX Design Intern</t>
+          <t>UI/UX Design Intern</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -25002,22 +26499,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad / remote claim requires confirmation</t>
+          <t>Pune; remote for now</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail accessible; official careers index also lists UX Designer–Intern in Hyderabad. Remote statement in Indeed conflicts with Hyderabad in current company index. Official careers site is dynamic; indexed role corroboration is stronger than its text-only rendering.</t>
+          <t>Official role and application form accessible. Employer prefers candidates in or near Pune. Remote arrangement is temporary; no promise of permanent remote. Application form not submitted.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Portfolio and Figma; Interaction/UX/graphic design or related degree; Research, wireframes, prototypes and developer specifications.</t>
+          <t>Figma basics; Few college, personal or professional design projects; Layout, wireframes, simple prototypes and checking developed screens.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -25030,37 +26527,37 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Zunderdog</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Senior Product Designer (AI Builder)</t>
+          <t>UI/UX Designer (Fresher)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Senior; outside internship target</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pune; remote for now</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4745511005</t>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Official job indexed; detailed requirements not assessed</t>
+          <t>Official role and application form accessible; Indeed discovery was a search result, not a uniquely verified job-detail URL. Employer prefers Pune or nearby candidates; current remote arrangement may change.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Figma and portfolio; personal/college/freelance work accepted; Flows, prototypes, accessible UI and design systems; Developer collaboration and usability reviews.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -25073,37 +26570,37 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Keyideas Infotech</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lead Product Designer</t>
+          <t>UI/UX Design Intern</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Lead; outside internship target</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote India (confirm eligibility)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/PHONEPELIMITED/1000000000004131-lead-product-designer</t>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Official job indexed; detailed requirements not assessed</t>
+          <t>Current accessible employer role page explicitly links this Naukri application. Original Naukri page is robots-blocked, so activity of that particular Naukri listing is unverified. Employer says remote; Naukri slug says Gurgaon. Confirm remote India eligibility and current application link.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>B.Des/M.Des or relevant design qualification; Figma and Illustrator; Research/usability, web/mobile design, components and brand styles.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -25116,37 +26613,37 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Techolution</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Product Design Manager</t>
+          <t>UX Design Intern</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Manager; outside internship target</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Location not verified</t>
+          <t>Hyderabad / remote claim requires confirmation</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://wormhole.jupiter.money/website/career/application-form/?designation=Product+Design+Manager&amp;requisitionId=566</t>
+          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Official application indexed; details not verified</t>
+          <t>Indeed detail accessible; official careers index also lists UX Designer–Intern in Hyderabad. Remote statement in Indeed conflicts with Hyderabad in current company index. Official careers site is dynamic; indexed role corroboration is stronger than its text-only rendering.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Portfolio and Figma; Interaction/UX/graphic design or related degree; Research, wireframes, prototypes and developer specifications.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -25159,17 +26656,17 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Whatfix</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Product Design Lead (Manager)</t>
+          <t>Senior Product Designer (AI Builder)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Lead / manager; outside internship target</t>
+          <t>Senior; outside internship target</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -25179,12 +26676,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://whatfix101.hire.trakstar.com/?country=India&amp;rsu=mile&amp;state=Karnataka</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4745511005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Official board indexed; detailed requirements not assessed</t>
+          <t>Official job indexed; detailed requirements not assessed</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -25202,37 +26699,37 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>WebEngage</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Senior User Experience Designer</t>
+          <t>Lead Product Designer</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Senior; 3+ years in indexed text</t>
+          <t>Lead; outside internship target</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Location not verified</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://webengage.hire.trakstar.com/jobs/fk0pgmn/</t>
+          <t>https://jobs.smartrecruiters.com/PHONEPELIMITED/1000000000004131-lead-product-designer</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Stale or unavailable: direct role URL returned 404</t>
+          <t>Official job indexed; detailed requirements not assessed</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Indexed text asks for at least three years in product research, UX, UI or similar</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -25245,32 +26742,32 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LeadSquared</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Intern - Product Design (Job_444)</t>
+          <t>Product Design Manager</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Internship; indexed board result</t>
+          <t>Manager; outside internship target</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka, India</t>
+          <t>Location not verified</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/q-product-design-intern-l-bengaluru%2C-karnataka-jobs.html</t>
+          <t>https://wormhole.jupiter.money/website/career/application-form/?designation=Product+Design+Manager&amp;requisitionId=566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Indeed index only; official role/application not verified</t>
+          <t>Official application indexed; details not verified</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -25288,32 +26785,32 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BookMyShow</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Senior Executive - Graphic Design</t>
+          <t>Product Design Lead (Manager)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Experienced / adjacent discipline</t>
+          <t>Lead / manager; outside internship target</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://bookmyshow.hire.trakstar.com/jobs/fk0ztil/</t>
+          <t>https://whatfix101.hire.trakstar.com/?country=India&amp;rsu=mile&amp;state=Karnataka</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Official role and board indexed; full JD not assessed</t>
+          <t>Official board indexed; detailed requirements not assessed</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -25331,37 +26828,37 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>WebEngage</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern</t>
+          <t>Senior User Experience Designer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Senior; 3+ years in indexed text</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India; office five days/week</t>
+          <t>Location not verified</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+          <t>https://webengage.hire.trakstar.com/jobs/fk0pgmn/</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible</t>
+          <t>Stale or unavailable: direct role URL returned 404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Design/HCI-related degree in progress or completed, or equivalent experience</t>
+          <t>Indexed text asks for at least three years in product research, UX, UI or similar</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -25374,37 +26871,37 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>LeadSquared</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern</t>
+          <t>Intern - Product Design (Job_444)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Internship; indexed board result</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India; office five days/week</t>
+          <t>Bangalore, Karnataka, India</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+          <t>https://in.indeed.com/q-product-design-intern-l-bengaluru%2C-karnataka-jobs.html</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible</t>
+          <t>Indeed index only; official role/application not verified</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Portfolio demonstrating digital-product thinking and execution</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -25417,37 +26914,37 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>BookMyShow</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern</t>
+          <t>Senior Executive - Graphic Design</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Experienced / adjacent discipline</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India; office five days/week</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+          <t>https://bookmyshow.hire.trakstar.com/jobs/fk0ztil/</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible</t>
+          <t>Official role and board indexed; full JD not assessed</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Familiarity with tools such as Figma, Adobe Creative Suite and Claude Code</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -25490,7 +26987,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Communication and collaboration; ability to commit six months</t>
+          <t>Design/HCI-related degree in progress or completed, or equivalent experience</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -25533,7 +27030,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Bonus: research/usability testing, design systems and accessibility</t>
+          <t>Portfolio demonstrating digital-product thinking and execution</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -25546,27 +27043,27 @@
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Frappe</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher: 0–2 years</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Location not specified on JD; careers policy encourages remote work</t>
+          <t>Bengaluru, India; office five days/week</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://frappe.io/careers/open-positions/designer</t>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -25576,7 +27073,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0–2 years experience</t>
+          <t>Familiarity with tools such as Figma, Adobe Creative Suite and Claude Code</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -25589,27 +27086,27 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Frappe</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher: 0–2 years</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Location not specified on JD; careers policy encourages remote work</t>
+          <t>Bengaluru, India; office five days/week</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://frappe.io/careers/open-positions/designer</t>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -25619,7 +27116,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Figma or comparable modern UI tools</t>
+          <t>Communication and collaboration; ability to commit six months</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -25632,27 +27129,27 @@
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Frappe</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher: 0–2 years</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Location not specified on JD; careers policy encourages remote work</t>
+          <t>Bengaluru, India; office five days/week</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://frappe.io/careers/open-positions/designer</t>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -25662,7 +27159,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Fast iteration</t>
+          <t>Bonus: research/usability testing, design systems and accessibility</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -25705,7 +27202,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Strong writing</t>
+          <t>0–2 years experience</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -25748,7 +27245,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Product thinking</t>
+          <t>Figma or comparable modern UI tools</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -25791,7 +27288,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Illustration is a bonus</t>
+          <t>Fast iteration</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -25804,37 +27301,37 @@
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Atomicwork</t>
+          <t>Frappe</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Design engineer</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Seniority not specified in accessible careers-page title</t>
+          <t>Junior / fresher: 0–2 years</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, IN</t>
+          <t>Location not specified on JD; careers policy encourages remote work</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://www.atomicwork.com/company/careers</t>
+          <t>https://frappe.io/careers/open-positions/designer</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Official careers page directly shows role title; full JD not assessed</t>
+          <t>Official role detail accessible</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Strong writing</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -25847,27 +27344,27 @@
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Juno</t>
+          <t>Frappe</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Junior / fresher: 0–2 years</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, onsite</t>
+          <t>Location not specified on JD; careers policy encourages remote work</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
+          <t>https://frappe.io/careers/open-positions/designer</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -25877,7 +27374,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Experience participating in several product shipping cycles</t>
+          <t>Product thinking</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -25890,27 +27387,27 @@
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Juno</t>
+          <t>Frappe</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Junior / fresher: 0–2 years</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, onsite</t>
+          <t>Location not specified on JD; careers policy encourages remote work</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
+          <t>https://frappe.io/careers/open-positions/designer</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -25920,7 +27417,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>High-fidelity mockups and prototyping using tools such as Figma, Rive and ProtoPie</t>
+          <t>Illustration is a bonus</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -25933,37 +27430,37 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Juno</t>
+          <t>Atomicwork</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern</t>
+          <t>Design engineer</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Seniority not specified in accessible careers-page title</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, onsite</t>
+          <t>Bangalore, IN</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
+          <t>https://www.atomicwork.com/company/careers</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible</t>
+          <t>Official careers page directly shows role title; full JD not assessed</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Strong visual execution</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -26006,7 +27503,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Clear communication and collaboration</t>
+          <t>Experience participating in several product shipping cycles</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -26049,7 +27546,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Bonus: motion and micro-interactions</t>
+          <t>High-fidelity mockups and prototyping using tools such as Figma, Rive and ProtoPie</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -26062,7 +27559,7 @@
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>Juno</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -26077,12 +27574,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru or remote India</t>
+          <t>Bengaluru, onsite</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -26092,7 +27589,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Figma and ability to turn ideas into polished UI</t>
+          <t>Strong visual execution</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -26105,7 +27602,7 @@
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>Juno</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -26120,12 +27617,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru or remote India</t>
+          <t>Bengaluru, onsite</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -26135,7 +27632,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Typography, layout, spacing and hierarchy</t>
+          <t>Clear communication and collaboration</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -26148,7 +27645,7 @@
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>Juno</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -26163,12 +27660,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru or remote India</t>
+          <t>Bengaluru, onsite</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -26178,7 +27675,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Product judgement and communication</t>
+          <t>Bonus: motion and micro-interactions</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -26221,7 +27718,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Demonstrable shipped or built work and independent ownership</t>
+          <t>Figma and ability to turn ideas into polished UI</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -26234,12 +27731,12 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Lokal</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Product Designer Intern</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -26249,22 +27746,22 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, onsite in search-indexed text</t>
+          <t>Bengaluru or remote India</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/lokal-app/j/CB2EDD7186</t>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Official ATS URL indexed; direct readable body empty</t>
+          <t>Official role detail accessible</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Typography, layout, spacing and hierarchy</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -26277,37 +27774,37 @@
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NetBramha Studios</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Senior UX Designer</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru or remote India</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://www.netbramha.com/careers</t>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Official role detail accessible</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5+ years professional experience</t>
+          <t>Product judgement and communication</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -26320,37 +27817,37 @@
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Lollypop Design Studio</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Associate UX Researcher</t>
+          <t>Product Design Intern</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Associate / experienced</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Mumbai, Chennai or Hyderabad</t>
+          <t>Bengaluru or remote India</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://lollypop.design/careers/associate-ux-researcher-jobs/</t>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Official role detail accessible</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1–3 years UX/design research experience</t>
+          <t>Demonstrable shipped or built work and independent ownership</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -26363,37 +27860,37 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Lollypop Design Studio</t>
+          <t>Lokal</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Associate UX Researcher</t>
+          <t>Product Designer Intern</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Associate / experienced</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Mumbai, Chennai or Hyderabad</t>
+          <t>Bengaluru, onsite in search-indexed text</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>https://lollypop.design/careers/associate-ux-researcher-jobs/</t>
+          <t>https://apply.workable.com/lokal-app/j/CB2EDD7186</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Official ATS URL indexed; direct readable body empty</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Relevant graduate/postgraduate degree</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -26406,27 +27903,27 @@
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Lollypop Design Studio</t>
+          <t>NetBramha Studios</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Associate UX Researcher</t>
+          <t>Senior UX Designer</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Associate / experienced</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Mumbai, Chennai or Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>https://lollypop.design/careers/associate-ux-researcher-jobs/</t>
+          <t>https://www.netbramha.com/careers</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -26436,7 +27933,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Qualitative research, interviews and usability testing</t>
+          <t>5+ years professional experience</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -26479,7 +27976,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Research synthesis and clear communication</t>
+          <t>1–3 years UX/design research experience</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -26522,7 +28019,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Figma/FigJam/Miro/Notion/Dovetail or similar tools</t>
+          <t>Relevant graduate/postgraduate degree</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -26535,27 +28032,27 @@
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Aubergine Solutions</t>
+          <t>Lollypop Design Studio</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Design internship program</t>
+          <t>Associate UX Researcher</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Internship program</t>
+          <t>Associate / experienced</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Ahmedabad; confirm role work mode</t>
+          <t>Bengaluru, Mumbai, Chennai or Hyderabad</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://www.aubergine.co/internships</t>
+          <t>https://lollypop.design/careers/associate-ux-researcher-jobs/</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -26565,7 +28062,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Qualitative research, interviews and usability testing</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -26578,37 +28075,37 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Yellowchalk Design</t>
+          <t>Lollypop Design Studio</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>Associate UX Researcher</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Associate / experienced</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru; confirm role location</t>
+          <t>Bengaluru, Mumbai, Chennai or Hyderabad</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>https://yellowchalk.com/careers/</t>
+          <t>https://lollypop.design/careers/associate-ux-researcher-jobs/</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Search-indexed official role page; not directly opened</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2–3 years relevant experience</t>
+          <t>Research synthesis and clear communication</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -26621,37 +28118,37 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Yellowchalk Design</t>
+          <t>Lollypop Design Studio</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>Associate UX Researcher</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Associate / experienced</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru; confirm role location</t>
+          <t>Bengaluru, Mumbai, Chennai or Hyderabad</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>https://yellowchalk.com/careers/</t>
+          <t>https://lollypop.design/careers/associate-ux-researcher-jobs/</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Search-indexed official role page; not directly opened</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Portfolio demonstrating web/mobile UI work</t>
+          <t>Figma/FigJam/Miro/Notion/Dovetail or similar tools</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -26664,37 +28161,37 @@
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Yellowchalk Design</t>
+          <t>Aubergine Solutions</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>Design internship program</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Internship program</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru; confirm role location</t>
+          <t>Ahmedabad; confirm role work mode</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>https://yellowchalk.com/careers/</t>
+          <t>https://www.aubergine.co/internships</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Search-indexed official role page; not directly opened</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Communication and developer handoff</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -26737,7 +28234,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Photoshop/Illustrator or other design tools</t>
+          <t>2–3 years relevant experience</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -26750,37 +28247,37 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Ungrammary</t>
+          <t>Yellowchalk Design</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>UX/UI Design Intern</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Mumbai / Remote</t>
+          <t>Bengaluru; confirm role location</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+          <t>https://yellowchalk.com/careers/</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Search-indexed official role page; not directly opened</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Graduate eligibility; not an academic-project placement</t>
+          <t>Portfolio demonstrating web/mobile UI work</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -26793,37 +28290,37 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Ungrammary</t>
+          <t>Yellowchalk Design</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>UX/UI Design Intern</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Mumbai / Remote</t>
+          <t>Bengaluru; confirm role location</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+          <t>https://yellowchalk.com/careers/</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Search-indexed official role page; not directly opened</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Six-month availability</t>
+          <t>Communication and developer handoff</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -26836,37 +28333,37 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Ungrammary</t>
+          <t>Yellowchalk Design</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>UX/UI Design Intern</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Mumbai / Remote</t>
+          <t>Bengaluru; confirm role location</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+          <t>https://yellowchalk.com/careers/</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Search-indexed official role page; not directly opened</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Strong UI/UX portfolio</t>
+          <t>Photoshop/Illustrator or other design tools</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -26909,7 +28406,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Figma and Google Material Design</t>
+          <t>Graduate eligibility; not an academic-project placement</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -26952,7 +28449,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Typography, visual and interaction design fundamentals</t>
+          <t>Six-month availability</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -26995,7 +28492,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Written/verbal/video communication</t>
+          <t>Strong UI/UX portfolio</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -27038,7 +28535,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Application: resume, portfolio and 2–3 minute intro video</t>
+          <t>Figma and Google Material Design</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -27056,22 +28553,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Associate UX/UI Designer</t>
+          <t>UX/UI Design Intern</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Mumbai / Remote headline; body says hybrid</t>
+          <t>Mumbai / Remote</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>https://club.ungrammary.com/ugjobs</t>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -27081,7 +28578,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1–2 years experience</t>
+          <t>Typography, visual and interaction design fundamentals</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -27099,22 +28596,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Associate UX/UI Designer</t>
+          <t>UX/UI Design Intern</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Mumbai / Remote headline; body says hybrid</t>
+          <t>Mumbai / Remote</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>https://club.ungrammary.com/ugjobs</t>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -27124,7 +28621,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Figma proficiency</t>
+          <t>Written/verbal/video communication</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -27142,22 +28639,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Associate UX/UI Designer</t>
+          <t>UX/UI Design Intern</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Mumbai / Remote headline; body says hybrid</t>
+          <t>Mumbai / Remote</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>https://club.ungrammary.com/ugjobs</t>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -27167,7 +28664,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Strong portfolio</t>
+          <t>Application: resume, portfolio and 2–3 minute intro video</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -27210,7 +28707,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Wireframes and design systems</t>
+          <t>1–2 years experience</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -27223,27 +28720,27 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Prismic Reflections</t>
+          <t>Ungrammary</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Product / UX / UI design general application</t>
+          <t>Associate UX/UI Designer</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Internship / Junior interest</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Confirm location</t>
+          <t>Mumbai / Remote headline; body says hybrid</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/15DMSVUBV_q-Zg3beowKo9PQJtujVGrKVUMWibs1iJ4k/viewform</t>
+          <t>https://club.ungrammary.com/ugjobs</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -27253,7 +28750,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Portfolio URL</t>
+          <t>Figma proficiency</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -27266,27 +28763,27 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Prismic Reflections</t>
+          <t>Ungrammary</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Product / UX / UI design general application</t>
+          <t>Associate UX/UI Designer</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Internship / Junior interest</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Confirm location</t>
+          <t>Mumbai / Remote headline; body says hybrid</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/15DMSVUBV_q-Zg3beowKo9PQJtujVGrKVUMWibs1iJ4k/viewform</t>
+          <t>https://club.ungrammary.com/ugjobs</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -27296,7 +28793,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Select desired design role and seniority</t>
+          <t>Strong portfolio</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -27309,27 +28806,27 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Prismic Reflections</t>
+          <t>Ungrammary</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Product / UX / UI design general application</t>
+          <t>Associate UX/UI Designer</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Internship / Junior interest</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Confirm location</t>
+          <t>Mumbai / Remote headline; body says hybrid</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/15DMSVUBV_q-Zg3beowKo9PQJtujVGrKVUMWibs1iJ4k/viewform</t>
+          <t>https://club.ungrammary.com/ugjobs</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -27339,7 +28836,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Brief career background</t>
+          <t>Wireframes and design systems</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -27352,37 +28849,37 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Nonlinear</t>
+          <t>Prismic Reflections</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>UX/UI Design Intern</t>
+          <t>Product / UX / UI design general application</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Internship / Junior interest</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in-office</t>
+          <t>Confirm location</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>https://nonlinear.in/careers</t>
+          <t>https://docs.google.com/forms/d/15DMSVUBV_q-Zg3beowKo9PQJtujVGrKVUMWibs1iJ4k/viewform</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Search-indexed official role page; not directly opened</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Hands-on Figma</t>
+          <t>Portfolio URL</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -27395,37 +28892,37 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Nonlinear</t>
+          <t>Prismic Reflections</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>UX/UI Design Intern</t>
+          <t>Product / UX / UI design general application</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Internship / Junior interest</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in-office</t>
+          <t>Confirm location</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>https://nonlinear.in/careers</t>
+          <t>https://docs.google.com/forms/d/15DMSVUBV_q-Zg3beowKo9PQJtujVGrKVUMWibs1iJ4k/viewform</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Search-indexed official role page; not directly opened</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>UX and interaction design fundamentals</t>
+          <t>Select desired design role and seniority</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -27438,37 +28935,37 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Nonlinear</t>
+          <t>Prismic Reflections</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>UX/UI Design Intern</t>
+          <t>Product / UX / UI design general application</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Internship / Junior interest</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in-office</t>
+          <t>Confirm location</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>https://nonlinear.in/careers</t>
+          <t>https://docs.google.com/forms/d/15DMSVUBV_q-Zg3beowKo9PQJtujVGrKVUMWibs1iJ4k/viewform</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Search-indexed official role page; not directly opened</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Personas, wireframes, mockups and prototypes</t>
+          <t>Brief career background</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -27511,7 +29008,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3–4 months availability</t>
+          <t>Hands-on Figma</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -27554,7 +29051,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Up to three sample designs / portfolio</t>
+          <t>UX and interaction design fundamentals</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -27597,7 +29094,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Two-hour design challenge followed by interview</t>
+          <t>Personas, wireframes, mockups and prototypes</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -27610,37 +29107,37 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Aufait UX</t>
+          <t>Nonlinear</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>UX/UI Design Intern</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Experience level not specified</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Bengaluru, in-office</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>https://www.aufaitux.com/job/ui-designer/</t>
+          <t>https://nonlinear.in/careers</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Search-indexed official role page; not directly opened</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Figma or Sketch</t>
+          <t>3–4 months availability</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -27653,37 +29150,37 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Aufait UX</t>
+          <t>Nonlinear</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>UX/UI Design Intern</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Experience level not specified</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Bengaluru, in-office</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>https://www.aufaitux.com/job/ui-designer/</t>
+          <t>https://nonlinear.in/careers</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Search-indexed official role page; not directly opened</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Visual interface design from flows/wireframes</t>
+          <t>Up to three sample designs / portfolio</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -27696,37 +29193,37 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Aufait UX</t>
+          <t>Nonlinear</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>UX/UI Design Intern</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Experience level not specified</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Bengaluru, in-office</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>https://www.aufaitux.com/job/ui-designer/</t>
+          <t>https://nonlinear.in/careers</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Search-indexed official role page; not directly opened</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Communication and attention to detail</t>
+          <t>Two-hour design challenge followed by interview</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -27769,7 +29266,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Feedback and current UI practices</t>
+          <t>Figma or Sketch</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -27787,12 +29284,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Experience level not specified</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -27802,7 +29299,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>https://www.aufaitux.com/job/ux-designer/</t>
+          <t>https://www.aufaitux.com/job/ui-designer/</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -27812,7 +29309,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2+ years professional UX experience</t>
+          <t>Visual interface design from flows/wireframes</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -27830,12 +29327,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Experience level not specified</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -27845,7 +29342,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>https://www.aufaitux.com/job/ux-designer/</t>
+          <t>https://www.aufaitux.com/job/ui-designer/</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -27855,7 +29352,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Figma wireframes, prototypes and handoff</t>
+          <t>Communication and attention to detail</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -27873,12 +29370,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Experience level not specified</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -27888,7 +29385,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>https://www.aufaitux.com/job/ux-designer/</t>
+          <t>https://www.aufaitux.com/job/ui-designer/</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -27898,7 +29395,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Research synthesis and usability testing</t>
+          <t>Feedback and current UI practices</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -27941,7 +29438,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Client communication</t>
+          <t>2+ years professional UX experience</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -27954,37 +29451,37 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WowMakers</t>
+          <t>Aufait UX</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Visual Designer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>https://www.wowmakers.com/careers/</t>
+          <t>https://www.aufaitux.com/job/ux-designer/</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Official page, old date 20 September 2022</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Figma wireframes, prototypes and handoff</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -27997,37 +29494,37 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>WowMakers</t>
+          <t>Aufait UX</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Senior Interaction Designer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>https://www.wowmakers.com/careers/</t>
+          <t>https://www.aufaitux.com/job/ux-designer/</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Official page, old date 28 June 2022</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Research synthesis and usability testing</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -28040,27 +29537,27 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Octet Design Studio</t>
+          <t>Aufait UX</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Junior / experienced</t>
+          <t>Experienced</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>https://octet.design/careers/</t>
+          <t>https://www.aufaitux.com/job/ux-designer/</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -28070,7 +29567,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1–2 years experience</t>
+          <t>Client communication</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -28083,37 +29580,37 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Octet Design Studio</t>
+          <t>WowMakers</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>UI UX Designer</t>
+          <t>Visual Designer</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Junior / experienced</t>
+          <t>Not verified</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>https://octet.design/careers/</t>
+          <t>https://www.wowmakers.com/careers/</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Official page, old date 20 September 2022</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1+ years experience</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -28126,12 +29623,12 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Octet Design Studio</t>
+          <t>WowMakers</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Senior UX Designer</t>
+          <t>Senior Interaction Designer</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -28141,22 +29638,22 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>https://octet.design/careers/</t>
+          <t>https://www.wowmakers.com/careers/</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Official career page observed</t>
+          <t>Official page, old date 28 June 2022</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>4–5 years experience</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -28169,27 +29666,27 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Userfacet</t>
+          <t>Octet Design Studio</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Senior UI/UX Designer</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Junior / experienced</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>https://www.userfacet.com/careers</t>
+          <t>https://octet.design/careers/</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -28199,7 +29696,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>3–5 years experience</t>
+          <t>1–2 years experience</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -28212,37 +29709,37 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ZEUX Innovation</t>
+          <t>Octet Design Studio</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>UX Design Intern</t>
+          <t>UI UX Designer</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Junior / experienced</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Confirm Mumbai / onsite</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/zeux-innovation_most-people-look-for-a-job-were-looking-activity-7459837297631457281-ZGJ3</t>
+          <t>https://octet.design/careers/</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Indexed employer LinkedIn post; displayed3months old</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Six-month program described</t>
+          <t>1+ years experience</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -28255,37 +29752,37 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ZEUX Innovation</t>
+          <t>Octet Design Studio</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>UX Design Intern</t>
+          <t>Senior UX Designer</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Confirm Mumbai / onsite</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/zeux-innovation_most-people-look-for-a-job-were-looking-activity-7459837297631457281-ZGJ3</t>
+          <t>https://octet.design/careers/</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Indexed employer LinkedIn post; displayed3months old</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>One-minute introductory video</t>
+          <t>4–5 years experience</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -28298,37 +29795,37 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ZEUX Innovation</t>
+          <t>Userfacet</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>UX Design Intern</t>
+          <t>Senior UI/UX Designer</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Confirm Mumbai / onsite</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/zeux-innovation_most-people-look-for-a-job-were-looking-activity-7459837297631457281-ZGJ3</t>
+          <t>https://www.userfacet.com/careers</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Indexed employer LinkedIn post; displayed3months old</t>
+          <t>Official career page observed</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Updated resume</t>
+          <t>3–5 years experience</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -28371,7 +29868,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Portfolio</t>
+          <t>Six-month program described</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -28384,12 +29881,12 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ProCreator</t>
+          <t>ZEUX Innovation</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>UX UI Designer Intern</t>
+          <t>UX Design Intern</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -28399,22 +29896,22 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Confirm Mumbai / onsite</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e342842eceeabd8a</t>
+          <t>https://www.linkedin.com/posts/zeux-innovation_most-people-look-for-a-job-were-looking-activity-7459837297631457281-ZGJ3</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Indexed Indeed detail; confirm employer intake</t>
+          <t>Indexed employer LinkedIn post; displayed3months old</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>3–6 months availability</t>
+          <t>One-minute introductory video</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -28427,12 +29924,12 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ProCreator</t>
+          <t>ZEUX Innovation</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>UX UI Designer Intern</t>
+          <t>UX Design Intern</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -28442,22 +29939,22 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Confirm Mumbai / onsite</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e342842eceeabd8a</t>
+          <t>https://www.linkedin.com/posts/zeux-innovation_most-people-look-for-a-job-were-looking-activity-7459837297631457281-ZGJ3</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Indexed Indeed detail; confirm employer intake</t>
+          <t>Indexed employer LinkedIn post; displayed3months old</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>UI/UX principles</t>
+          <t>Updated resume</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -28470,12 +29967,12 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ProCreator</t>
+          <t>ZEUX Innovation</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>UX UI Designer Intern</t>
+          <t>UX Design Intern</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -28485,22 +29982,22 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Confirm Mumbai / onsite</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e342842eceeabd8a</t>
+          <t>https://www.linkedin.com/posts/zeux-innovation_most-people-look-for-a-job-were-looking-activity-7459837297631457281-ZGJ3</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Indexed Indeed detail; confirm employer intake</t>
+          <t>Indexed employer LinkedIn post; displayed3months old</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Figma or Adobe XD</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -28543,7 +30040,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Portfolio with academic/personal work</t>
+          <t>3–6 months availability</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -28586,7 +30083,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Wireframing and prototyping</t>
+          <t>UI/UX principles</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -28629,7 +30126,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Communication; design systems/HTML/CSS/research are desirable</t>
+          <t>Figma or Adobe XD</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -28642,12 +30139,12 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SuperKalam</t>
+          <t>ProCreator</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Product Designer (Internship)</t>
+          <t>UX UI Designer Intern</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -28657,22 +30154,22 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru or remote within India</t>
+          <t>Navi Mumbai</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
+          <t>https://in.indeed.com/viewjob?jk=e342842eceeabd8a</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Employer-posted YC detail and current company board accessible; older original posting date retained</t>
+          <t>Indexed Indeed detail; confirm employer intake</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Portfolio or previous product-design internship</t>
+          <t>Portfolio with academic/personal work</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -28685,12 +30182,12 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SuperKalam</t>
+          <t>ProCreator</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Product Designer (Internship)</t>
+          <t>UX UI Designer Intern</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -28700,22 +30197,22 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru or remote within India</t>
+          <t>Navi Mumbai</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
+          <t>https://in.indeed.com/viewjob?jk=e342842eceeabd8a</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Employer-posted YC detail and current company board accessible; older original posting date retained</t>
+          <t>Indexed Indeed detail; confirm employer intake</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Investigate audiences and product problems</t>
+          <t>Wireframing and prototyping</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -28728,12 +30225,12 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SuperKalam</t>
+          <t>ProCreator</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Product Designer (Internship)</t>
+          <t>UX UI Designer Intern</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -28743,22 +30240,22 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru or remote within India</t>
+          <t>Navi Mumbai</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
+          <t>https://in.indeed.com/viewjob?jk=e342842eceeabd8a</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Employer-posted YC detail and current company board accessible; older original posting date retained</t>
+          <t>Indexed Indeed detail; confirm employer intake</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Design flows for different learner cohorts</t>
+          <t>Communication; design systems/HTML/CSS/research are desirable</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -28801,7 +30298,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Research, feedback and usable UI</t>
+          <t>Portfolio or previous product-design internship</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -28844,7 +30341,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Communication and independent ownership</t>
+          <t>Investigate audiences and product problems</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -28887,7 +30384,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Bonus: Jitter/Rive motion skills</t>
+          <t>Design flows for different learner cohorts</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -28930,7 +30427,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Availability for a four-to-six-month internship</t>
+          <t>Research, feedback and usable UI</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -28943,27 +30440,27 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Coulomb AI</t>
+          <t>SuperKalam</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Product Designer (Internship)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru or remote within India</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
+          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -28973,7 +30470,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Relevant design study, current or completed</t>
+          <t>Communication and independent ownership</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -28986,27 +30483,27 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Coulomb AI</t>
+          <t>SuperKalam</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Product Designer (Internship)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru or remote within India</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
+          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -29016,7 +30513,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Figma or comparable design tools</t>
+          <t>Bonus: Jitter/Rive motion skills</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -29029,27 +30526,27 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Coulomb AI</t>
+          <t>SuperKalam</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Product Designer (Internship)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru or remote within India</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
+          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -29059,7 +30556,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Research and usability fundamentals</t>
+          <t>Availability for a four-to-six-month internship</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -29102,7 +30599,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Explain decisions and collaborate</t>
+          <t>Relevant design study, current or completed</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -29145,7 +30642,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Portfolio; academic projects accepted</t>
+          <t>Figma or comparable design tools</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -29188,7 +30685,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Bonus: frontend or motion/prototyping experience</t>
+          <t>Research and usability fundamentals</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -29201,37 +30698,37 @@
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Cardboard</t>
+          <t>Coulomb AI</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Founding Design Engineer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Adjacent engineering role; advanced technical expectations</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru / San Francisco; US-visa flag conflicts with India location</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/cardboard/jobs/CPnEG9f-founding-design-engineer</t>
+          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Opened employer-posted YC detail; eligibility conflict remains</t>
+          <t>Employer-posted YC detail and current company board accessible; older original posting date retained</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>GSAP, Framer Motion and Three.js fluency</t>
+          <t>Explain decisions and collaborate</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -29244,37 +30741,37 @@
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Cardboard</t>
+          <t>Coulomb AI</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Founding Design Engineer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Adjacent engineering role; advanced technical expectations</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru / San Francisco; US-visa flag conflicts with India location</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/cardboard/jobs/CPnEG9f-founding-design-engineer</t>
+          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Opened employer-posted YC detail; eligibility conflict remains</t>
+          <t>Employer-posted YC detail and current company board accessible; older original posting date retained</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>WebGL/GLSL and browser-rendering expertise</t>
+          <t>Portfolio; academic projects accepted</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -29287,37 +30784,37 @@
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Cardboard</t>
+          <t>Coulomb AI</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Founding Design Engineer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Adjacent engineering role; advanced technical expectations</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru / San Francisco; US-visa flag conflicts with India location</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/cardboard/jobs/CPnEG9f-founding-design-engineer</t>
+          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Opened employer-posted YC detail; eligibility conflict remains</t>
+          <t>Employer-posted YC detail and current company board accessible; older original posting date retained</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Animation timing, performance and reusable components</t>
+          <t>Bonus: frontend or motion/prototyping experience</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -29330,37 +30827,37 @@
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Cardog</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Founding Design Engineer</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Unconfirmed; engineering/design adjacent</t>
+          <t>Adjacent engineering role; advanced technical expectations</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Remote; countries not specified in extracted careers overview</t>
+          <t>Bengaluru / San Francisco; US-visa flag conflicts with India location</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>https://cardog.app/careers</t>
+          <t>https://www.ycombinator.com/companies/cardboard/jobs/CPnEG9f-founding-design-engineer</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Employer HN post plus official overview; detailed experience/country criteria not verified</t>
+          <t>Opened employer-posted YC detail; eligibility conflict remains</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>React, Next.js and Tailwind implementation</t>
+          <t>GSAP, Framer Motion and Three.js fluency</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -29373,37 +30870,37 @@
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Cardog</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Founding Design Engineer</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Unconfirmed; engineering/design adjacent</t>
+          <t>Adjacent engineering role; advanced technical expectations</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Remote; countries not specified in extracted careers overview</t>
+          <t>Bengaluru / San Francisco; US-visa flag conflicts with India location</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>https://cardog.app/careers</t>
+          <t>https://www.ycombinator.com/companies/cardboard/jobs/CPnEG9f-founding-design-engineer</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Employer HN post plus official overview; detailed experience/country criteria not verified</t>
+          <t>Opened employer-posted YC detail; eligibility conflict remains</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Own component library and data-interface screens</t>
+          <t>WebGL/GLSL and browser-rendering expertise</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -29416,37 +30913,37 @@
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Cardog</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Founding Design Engineer</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Unconfirmed; engineering/design adjacent</t>
+          <t>Adjacent engineering role; advanced technical expectations</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Remote; countries not specified in extracted careers overview</t>
+          <t>Bengaluru / San Francisco; US-visa flag conflicts with India location</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://cardog.app/careers</t>
+          <t>https://www.ycombinator.com/companies/cardboard/jobs/CPnEG9f-founding-design-engineer</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Employer HN post plus official overview; detailed experience/country criteria not verified</t>
+          <t>Opened employer-posted YC detail; eligibility conflict remains</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Design in browser and merge implementation</t>
+          <t>Animation timing, performance and reusable components</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -29459,37 +30956,37 @@
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Sundream Studio</t>
+          <t>Cardog</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Unspecified full-time / contract</t>
+          <t>Unconfirmed; engineering/design adjacent</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>NYC / Remote; India not confirmed</t>
+          <t>Remote; countries not specified in extracted careers overview</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49932275</t>
+          <t>https://cardog.app/careers</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Employer post in October2026 HN thread; no detailed criteria captured</t>
+          <t>Employer HN post plus official overview; detailed experience/country criteria not verified</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>React, Next.js and Tailwind implementation</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -29502,37 +30999,37 @@
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Icogz</t>
+          <t>Cardog</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX / Web Designer</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Unconfirmed; engineering/design adjacent</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Oshiwara, Mumbai, Maharashtra</t>
+          <t>Remote; countries not specified in extracted careers overview</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
+          <t>https://cardog.app/careers</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
+          <t>Employer HN post plus official overview; detailed experience/country criteria not verified</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>UI/UX or web-design coursework, personal projects or freelance work</t>
+          <t>Own component library and data-interface screens</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -29545,37 +31042,37 @@
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Icogz</t>
+          <t>Cardog</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX / Web Designer</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Unconfirmed; engineering/design adjacent</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Oshiwara, Mumbai, Maharashtra</t>
+          <t>Remote; countries not specified in extracted careers overview</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
+          <t>https://cardog.app/careers</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
+          <t>Employer HN post plus official overview; detailed experience/country criteria not verified</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Responsive/mobile-first design, typography, colour, layout and hierarchy</t>
+          <t>Design in browser and merge implementation</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -29588,37 +31085,37 @@
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Icogz</t>
+          <t>Sundream Studio</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX / Web Designer</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Unspecified full-time / contract</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Oshiwara, Mumbai, Maharashtra</t>
+          <t>NYC / Remote; India not confirmed</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
+          <t>https://news.ycombinator.com/item?id=49932275</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
+          <t>Employer post in October2026 HN thread; no detailed criteria captured</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Familiarity with Figma, Adobe XD, Canva or similar</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -29661,7 +31158,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Willingness to learn HTML/CSS and AI-assisted development</t>
+          <t>UI/UX or web-design coursework, personal projects or freelance work</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -29704,7 +31201,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Relevant degree/diploma/certification or equivalent self-taught experience</t>
+          <t>Responsive/mobile-first design, typography, colour, layout and hierarchy</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -29747,7 +31244,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Portfolio and relevant landing-page or WordPress examples</t>
+          <t>Familiarity with Figma, Adobe XD, Canva or similar</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -29790,7 +31287,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Three-month internship; communication and feedback</t>
+          <t>Willingness to learn HTML/CSS and AI-assisted development</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -29803,12 +31300,12 @@
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>VictorFlow</t>
+          <t>Icogz</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Intern</t>
+          <t>Intern - UI/UX / Web Designer</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -29818,22 +31315,22 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Pollachi, Tamil Nadu, India</t>
+          <t>Oshiwara, Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
+          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
+          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Pursuing or completed bachelor degree</t>
+          <t>Relevant degree/diploma/certification or equivalent self-taught experience</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -29846,12 +31343,12 @@
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>VictorFlow</t>
+          <t>Icogz</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Intern</t>
+          <t>Intern - UI/UX / Web Designer</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -29861,22 +31358,22 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Pollachi, Tamil Nadu, India</t>
+          <t>Oshiwara, Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
+          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
+          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Portfolio of mobile/website UI/UX work</t>
+          <t>Portfolio and relevant landing-page or WordPress examples</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -29889,12 +31386,12 @@
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>VictorFlow</t>
+          <t>Icogz</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Intern</t>
+          <t>Intern - UI/UX / Web Designer</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -29904,22 +31401,22 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Pollachi, Tamil Nadu, India</t>
+          <t>Oshiwara, Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
+          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
+          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Figma proficiency; Adobe XD bonus</t>
+          <t>Three-month internship; communication and feedback</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -29962,7 +31459,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Wireframes, prototypes, research and usability testing</t>
+          <t>Pursuing or completed bachelor degree</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -30005,7 +31502,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Developer collaboration and communication</t>
+          <t>Portfolio of mobile/website UI/UX work</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -30018,7 +31515,7 @@
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Balusen Technologies</t>
+          <t>VictorFlow</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -30033,22 +31530,22 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru / Remote India</t>
+          <t>Pollachi, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=846c4cef6fe81a21</t>
+          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
+          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>0–1 years / fresher</t>
+          <t>Figma proficiency; Adobe XD bonus</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -30061,7 +31558,7 @@
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Balusen Technologies</t>
+          <t>VictorFlow</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -30076,22 +31573,22 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru / Remote India</t>
+          <t>Pollachi, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=846c4cef6fe81a21</t>
+          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
+          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Figma and school/personal-project portfolio</t>
+          <t>Wireframes, prototypes, research and usability testing</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -30104,7 +31601,7 @@
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Balusen Technologies</t>
+          <t>VictorFlow</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -30119,22 +31616,22 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru / Remote India</t>
+          <t>Pollachi, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=846c4cef6fe81a21</t>
+          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
+          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Interest in UX research and accessibility</t>
+          <t>Developer collaboration and communication</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -30177,7 +31674,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Wireframes, component libraries and design docs</t>
+          <t>0–1 years / fresher</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -30220,7 +31717,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Collaborative mindset</t>
+          <t>Figma and school/personal-project portfolio</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -30263,7 +31760,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Listing requests 10–15 day join availability and CTC/take-home information</t>
+          <t>Interest in UX research and accessibility</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -30276,7 +31773,7 @@
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Gunadhya Software Solutions</t>
+          <t>Balusen Technologies</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -30291,22 +31788,22 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Pune, Maharashtra; exact office/work mode to confirm</t>
+          <t>Bengaluru / Remote India</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
+          <t>https://in.indeed.com/viewjob?jk=846c4cef6fe81a21</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
+          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Freshers /0–1 years with relevant degree or study</t>
+          <t>Wireframes, component libraries and design docs</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -30319,7 +31816,7 @@
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Gunadhya Software Solutions</t>
+          <t>Balusen Technologies</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -30334,22 +31831,22 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Pune, Maharashtra; exact office/work mode to confirm</t>
+          <t>Bengaluru / Remote India</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
+          <t>https://in.indeed.com/viewjob?jk=846c4cef6fe81a21</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
+          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Figma, wireframes, prototypes and user flows</t>
+          <t>Collaborative mindset</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -30362,7 +31859,7 @@
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Gunadhya Software Solutions</t>
+          <t>Balusen Technologies</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -30377,22 +31874,22 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Pune, Maharashtra; exact office/work mode to confirm</t>
+          <t>Bengaluru / Remote India</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
+          <t>https://in.indeed.com/viewjob?jk=846c4cef6fe81a21</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
+          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Responsive design, typography, spacing and hierarchy</t>
+          <t>Listing requests 10–15 day join availability and CTC/take-home information</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -30435,7 +31932,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Communication, teamwork and feedback</t>
+          <t>Freshers /0–1 years with relevant degree or study</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -30478,7 +31975,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Portfolio or academic/personal UI/UX work desirable</t>
+          <t>Figma, wireframes, prototypes and user flows</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -30521,7 +32018,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Bonus: HTML/CSS, research/usability, components and accessibility</t>
+          <t>Responsive design, typography, spacing and hierarchy</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -30534,37 +32031,37 @@
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Qoruz</t>
+          <t>Gunadhya Software Solutions</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Junior UX Designer</t>
+          <t>UI/UX Intern</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka</t>
+          <t>Pune, Maharashtra; exact office/work mode to confirm</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
+          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1–3 years experience as listed</t>
+          <t>Communication, teamwork and feedback</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -30577,37 +32074,37 @@
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Qoruz</t>
+          <t>Gunadhya Software Solutions</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Junior UX Designer</t>
+          <t>UI/UX Intern</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka</t>
+          <t>Pune, Maharashtra; exact office/work mode to confirm</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
+          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Figma and production-ready UI</t>
+          <t>Portfolio or academic/personal UI/UX work desirable</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -30620,37 +32117,37 @@
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Qoruz</t>
+          <t>Gunadhya Software Solutions</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Junior UX Designer</t>
+          <t>UI/UX Intern</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Junior / fresher</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka</t>
+          <t>Pune, Maharashtra; exact office/work mode to confirm</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
+          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Data-heavy dashboards, tables, search/filter and error/loading/permission states</t>
+          <t>Bonus: HTML/CSS, research/usability, components and accessibility</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -30693,7 +32190,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Research and product thinking</t>
+          <t>1–3 years experience as listed</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -30736,7 +32233,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Engineering collaboration, implementation review and design systems</t>
+          <t>Figma and production-ready UI</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -30749,37 +32246,37 @@
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Energise.pro</t>
+          <t>Qoruz</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>Junior UX Designer</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Junior / experienced:1–2 commercial years</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Worldwide remote; listing explicitly allows all countries</t>
+          <t>Bengaluru, Karnataka</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Public role detail and per-job API 200; official site did not expose this role</t>
+          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1–2 years commercial Product/UX/UI design experience</t>
+          <t>Data-heavy dashboards, tables, search/filter and error/loading/permission states</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -30792,37 +32289,37 @@
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Energise.pro</t>
+          <t>Qoruz</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>Junior UX Designer</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Junior / experienced:1–2 commercial years</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Worldwide remote; listing explicitly allows all countries</t>
+          <t>Bengaluru, Karnataka</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Public role detail and per-job API 200; official site did not expose this role</t>
+          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Confident Figma use and mobile-app UI/UX work</t>
+          <t>Research and product thinking</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -30835,37 +32332,37 @@
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Energise.pro</t>
+          <t>Qoruz</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>Junior UX Designer</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Junior / experienced:1–2 commercial years</t>
+          <t>Junior / fresher</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Worldwide remote; listing explicitly allows all countries</t>
+          <t>Bengaluru, Karnataka</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Public role detail and per-job API 200; official site did not expose this role</t>
+          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Competitive analysis, user research, flows, wireframes and prototypes</t>
+          <t>Engineering collaboration, implementation review and design systems</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -30908,7 +32405,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Collaboration with product management and engineering, including handoff</t>
+          <t>1–2 years commercial Product/UX/UI design experience</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -30951,7 +32448,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Basic product metrics; design systems and iOS/Android patterns are preferred</t>
+          <t>Confident Figma use and mobile-app UI/UX work</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -30994,7 +32491,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>English B1+ is a listed bonus; original advert is in Ukrainian</t>
+          <t>Competitive analysis, user research, flows, wireframes and prototypes</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -31007,37 +32504,37 @@
     <row r="150" ht="42" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Energise.pro</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Product Design Expression of Interest Form</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Talent pool; no internship or junior opening established</t>
+          <t>Junior / experienced:1–2 commercial years</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Role-specific country hiring guidelines apply</t>
+          <t>Worldwide remote; listing explicitly allows all countries</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/gitlab-com/jobs/product-design-expression-of-interest-form</t>
+          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Documented API description explicitly identifies future talent pool</t>
+          <t>Public role detail and per-job API 200; official site did not expose this role</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>No detailed requirements captured; open source</t>
+          <t>Collaboration with product management and engineering, including handoff</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -31050,37 +32547,37 @@
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Troopr.ai / Troopr Labs</t>
+          <t>Energise.pro</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Product Designer (Remote)</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Experienced;3–5 years; outside internship shortlist</t>
+          <t>Junior / experienced:1–2 commercial years</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Remote; explicit India eligibility should be checked with employer</t>
+          <t>Worldwide remote; listing explicitly allows all countries</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>https://troopr.freshteam.com/jobs/1Q615E3mmTmP/product-designer-remote</t>
+          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Official ATS detail opened</t>
+          <t>Public role detail and per-job API 200; official site did not expose this role</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>3–5 years professional B2B SaaS product design</t>
+          <t>Basic product metrics; design systems and iOS/Android patterns are preferred</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -31093,37 +32590,37 @@
     <row r="152" ht="42" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Troopr.ai / Troopr Labs</t>
+          <t>Energise.pro</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Product Designer (Remote)</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Experienced;3–5 years; outside internship shortlist</t>
+          <t>Junior / experienced:1–2 commercial years</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Remote; explicit India eligibility should be checked with employer</t>
+          <t>Worldwide remote; listing explicitly allows all countries</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>https://troopr.freshteam.com/jobs/1Q615E3mmTmP/product-designer-remote</t>
+          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Official ATS detail opened</t>
+          <t>Public role detail and per-job API 200; official site did not expose this role</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Complex technical software-product design</t>
+          <t>English B1+ is a listed bonus; original advert is in Ukrainian</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -31136,37 +32633,37 @@
     <row r="153" ht="42" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Troopr.ai / Troopr Labs</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Product Designer (Remote)</t>
+          <t>Product Design Expression of Interest Form</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Experienced;3–5 years; outside internship shortlist</t>
+          <t>Talent pool; no internship or junior opening established</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Remote; explicit India eligibility should be checked with employer</t>
+          <t>Role-specific country hiring guidelines apply</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>https://troopr.freshteam.com/jobs/1Q615E3mmTmP/product-designer-remote</t>
+          <t>https://himalayas.app/companies/gitlab-com/jobs/product-design-expression-of-interest-form</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Official ATS detail opened</t>
+          <t>Documented API description explicitly identifies future talent pool</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Advanced Figma, prototyping and engineering handoff</t>
+          <t>No detailed requirements captured; open source</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -31209,7 +32706,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Lead and mentor junior designers</t>
+          <t>3–5 years professional B2B SaaS product design</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -31222,37 +32719,37 @@
     <row r="155" ht="42" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Attira</t>
+          <t>Troopr.ai / Troopr Labs</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX and QA (separate internship tracks)</t>
+          <t>Product Designer (Remote)</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Internship; platform type saysFull Time</t>
+          <t>Experienced;3–5 years; outside internship shortlist</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Remote everywhere; PT / ET / CET timezone preference</t>
+          <t>Remote; explicit India eligibility should be checked with employer</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>https://wellfound.com/jobs/4823701-intern-ui-ux-and-qa</t>
+          <t>https://troopr.freshteam.com/jobs/1Q615E3mmTmP/product-designer-remote</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Wellfound detail opened; employer-linked form published</t>
+          <t>Official ATS detail opened</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Wireframes, prototypes and user flows</t>
+          <t>Complex technical software-product design</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -31265,37 +32762,37 @@
     <row r="156" ht="42" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Attira</t>
+          <t>Troopr.ai / Troopr Labs</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX and QA (separate internship tracks)</t>
+          <t>Product Designer (Remote)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Internship; platform type saysFull Time</t>
+          <t>Experienced;3–5 years; outside internship shortlist</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Remote everywhere; PT / ET / CET timezone preference</t>
+          <t>Remote; explicit India eligibility should be checked with employer</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>https://wellfound.com/jobs/4823701-intern-ui-ux-and-qa</t>
+          <t>https://troopr.freshteam.com/jobs/1Q615E3mmTmP/product-designer-remote</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Wellfound detail opened; employer-linked form published</t>
+          <t>Official ATS detail opened</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>No experience required; willingness to learn</t>
+          <t>Advanced Figma, prototyping and engineering handoff</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -31308,37 +32805,37 @@
     <row r="157" ht="42" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Attira</t>
+          <t>Troopr.ai / Troopr Labs</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX and QA (separate internship tracks)</t>
+          <t>Product Designer (Remote)</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Internship; platform type saysFull Time</t>
+          <t>Experienced;3–5 years; outside internship shortlist</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Remote everywhere; PT / ET / CET timezone preference</t>
+          <t>Remote; explicit India eligibility should be checked with employer</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>https://wellfound.com/jobs/4823701-intern-ui-ux-and-qa</t>
+          <t>https://troopr.freshteam.com/jobs/1Q615E3mmTmP/product-designer-remote</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Wellfound detail opened; employer-linked form published</t>
+          <t>Official ATS detail opened</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Attention to detail and communication</t>
+          <t>Lead and mentor junior designers</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -31351,37 +32848,37 @@
     <row r="158" ht="42" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>BigThinkCode Technologies</t>
+          <t>Attira</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Design Internship (Fresher)</t>
+          <t>Intern - UI/UX and QA (separate internship tracks)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Internship with cohort restrictions</t>
+          <t>Internship; platform type saysFull Time</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Chennai / Pondicherry; in-office</t>
+          <t>Remote everywhere; PT / ET / CET timezone preference</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>https://cutshort.io/job/UI-UX-Design-Internship-Fresher-Chennai-Pondicherry-BigThinkCode-Technologies-hHEZeQYZ</t>
+          <t>https://wellfound.com/jobs/4823701-intern-ui-ux-and-qa</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Cutshort detail opened; annual pay range retained as annual</t>
+          <t>Wellfound detail opened; employer-linked form published</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2025–2026 graduate in design/architecture/CS or related field</t>
+          <t>Wireframes, prototypes and user flows</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -31394,37 +32891,37 @@
     <row r="159" ht="42" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>BigThinkCode Technologies</t>
+          <t>Attira</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Design Internship (Fresher)</t>
+          <t>Intern - UI/UX and QA (separate internship tracks)</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Internship with cohort restrictions</t>
+          <t>Internship; platform type saysFull Time</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Chennai / Pondicherry; in-office</t>
+          <t>Remote everywhere; PT / ET / CET timezone preference</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>https://cutshort.io/job/UI-UX-Design-Internship-Fresher-Chennai-Pondicherry-BigThinkCode-Technologies-hHEZeQYZ</t>
+          <t>https://wellfound.com/jobs/4823701-intern-ui-ux-and-qa</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Cutshort detail opened; annual pay range retained as annual</t>
+          <t>Wellfound detail opened; employer-linked form published</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Completed recognised UI/UX certification</t>
+          <t>No experience required; willingness to learn</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -31437,37 +32934,37 @@
     <row r="160" ht="42" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>BigThinkCode Technologies</t>
+          <t>Attira</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>UI/UX Design Internship (Fresher)</t>
+          <t>Intern - UI/UX and QA (separate internship tracks)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Internship with cohort restrictions</t>
+          <t>Internship; platform type saysFull Time</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Chennai / Pondicherry; in-office</t>
+          <t>Remote everywhere; PT / ET / CET timezone preference</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>https://cutshort.io/job/UI-UX-Design-Internship-Fresher-Chennai-Pondicherry-BigThinkCode-Technologies-hHEZeQYZ</t>
+          <t>https://wellfound.com/jobs/4823701-intern-ui-ux-and-qa</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Cutshort detail opened; annual pay range retained as annual</t>
+          <t>Wellfound detail opened; employer-linked form published</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Strong portfolio and advanced Figma auto-layout, components, variants, systems and prototyping</t>
+          <t>Attention to detail and communication</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -31510,18 +33007,792 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
+          <t>2025–2026 graduate in design/architecture/CS or related field</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>BigThinkCode Technologies</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Internship (Fresher)</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Internship with cohort restrictions</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Chennai / Pondicherry; in-office</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/UI-UX-Design-Internship-Fresher-Chennai-Pondicherry-BigThinkCode-Technologies-hHEZeQYZ</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Cutshort detail opened; annual pay range retained as annual</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Completed recognised UI/UX certification</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>BigThinkCode Technologies</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Internship (Fresher)</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Internship with cohort restrictions</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Chennai / Pondicherry; in-office</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/UI-UX-Design-Internship-Fresher-Chennai-Pondicherry-BigThinkCode-Technologies-hHEZeQYZ</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Cutshort detail opened; annual pay range retained as annual</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Strong portfolio and advanced Figma auto-layout, components, variants, systems and prototyping</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>BigThinkCode Technologies</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Internship (Fresher)</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Internship with cohort restrictions</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Chennai / Pondicherry; in-office</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/UI-UX-Design-Internship-Fresher-Chennai-Pondicherry-BigThinkCode-Technologies-hHEZeQYZ</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Cutshort detail opened; annual pay range retained as annual</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
           <t>6–8 month office internship; Chennai</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Unassessed</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX &amp; Product Design Internship (Web, Mobile &amp; AI Systems)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>UI hierarchy, typography, contrast and responsive layouts</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX &amp; Product Design Internship (Web, Mobile &amp; AI Systems)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Component libraries, auto-layout, tokens and interaction states</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX &amp; Product Design Internship (Web, Mobile &amp; AI Systems)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Client discovery, end-to-end flows and engineering collaboration</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX &amp; Product Design Internship (Web, Mobile &amp; AI Systems)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Interest in generative visuals; motion and frontend knowledge are bonuses</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX &amp; Product Design Internship (Web, Mobile &amp; AI Systems)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Prahladnagar, Ahmedabad; strictly on-site</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Final-year design/technical students, recent graduates or self-taught designers; six- or twelve-month options</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Intern</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Bengaluru-based employer description</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Enrolled in design, HCI or a related degree</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Intern</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Bengaluru-based employer description</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Basic interface-design tools and principles</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Intern</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Bengaluru-based employer description</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Research, wireframes, prototypes and usability testing</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>UI UX Intern</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Bengaluru-based employer description</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>https://careerspage.io/innovexis/ui-ux-intern-in295</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Team communication; portfolio and edtech familiarity are helpful</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Internship</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Remote (India), full-time</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Employer Dover ATS search index contains role and application fields; direct opening returned a JavaScript shell. Indexed employer copy was crawled about five months before review, not a posting date. Remotive mirror returned403; its relative age does not prove freshness. Pay and duration undisclosed.</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Listed experience band zero to two years</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Internship</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Remote (India), full-time</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Employer Dover ATS search index contains role and application fields; direct opening returned a JavaScript shell. Indexed employer copy was crawled about five months before review, not a posting date. Remotive mirror returned403; its relative age does not prove freshness. Pay and duration undisclosed.</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Figma and Adobe visual/motion tools</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Internship</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Remote (India), full-time</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Employer Dover ATS search index contains role and application fields; direct opening returned a JavaScript shell. Indexed employer copy was crawled about five months before review, not a posting date. Remotive mirror returned403; its relative age does not prove freshness. Pay and duration undisclosed.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Design systems, user research, testing and prototypes</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>UI and UX designer Fresher</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Fresher — historical advertisement, not active recommendation</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in-person</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/jobs/ux-designer-job/</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Official role page has an application form but metadata originally dates to 11 October2022, modified8 April2025. Corresponding LinkedIn crosspost explicitly closed. Watchlist only; no active job card.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Formal UX training and portfolio with multiple mobile and web projects</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178" ht="42" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>UI and UX designer Fresher</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Fresher — historical advertisement, not active recommendation</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in-person</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/jobs/ux-designer-job/</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Official role page has an application form but metadata originally dates to 11 October2022, modified8 April2025. Corresponding LinkedIn crosspost explicitly closed. Watchlist only; no active job card.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Figma, handoff, systems and interface testing</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179" ht="42" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>UI and UX designer Fresher</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Fresher — historical advertisement, not active recommendation</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in-person</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>https://bicsom.co/jobs/ux-designer-job/</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Official role page has an application form but metadata originally dates to 11 October2022, modified8 April2025. Corresponding LinkedIn crosspost explicitly closed. Watchlist only; no active job card.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Mobile platform guidelines and English communication</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I161"/>
+  <autoFilter ref="A1:I179"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Unassessed,Met,Partly met,Gap"</formula1>
@@ -31688,6 +33959,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31699,7 +33988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32426,6 +34715,78 @@
         </is>
       </c>
     </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Kixar</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Melento</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>BetterStory</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Redliner</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Veril Studio</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Official design internship explicitly unpaid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>BiCSoM</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$256</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Company still exposes the role page and links it from careers. It is an older May posting; current hiring and stipend require confirmation.</t>
+          <t>Company still exposes the role page and links it from careers. It is an older May posting; current hiring and stipend require confirmation. Recheck25 October: employer page remains accessible; linked Wellfound4209561 now returns410 Gone. The employer page alone does not establish a renewed intake.</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr"/>
@@ -1777,34 +1777,38 @@
           <t>on_hold</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Confirm stipend, office arrangement, duration and start window via the official role.</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Job board</t>
+          <t>Company careers</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>https://www.studentsmart.co.in/student/internships/glance-ux-design-intern</t>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>https://www.studentsmart.co.in/student/internships/glance-ux-design-intern</t>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Job-board sign-in; find original employer listing</t>
+          <t>Official Greenhouse application</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>StudentSmart reports ₹30k–₹40k/month and Bengaluru; original employer confirmation and work arrangement are still needed.</t>
+          <t>Original Glance Greenhouse role and application are available. Stipend is not stated; the prior StudentSmart INR30–40k/month claim remains unverified. Confirm work arrangement and start date.</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1815,7 +1819,7 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15 October 2026 on job board</t>
+          <t>Employer date unstated; 15 October was the aggregator date</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -1825,7 +1829,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr"/>
@@ -1919,7 +1923,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -2013,7 +2017,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr"/>
@@ -2107,7 +2111,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -2201,7 +2205,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -2765,7 +2769,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr"/>
@@ -2859,7 +2863,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -3448,7 +3452,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Intern - UI/UX / Web Designer</t>
+          <t>Intern-UI/UX</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3512,7 +3516,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
+          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed. Original detail now uses Intern-UI/UX; stable record ID preserved.</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3533,7 +3537,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr"/>
@@ -3994,7 +3998,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>Himalayas detail and documented public API both accessible; API per-job check returned200. Detail explicitly permits all countries and API has no country restrictions plus UTC+05:30. Original company site was opened but only ASO/User Acquisition roles were visible, so the UX vacancy is not corroborated on its site. Pay undisclosed. Board labels entry-level while body requires1–2 commercial years.</t>
+          <t>Himalayas detail and documented public API both accessible; API per-job check returned200. Detail explicitly permits all countries and API has no country restrictions plus UTC+05:30. Original company site was opened but only ASO/User Acquisition roles were visible, so the UX vacancy is not corroborated on its site. Pay undisclosed. Board labels entry-level while body requires1–2 commercial years. Recheck25 October: board detail still gives5 November deadline. Job expired? is a reporting control, not a closure notice.</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
@@ -4148,12 +4152,12 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Confirm current paid employment intake, no applicant fees, India eligibility, duration/start window and remote stipend around INR30,000/month; INR25,000 only considered individually.</t>
+          <t>Archived: original role removed. Reopen only when a current employer vacancy is evidenced.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
@@ -4182,7 +4186,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation. Recheck25 October: original role returned404 in direct check and410 Gone through web research. Archived as a removed listing; no claim that all company hiring ended.</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4203,7 +4207,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -4302,8 +4306,392 @@
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
     </row>
+    <row r="41" ht="95" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Gurugram office optional/preferred</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Confirm monthly stipend, internship duration and start window; review the portfolio request.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern/apply</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS/form; manual review and submission</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>Employer detail and application page are available; the form explicitly permits work from home within India. Duration, stipend amount and cohort/start dates are unstated. General employee perks are not confirmed intern benefits.</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>Figma proficiency and a portfolio showing design reasoning; Interface fundamentals, interaction flows and usability; Independent ownership and collaboration with engineering; Interest in AI creative tools; prior product work is optional</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>12 October 2026 in employer JobPosting metadata</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="95" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Thane / Mumbai, Maharashtra; employer pages use both locations</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Confirm stipend, duration, office location and start date with the official listing; complete both required steps only after review.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>https://revvity.wd103.myworkdayjobs.com/External/job/Mumbai/UX-Intern_JR-045767/apply</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS/form; manual review and submission</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Awareness of UX design and research methods; Clear English communication and presenting design decisions; Curiosity, feedback and collaboration; Work includes prototyping and research sessions</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>The employer requires its questionnaire https://forms.cloud.microsoft/r/agdKBU4dTM and submission to Workday for JR-045767. Review both before sending anything.</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>8 October 2026 in official careers structured data; mirror dates differ</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="95" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>UI / UX Design Trainee (Fresher)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>INR 250000–400000/year</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Confirm full-time eligibility, joining window and annual package; use the paid-job ATS route, not training programs.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/apply.php?job_id=50</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS/form; manual review and submission</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS and corporate careers page corroborate this paid job. Unpaid training programs are separate and excluded. Apply through ATS only; the support address is technical support, not a recruitment inbox. Start timing and employment terms need confirmation.</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>Design, HCI, fine-arts or related qualification; Working Figma knowledge and a portfolio; coursework is accepted; Wireframes, design-system components and research support; Openness to critique</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>19 September 2026 on original employer detail</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="95" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer – 0–1 Years Experience</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Confirm salary, student/graduate eligibility, later joining and actual office schedule before applying.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS/form; manual review and submission</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0–1 years; graduates with a portfolio are welcome; Figma and strong typography, spacing, grids and interface hierarchy; Basic UX knowledge and responsive SaaS interfaces; Collaboration, iteration and curiosity about AI tools; Bonus: design systems, HTML/CSS and prior design internship</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Original posting date unstated; update age is not a publication date</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z40"/>
+  <autoFilter ref="A1:Z44"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
@@ -4388,6 +4776,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4399,7 +4795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F242"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4465,12 +4861,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Manual check required: robots policy unavailable or disallows automated fetch.</t>
+          <t>Robots policy unavailable or disallows automated fetch; not proof the role closed.</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4893,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4925,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Manual check required: robots policy unavailable or disallows automated fetch.</t>
+          <t>Robots policy unavailable or disallows automated fetch; not proof the role closed.</t>
         </is>
       </c>
     </row>
@@ -4561,12 +4957,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Manual check required: robots policy unavailable or disallows automated fetch.</t>
+          <t>Robots policy unavailable or disallows automated fetch; not proof the role closed.</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4989,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Manual check required: robots policy unavailable or disallows automated fetch.</t>
+          <t>Robots policy unavailable or disallows automated fetch; not proof the role closed.</t>
         </is>
       </c>
     </row>
@@ -4625,12 +5021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4657,12 +5053,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4689,12 +5085,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4721,12 +5117,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4753,12 +5149,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4785,12 +5181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4817,12 +5213,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Public page fetched; hiring availability still needs employer confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4844,17 +5240,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:37:35+00:00</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Manual check required: robots policy unavailable or disallows automated fetch.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -4940,11 +5336,19 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -4964,11 +5368,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -4988,11 +5400,19 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -5012,11 +5432,19 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -5036,11 +5464,19 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Exact prior title not found; manual review required, not proof of closure.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -5060,11 +5496,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -5084,11 +5528,19 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -7305,12 +7757,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible. Employer listing checked directly and corroborated on company product-team page. Pay undisclosed; hold until stipend confirmed.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -7369,12 +7821,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible. Full-time early-career role, not an internship. Employer JD and remote-policy careers page were directly read; pay undisclosed.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7917,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible. Current official board and JD both read. Internship title still asks for shipping experience; do not assume a first-time applicant qualifies. Pay not disclosed.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7981,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Official role detail accessible. Official JD and application form accessible. Remote-first company. Application requires resume, portfolio, start availability, expected monthly stipend and an everyday-app improvement answer. Current stipend not disclosed.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -8324,17 +8776,17 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search-indexed official page; not directly opened. </t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8941,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Official page opened. </t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9252,17 +9704,17 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Employer homepage links its YC careers board. Original metadata is from 2024; current intake is unconfirmed. Visible pay says INR 25–40K without a period, while JSON-LD says USD/year; no monthly stipend is confirmed.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9284,17 +9736,17 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>YC board retains this role, originally posted in 2024. Header asks 1+ years, while the body permits current/recent design students and class projects. Employer Join Us currently shows engineering roles. Salary is USD 8–12K/year in structured data, not a monthly INR stipend.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9316,17 +9768,17 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened. Three-month UI/UX and web/landing-page internship, in person in Mumbai. Employer careers page confirms company and publishes general HR contact, but this internship was not visible in extracted official openings. Pay/current intake unconfirmed.</t>
+          <t>Public page fetched. Exact prior title not found; manual review required, not proof of closure.</t>
         </is>
       </c>
     </row>
@@ -9348,17 +9800,17 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Indeed and official careers/role page opened. Explicit Pollachi onsite; remote not assumed. Full-time internship; stipend and posting/closing dates undisclosed.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9380,17 +9832,17 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail publicly opened: Remote India, internship 0–1y. Body dated21 May 2026. CareerScan date3 Oct 2026 repeats the May body; not evidence of a new original posting. Official careers route opened without extractable roles. Verify intake, pay and start window.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9412,17 +9864,17 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Indeed detail and employer career page opened, both list matching UI/UX Intern0–1. Company Pune-based; specific remote arrangements not confirmed. Stipend/date unknown. Ignore expiry assigned by unrelated mirrors.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9444,17 +9896,17 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Employer/recruiter-posted Cutshort detail opened. Junior full-time alternative, not internship, asking1–3 years. Listing quotes INR4–6lakh per YEAR; monthly stipend fields must remain null. Work arrangement/current intake require confirmation.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -9476,17 +9928,17 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Himalayas detail and documented public API both accessible; API per-job check returned200. Detail explicitly permits all countries and API has no country restrictions plus UTC+05:30. Original company site was opened but only ASO/User Acquisition roles were visible, so the UX vacancy is not corroborated on its site. Pay undisclosed. Board labels entry-level while body requires1–2 commercial years.</t>
+          <t>Detail remains available with a 5 November board deadline. The Job expired? control is a report button, not a closure statement.</t>
         </is>
       </c>
     </row>
@@ -11465,12 +11917,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Official detail accessible. Stipend is negotiable with no amount. Careers index advertises immediate joining; later intake is unconfirmed. No remote option. Other company internships have unpaid options, so confirm the design-role policy separately.</t>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
         </is>
       </c>
     </row>
@@ -11492,17 +11944,17 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+          <t>Tracked in295 original removed404/410; archived stable record, application history retained.</t>
         </is>
       </c>
     </row>
@@ -11524,17 +11976,17 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Employer Dover ATS search index contains role and application fields; direct opening returned a JavaScript shell. Indexed employer copy was crawled about five months before review, not a posting date. Remotive mirror returned403; its relative age does not prove freshness. Pay and duration undisclosed.</t>
+          <t>Public page fetched. Exact prior title not found; manual review required, not proof of closure.</t>
         </is>
       </c>
     </row>
@@ -11940,17 +12392,17 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25T07:18:54+00:00</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.</t>
+          <t>Indeed explicitly expired; up to30k is not a guaranteed minimum.</t>
         </is>
       </c>
     </row>
@@ -11986,8 +12438,456 @@
         </is>
       </c>
     </row>
+    <row r="243" ht="42" customHeight="1">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Ungrammary</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Public page fetched. Role title found; a fetch alone does not reconfirm intake or compensation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="42" customHeight="1">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Employer detail and application page are available; the form explicitly permits work from home within India. Duration, stipend amount and cohort/start dates are unstated. General employee perks are not confirmed intern benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="42" customHeight="1">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="42" customHeight="1">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS and corporate careers page corroborate this paid job. Unpaid training programs are separate and excluded. Apply through ATS only; the support address is technical support, not a recruitment inbox. Start timing and employment terms need confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="42" customHeight="1">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="42" customHeight="1">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Original Glance Greenhouse role and application are available. Stipend is not stated; the prior StudentSmart INR30–40k/month claim remains unverified. Confirm work arrangement and start date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="42" customHeight="1">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>https://salesforce.wd12.myworkdayjobs.com/en-US/External_Career_Site/job/Summer-2027-Intern---UI-UX-Designer_JR363342</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Original indexed deadline17 October2026 has passed; fresher mirror dates do not prove renewed intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="42" customHeight="1">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Ecolibrium</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ecolibrium.io/careers/</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Climate/building analytics software. Static careers names UI/UX Intern, but the linked live ATS shows a visual-marketing intern and a product designer requiring3–5 years. No verified current qualifying UX internship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="42" customHeight="1">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Construe Labs</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>https://construelabs.freshteam.com/jobs/iaTEUebfJP5j/ui-ux-design-intern-remote</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS exposes a three-month UI/UX internship,4–6 hours/day, five days/week. Pay, current intake and India eligibility are not stated. Historical India company evidence does not confirm this intake; watchlist pending clarification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="42" customHeight="1">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>AVYAM LABS</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4829685-ui-ux-designer-intern</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Original advert explicitly unpaid; excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="42" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Entrupy</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4147591-design-intern</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Indexed internship original now410 Gone; not an active lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="42" customHeight="1">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>MediNex Workforce</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>https://thejobcompany.co.in/frontend/job_details?job_id=6490</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Mirror reports17.5k/month, below remote target; no qualifying card added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="42" customHeight="1">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>CoreByte Studio</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>https://corebytestudio.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Remote role explicitly hires within Pakistan, not India.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="42" customHeight="1">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Ecolibrium</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>https://employmenthero.com/jobs/position/ecolibrium-product-designer-72w0q/</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:54+00:00</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Current product role requires3–5 years; not a junior/internship match.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F242"/>
+  <autoFilter ref="A1:F256"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12060,22 +12960,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>searched</t>
+          <t>Targeted public design search</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Reviewed public design search and selected company job details. Two eligible-region conditional leads retained with older dates and pay caveats. No newly confirmed qualifying monthly stipend. Additional pass: Additional targeted public design/intern search produced no new verified eligible role. Older SuperKalam/Coulomb records remain older listings, not new postings.</t>
+          <t>Public design board and selected details checked. Existing older SuperKalam/Coulomb leads retained with date/pay caveats. No additional newly verified qualifying role.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Public details accessible; applying through YC may require a profile. Company directory is a discovery source, not a vacancy guarantee.</t>
+          <t>Senior and US-only listings excluded; a landing-page listing is not proof of a renewed cohort.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -12093,22 +12993,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>Targeted indexed search</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Direct filtered route was not accessible in the research tool; public YC employer pages provide overlapping job content. Additional pass: Additional targeted public design/intern search produced no new verified eligible role. Older SuperKalam/Coulomb records remain older listings, not new postings.</t>
+          <t>India design-intern search performed alongside YC board review; no additional eligible detail verified.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Do not double-count YC and Work at a Startup mirrors as different openings.</t>
+          <t>Public targeted sample, not an exhaustive database crawl.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -12126,22 +13026,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>searched</t>
+          <t>API scan and targeted review</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fetched the actual October2026 thread via Algolia API:266 top-level posts,25 mentioning designer/UX/design-engineer terms. No verified India-eligible UX/product internship or junior role from this pass. Cardog and Sundream retained as conditional company targets. Additional pass: Additional Algolia API scan of266 top-level comments: strict designer/UX/UI/product-design terms matched20 (different methodology from prior25-term count). No additional paid India-eligible junior design internship verified.</t>
+          <t>October thread Algolia API again returned266 top-level comments;20 strict design/UX/UI term matches. Sampled matching posts did not yield another verified India-eligible paid UX/product internship or junior vacancy.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Engineering, senior, North-America/Europe-only and volunteer posts were not promoted as qualifying design internships.</t>
+          <t>Strict term matching differs from the older25-term count; engineering, senior, volunteer and restricted-geography posts are not recommendations.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -12192,22 +13092,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Public details and search results accessible</t>
+          <t>Public details and targeted search</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expanded targeted searches beyond four earlier listings. Four new relevant details retained with undisclosed stipend (Icogz, VictorFlow, Balusen, Gunadhya), plus genuine cross-post enrichments. Numerous other interns are below pay floor, unpaid, wrong discipline or expired; no inference that search counts equal relevant vacancies. Additional pass: Additional targeted check: BiCSoM fresher detail opened, but old original/closed LinkedIn makes it watchlist-only; Melento minimum INR11k is below target; Kixar and Redliner copies expired. No new qualifying Indeed vacancy added.</t>
+          <t>Existing Indeed detail pages rechecked. Icogz title corrected to original Intern-UI/UX without changing ID. Redliner explicitly expired; low pay and misleading maximum-only claims excluded. No additional qualifying Indeed-primary role added.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Search sample, not the entire inventory; current pay remains unstated unless original advert says otherwise.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12229,7 +13129,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -12239,12 +13139,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Direct/domain public queries again reported robots restrictions. No newly verified original Naukri role; existing employer-linked route retained. Account connection was not tested or required for these public-source checks; do not imply signed-in access. Additional pass: Targeted public queries again blocked by robots; no original or signed-in access verified and no new role invented.</t>
+          <t>Targeted original/domain search again blocked or inaccessible; no new original vacancy verified. Existing employer-linked route retained.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>No signed-in account access or bypass used.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -12262,22 +13162,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Public role details accessible; apply uses candidate login</t>
+          <t>Targeted public search</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Qoruz junior product UX alternative found with annual pay preserved; Ungrammary matching internship adds below-target advertised pay context. Monsoonfish/Integra/AMPM below target and unrelated Product Management roles excluded. Current public examples were mostly below target: Integra Magna INR 3–5k/month, AMPM INR 10–15k/month, SDS INR 7–15k/month. BigThinkCode has an annual INR 1–3 lakh header and restrictive cohort/certification requirements, retained as company research. Ungrammary cross-post adds an annual range and inactive-recruiter caveat to an existing role. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+          <t>Current-looking results included Integra Magna3–5k/month and Monsoonfish5–10k/month, below target. No source quota filled with unsuitable cards.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Original monthly ranges kept distinct from annual salary and aggregator maxima.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12336,22 +13236,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Blocked by robots.txt</t>
+          <t>Restricted public access</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Public domain search reported robots restriction. No new original role verified; no CAPTCHA bypass or signed-in session attempted. Additional pass: Additional public domain queries again robots-blocked; no original session or access-control bypass attempted.</t>
+          <t>Direct public UI/UX route unavailable through research tool. No original details verified in this pass.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>No authenticated access or blanket freshness claim.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -12369,22 +13269,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Targeted public search only</t>
+          <t>Targeted indexed search</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Targeted indexed design-intern/0–1 year queries produced no independently verified eligible detail in this pass. This is a coverage limitation, not proof of no jobs; authenticated matching workflow not inspected. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+          <t>Design-intern site query did not produce a newly verified eligible detail in this pass.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>No original/authenticated inventory inspection established.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -12402,22 +13302,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Partial public coverage; originals individually checked</t>
+          <t>Original details checked; stale indexes flagged</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Several indexed internships were expired on direct check; accessible ads often unpaid or below target. Attira preserved as company/conditional research, no proven qualifying stipend. Accounts may be needed to apply/save, not to research these public detail pages. Additional pass: BetterStory remote INR25k visual internship detail opened; employer explicitly excludes product/UX scope, so not shortlisted.</t>
+          <t>Entrupy and Chiblu4209561 originals now410. Chiblu employer page remains separate evidence and record stays on hold. AVYAM and Ourora unpaid; BetterStory outside UX/product scope. No suitable new verified vacancy added.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Indexed cards may survive removed originals. Header compensation periods must not be guessed.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12439,22 +13339,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Public API and individual details checked</t>
+          <t>Existing detail rechecked and targeted search</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Documented public API checks: India product-designer internships returned 0; UX internships returned 6, including five developer/graphic roles and GWEN fee-based training. Entry-level UI/UX search returned 6 records: one plausible junior opening at Energise.pro, an experienced Cloud Counselage role, a GitLab talent pool, adjacent QA and graphic roles. Category counts alone do not establish suitable vacancies. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+          <t>Energise.pro listing still states worldwide, one-year minimum and5 November board deadline. Job expired? is a report button. No new suitable internship verified.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Full-time junior alternative remains on hold for commercial experience/pay/employer intake; no automatic closure from report controls.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12476,22 +13376,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Public category opened; sample checked</t>
+          <t>Targeted public search</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>No suitable India-eligible UX/product internship or fresher role verified in the examined public sample. Visible roles were predominantly senior/principal/manager or geographically restricted. Category-level Anywhere in the World labels are insufficient evidence of country eligibility. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+          <t>Reviewed indexed design/contract results and Construelabs company page. No new verified full-time India-eligible junior/intern product role. LooseGrip part-time contract not established as an eligible internship.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>General worldwide labels can conflict with title/office geography; individual detail verification required.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12513,22 +13413,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Public listing/category checked; limited role detail</t>
+          <t>Targeted indexed search</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>No suitable India-eligible UX/product internship or junior role verified from examined categories and junior filters. A junior brand-design example was Canada-only; a worldwide junior graphic role was outside the requested discipline. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+          <t>Search surfaced worker profiles rather than suitable employer details; no new role accepted.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Worker profiles are people seeking work, not vacancies.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12550,22 +13450,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Indexed leads with employer corroboration; mirror details403/404</t>
+          <t>Targeted public search</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Opened design, India andinternpublicpages. No suitable UX/product internship or junior role verified; visible examples were geographic restrictions, senior, graphic/video or other disciplines. Did not bypass paid access or promise comprehensive coverage. Additional pass: Unitedover mirror403 and Innovexis mirror404. Innovexis employer-hosted in295 detail accessible with undisclosed amount; Unitedover employer Dover index only, direct JS shell. Both kept on hold with separate verification limits; mirror relative dates are not original posting dates.</t>
+          <t>Trackier graphic-design intern surfaced; broad marketing/video scope not promoted as a focused UX/product role. Unitedover prior lead retained with original intake limits.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>No new confirmed stipend or fresh-original assertion.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12587,22 +13487,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Public category opened; sample checked</t>
+          <t>Targeted public search</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Examined public designcategory. Product/visual roles predominantly US-national orUSlocal/hybrid; no suitable Indiaeligibleintern/junior verified. Additional pass: Additional targeted public search/category sample yielded no new independently verified qualifying UX/product internship or fresher detail. Coverage is sampled; no claim that all listings were searched.</t>
+          <t>India design search surfaced experienced sound-design work outside requested discipline; no qualifying new role verified.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Targeted indexed sample only.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12624,22 +13524,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Alternate public category opened; no eligible detail verified</t>
+          <t>Direct route inaccessible; targeted search limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Design URL could not be accessed and targetedpublicsearch yielded no independently verifiable matching detail. This is an access/coverage gap, not evidence of no jobs. Additional pass: Alternate /remote-entry-level-product-design-jobs page opened. No new India-eligible internship/junior employer detail verified; index/category labels alone do not establish experience or geography.</t>
+          <t>Design route could not be opened through research tool; cross-board indexed search yielded no verified new matching detail.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Do not claim full board inspection.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -12690,22 +13590,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Public employer directory inspected</t>
+          <t>Attempted directory route; unavailable</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Accessible India startup directory includes existing targets such as Swiggy, Meesho, Groww and Juspay. Rankings/funding do not establish an active business, stipend or design vacancy; verify official careers. Additional pass: Public discovery page reopened; no vacancy inferred from map membership or funding/rank. Role acceptance still requires employer/job-detail evidence.</t>
+          <t>The /startups/india route returned404. No vacancy inferred from directory membership.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Best-effort public targeted sample; original dates, intake and eligibility are verified only where explicitly documented.</t>
+          <t>Employer discovery only; do not claim an entire map was inspected.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -12789,22 +13689,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Targeted public checks</t>
+          <t>Employer/ATS research and existing-lead recheck</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>New Arihant AI and Innovexis employer-hosted internships have undisclosed pay; Unitedover indexed employer ATS remains current-intake unverified. Parallel internship archived; BiCSoM historical fresher page is watchlist-only.</t>
+          <t>Rechecked all39 existing primary URLs subject to robots/access limits:34 pages fetched,4 blocked and1 original removed. New Atlabs/Revvity internships and Moonfire/Enterprise Bot fresher jobs; Glance upgraded to original Greenhouse. Innovexis in295 archived. Ecolibrium stale-careers discrepancy recorded.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Public sample only; no exhaustive or authenticated access claim.</t>
+          <t>A fetched page alone is not proof of active intake. Stipend, cohort dates and office terms remain held where unstated.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -12822,22 +13722,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Targeted public checks</t>
+          <t>Public indexed search; no new verified original</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Targeted indexed UX/product/interaction internship searches produced no newly independently verified original X hiring post. Existing Wint/BThree crossposts retained; no claim of original authenticated access.</t>
+          <t>Targeted India UX/product internship searches produced no newly independently verified original post. Earlier Wint/BThree crossposts retained.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Public sample only; no exhaustive or authenticated access claim.</t>
+          <t>No signed-in X session; zero new verified results does not imply no vacancies exist.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -12855,22 +13755,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Targeted public checks</t>
+          <t>Targeted public search and corroboration</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Targeted early-career searches used as corroboration. BiCSoM crosspost explicitly closed; no new LinkedIn-primary role added. Relative ages are not verified original posting dates.</t>
+          <t>Revvity employer crosspost enriches the same new official role, not a duplicate. BNP remote advert is four months old with amount/current intake unverified; not promoted as newly active. Generic/low-pay listings not added for source quotas.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Public sample only; no exhaustive or authenticated access claim.</t>
+          <t>Relative ages and discovery dates are distinct from original publication dates.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -12887,7 +13787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18363,7 +19263,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18461,8 +19361,384 @@
         </is>
       </c>
     </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Suggested employer target based on a published early-career role; no hiring probability implied.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Remote-India product-design internship on AI video workflows. Employer offers a competitive stipend without an amount.</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Suggested employer target based on a published early-career role; no hiring probability implied.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Life-sciences software UX internship spanning research and design. Stipend, duration and intake timing require confirmation.</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Suggested employer target based on a published early-career role; no hiring probability implied.</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Paid permanent fresher alternative, not an internship. Original salary is INR 2.5–4 lakh per year.</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Suggested employer target based on a published early-career role; no hiring probability implied.</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Permanent early-career UI/product-interface role, not an internship. Pay is absent from the original employer ATS.</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Published UX internship; pay and intake still need confirmation.</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="n"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>No employer-stated amount; aggregator INR30–40k/month is unverified.</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>https://glance.com/careers/latest</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Summer2027 M.Des class-of2027 role. Original indexed deadline17 October has passed despite later mirror dates; no current card added. Check for reopened cohorts.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>No current qualifying stipend established</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>https://salesforce.wd12.myworkdayjobs.com/en-US/External_Career_Site/job/Summer-2027-Intern---UI-UX-Designer_JR363342</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Ecolibrium</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Climate/building analytics software. Static careers names UI/UX Intern, but the linked live ATS shows a visual-marketing intern and a product designer requiring3–5 years. No verified current qualifying UX internship.</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>No current qualifying stipend established</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ecolibrium.io/careers/</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Construe Labs</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS exposes a three-month UI/UX internship,4–6 hours/day, five days/week. Pay, current intake and India eligibility are not stated. Historical India company evidence does not confirm this intake; watchlist pending clarification.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>No current qualifying stipend established</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>https://construelabs.freshteam.com/jobs/iaTEUebfJP5j/ui-ux-design-intern-remote</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M116"/>
+  <autoFilter ref="A1:M124"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Dream,Workable,Possible"</formula1>
@@ -18602,6 +19878,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18613,7 +19897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25686,7 +26970,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Advertised internship; pay and intake require confirmation</t>
+          <t>Tracked in295 role removed; company target retained without an active-vacancy claim</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -25717,7 +27001,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -25847,8 +27131,456 @@
         </is>
       </c>
     </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>AI video creation software</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Gurugram office optional/preferred</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Advertised role; eligibility, pay and intake need review</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern/apply</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Published application route</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Life-sciences technology and software</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Thane / Mumbai, Maharashtra; employer pages use both locations</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Advertised role; eligibility, pay and intake need review</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>https://revvity.wd103.myworkdayjobs.com/External/job/Mumbai/UX-Intern_JR-045767/apply</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Published application route</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Services / technology group</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Business software and technology services</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Advertised role; eligibility, pay and intake need review</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/apply.php?job_id=50</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Published application route</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Conversational AI and enterprise automation</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Advertised role; eligibility, pay and intake need review</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Published application route</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>AI shopping and television experiences</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; remote eligibility not stated</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Official UX internship detail and application available</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>https://glance.com/careers/latest</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Official application</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Summer2027 M</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru / Hyderabad</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Watchlist only; no qualifying current vacancy confirmed</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>https://salesforce.wd12.myworkdayjobs.com/en-US/External_Career_Site/job/Summer-2027-Intern---UI-UX-Designer_JR363342</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Ecolibrium</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Climate/building analytics software</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Watchlist only; no qualifying current vacancy confirmed</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ecolibrium.io/careers/</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Construe Labs</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Services company</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS exposes a three-month UI/UX internship,4–6 hours/day, five days/week</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Remote; current country eligibility unstated</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Watchlist only; no qualifying current vacancy confirmed</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>https://construelabs.freshteam.com/jobs/iaTEUebfJP5j/ui-ux-design-intern-remote</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M116"/>
+  <autoFilter ref="A1:M124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -26065,6 +27797,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId228"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26076,7 +27821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -33389,7 +35134,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+          <t>Original in295 role removed (404/410) on25 October2026; retained for history.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -33432,7 +35177,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+          <t>Original in295 role removed (404/410) on25 October2026; retained for history.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -33475,7 +35220,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+          <t>Original in295 role removed (404/410) on25 October2026; retained for history.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -33518,7 +35263,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Employer-hosted ATS detail accessible. Mentions annual compensation without a figure; no monthly stipend established. Relative publication ages vary across indexed copies and are not reliable original dates. A different older same-company ATS listing advertises INR20–25k/month, below the remote target; it does not set this listing’s pay. Employer also sells training; employment terms and absence of fees need confirmation.</t>
+          <t>Original in295 role removed (404/410) on25 October2026; retained for history.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -33791,8 +35536,1040 @@
       </c>
       <c r="I179" s="2" t="inlineStr"/>
     </row>
+    <row r="180" ht="42" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Gurugram office optional/preferred</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Employer detail and application page are available; the form explicitly permits work from home within India. Duration, stipend amount and cohort/start dates are unstated. General employee perks are not confirmed intern benefits.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Figma proficiency and a portfolio showing design reasoning</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Gurugram office optional/preferred</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Employer detail and application page are available; the form explicitly permits work from home within India. Duration, stipend amount and cohort/start dates are unstated. General employee perks are not confirmed intern benefits.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Interface fundamentals, interaction flows and usability</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Gurugram office optional/preferred</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Employer detail and application page are available; the form explicitly permits work from home within India. Duration, stipend amount and cohort/start dates are unstated. General employee perks are not confirmed intern benefits.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Independent ownership and collaboration with engineering</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183" ht="42" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Gurugram office optional/preferred</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Employer detail and application page are available; the form explicitly permits work from home within India. Duration, stipend amount and cohort/start dates are unstated. General employee perks are not confirmed intern benefits.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Interest in AI creative tools; prior product work is optional</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184" ht="42" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Thane / Mumbai, Maharashtra; employer pages use both locations</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Awareness of UX design and research methods</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185" ht="42" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Thane / Mumbai, Maharashtra; employer pages use both locations</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Clear English communication and presenting design decisions</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186" ht="42" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Thane / Mumbai, Maharashtra; employer pages use both locations</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Curiosity, feedback and collaboration</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187" ht="42" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>UX Intern</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Thane / Mumbai, Maharashtra; employer pages use both locations</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Work includes prototyping and research sessions</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188" ht="42" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>UI / UX Design Trainee (Fresher)</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS and corporate careers page corroborate this paid job. Unpaid training programs are separate and excluded. Apply through ATS only; the support address is technical support, not a recruitment inbox. Start timing and employment terms need confirmation.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Design, HCI, fine-arts or related qualification</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189" ht="42" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>UI / UX Design Trainee (Fresher)</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS and corporate careers page corroborate this paid job. Unpaid training programs are separate and excluded. Apply through ATS only; the support address is technical support, not a recruitment inbox. Start timing and employment terms need confirmation.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Working Figma knowledge and a portfolio; coursework is accepted</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>UI / UX Design Trainee (Fresher)</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS and corporate careers page corroborate this paid job. Unpaid training programs are separate and excluded. Apply through ATS only; the support address is technical support, not a recruitment inbox. Start timing and employment terms need confirmation.</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Wireframes, design-system components and research support</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191" ht="42" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>UI / UX Design Trainee (Fresher)</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS and corporate careers page corroborate this paid job. Unpaid training programs are separate and excluded. Apply through ATS only; the support address is technical support, not a recruitment inbox. Start timing and employment terms need confirmation.</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Openness to critique</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192" ht="42" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer – 0–1 Years Experience</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>0–1 years; graduates with a portfolio are welcome</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193" ht="42" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer – 0–1 Years Experience</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Figma and strong typography, spacing, grids and interface hierarchy</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194" ht="42" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer – 0–1 Years Experience</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Basic UX knowledge and responsive SaaS interfaces</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195" ht="42" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer – 0–1 Years Experience</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Collaboration, iteration and curiosity about AI tools</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196" ht="42" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer – 0–1 Years Experience</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; ATS says hybrid but also five days/week on-site</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>JOIN employer detail advertises 45 hours/week, six-month probation and ASAP start. Hybrid header conflicts with five on-site days. A mirror advertises INR30–50k/month, which the original does not confirm; no verified stipend is inferred.</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Bonus: design systems, HTML/CSS and prior design internship</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197" ht="42" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Official role accessible; pay/intake unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Design student or recent graduate with a portfolio showing reasoning and craft</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198" ht="42" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Official role accessible; pay/intake unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Interaction and system thinking for TV shopping experiences</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199" ht="42" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Official role accessible; pay/intake unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Design-system patterns, iteration and engineering handoff</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200" ht="42" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Official role accessible; pay/intake unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Interest in AI or large-screen products is optional</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201" ht="42" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Summer2027 Intern - UI/UX Designer</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Expired cohort evidence</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru / Hyderabad</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>https://salesforce.wd12.myworkdayjobs.com/en-US/External_Career_Site/job/Summer-2027-Intern---UI-UX-Designer_JR363342</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Summer2027 M.Des class-of2027 role. Original indexed deadline17 October has passed despite later mirror dates; no current card added. Check for reopened cohorts.</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202" ht="42" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Ecolibrium</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Unverified current intake</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ecolibrium.io/careers/</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Climate/building analytics software. Static careers names UI/UX Intern, but the linked live ATS shows a visual-marketing intern and a product designer requiring3–5 years. No verified current qualifying UX internship.</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203" ht="42" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Construe Labs</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern (Remote)</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Part-time internship; intake/geography unconfirmed</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Remote; current country eligibility unstated</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>https://construelabs.freshteam.com/jobs/iaTEUebfJP5j/ui-ux-design-intern-remote</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Employer ATS exposes a three-month UI/UX internship,4–6 hours/day, five days/week. Pay, current intake and India eligibility are not stated. Historical India company evidence does not confirm this intake; watchlist pending clarification.</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I179"/>
+  <autoFilter ref="A1:I203"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Unassessed,Met,Partly met,Gap"</formula1>
@@ -33977,6 +36754,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33988,7 +36789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34003,7 +36804,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Research snapshot: 2026-10-24</t>
+          <t>Research snapshot: 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -34784,6 +37585,90 @@
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>AVYAM LABS</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Original advert explicitly unpaid; excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Entrupy</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Indexed internship original now410 Gone; not an active lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Original indexed deadline17 October2026 has passed; fresher mirror dates do not prove renewed intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>MediNex Workforce</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Mirror reports17.5k/month, below remote target; no qualifying card added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CoreByte Studio</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Remote role explicitly hires within Pakistan, not India.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Ecolibrium</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Current product role requires3–5 years; not a junior/internship match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Tracked in295 original removed404/410; archived stable record, application history retained.</t>
         </is>
       </c>
     </row>

--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$256</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -4690,8 +4690,400 @@
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
     </row>
+    <row r="45" ht="95" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Confirm paid status, monthly stipend, duration and joining window; review AI/mobile-design expectations.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern?apply=1</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Published employer form/contact; manual review</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio; student or personal projects accepted; Figma components, responsive layouts and design systems; Practical AI-assisted design and an interest in funnel analysis; Android/Material conventions and ability to iterate quickly</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Employer posting date not stated; newly researched, not newly posted</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="95" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Ahmedabad-based product team, India</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Confirm stipend, hours, India work arrangement and a suitable 3–4 month duration; use the employer internship form.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Published employer form/contact; manual review</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>Figma, prototyping, user research and design-system skills named; Interest in student-editor and faculty-dashboard usability; Clarify hours and duration before proceeding</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Employer posting date not stated; newly researched, not newly posted</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="95" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Remote Global / Singapore; confirm India contracting and hours</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Confirm paid status, monthly amount, duration, India engagement and time-zone overlap before applying.</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>mailto:careers@formas.ai</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>careers@formas.ai</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Published employer form/contact; manual review</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>Design/HCI/interaction-design student or recent graduate; Figma familiarity and interface-design fundamentals; Prototyping, component-library work and usability-test support</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Employer requests portfolio, resume and a short note about design technology and AI.</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Employer posting date not stated; newly researched, not newly posted</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="95" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Confirm compensation, eligibility and start window through the published careers contact before proceeding.</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>mailto:daankart.com@gmail.com</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>daankart.com@gmail.com</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Published employer form/contact; manual review</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>Figma comfort and user-journey thinking; Explain design decisions and work with engineering; Research, prototyping and usability testing; Design for trust and conversion; six-month office commitment</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Published careers contact for the Hyderabad product/UI internship; confirm paid terms before sending an application.</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Employer posting date not stated; newly researched, not newly posted</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z44"/>
+  <autoFilter ref="A1:Z48"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
@@ -4784,6 +5176,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4795,7 +5195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12886,8 +13286,552 @@
         </is>
       </c>
     </row>
+    <row r="257" ht="42" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="42" customHeight="1">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="42" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="42" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="42" customHeight="1">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Coachingle</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coachingle.com/careers</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Official product role requires3+ years, confirmed in the public role-description bundle. Company target only, not an intern/junior recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="42" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Cravv</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4716470-product-design-intern</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="42" customHeight="1">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Figr</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.antler.co/companies/figr/jobs/48650001-product-design-intern</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="42" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Grexa AI</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>https://peerlist.io/company/grexa_ai/careers/product-design-intern/jobhlknq7lkradbbdc7dbmeg9ne98p</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="42" customHeight="1">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Globalli</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>https://globalli.io/company/careers</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Current official linked Greenhouse API exposes13 jobs and no designer role. Mirrored junior descriptions remain unverified; no active card added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="42" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Superteams.ai</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.superteams.ai/career/figma-design-intern/</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Original role explicitly closed despite its listing on the general careers index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="42" customHeight="1">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Leap</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>https://leapfinance.freshteam.com/jobs/sTgwRD31WhNQ/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Original ATS host/detail returns a site-not-found page; indexed internship not confirmed current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="42" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>LeelaRam Technologies</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leelaramtechnologies.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Original stipend10–15k/month in Mumbai, below target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="42" customHeight="1">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>GoPratle</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4555222-ui-ux-intern-remote-clone</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Original header2–5k and final-year/fresher restriction; not a qualifying stipend match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="42" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4029436-product-design-intern</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Original410 Gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="42" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>frover</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/3307361-product-designer-intern-ui-ux</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Original410 Gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="42" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Mowka</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4503290-product-designer-intern</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Original410 Gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="42" customHeight="1">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>eLeoRex Technologies</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>https://eleorex.com/about-us/career/ui-ux-design-intern/</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Original1October2026 deadline passed; not a current internship recommendation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F256"/>
+  <autoFilter ref="A1:F273"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12898,7 +13842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13775,8 +14719,45 @@
       </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Startup design hiring</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Targeted original-role and startup-board checks</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Four new on-hold startup internships:Propel, Kodin/Autometa Labs, FORMAS.AI and Daankart. Six existing startup leads tagged for search, without duplicate job cards. Added missing employer-directory records and five caveated company targets. Figr/Grexa/Superteams closed, Leap original unavailable, Coachingle experienced-only, Globalli no current ATS designer role; low-pay roles excluded. No new qualifying monthly stipend confirmed.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Best-effort employer, Wellfound, Peerlist, Antler and public search sample. Newly discovered does not mean newly posted. Remote Global still requires India contracting/time-zone confirmation. Startup stage/funding is not independently audited.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Superteams.ai: Original role explicitly closed despite its listing on the general careers index.; Leap: Original ATS host/detail returns a site-not-found page; indexed internship not confirmed current.; LeelaRam Technologies: Original stipend10–15k/month in Mumbai, below target.; GoPratle: Original header2–5k and final-year/fresher restriction; not a qualifying stipend match.; FLIP: Original410 Gone.; frover: Original410 Gone.; Mowka: Original410 Gone.; eLeoRex Technologies: Original1October2026 deadline passed; not a current internship recommendation.; Figr: Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.; Grexa AI: Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.; Cravv: Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13787,7 +14768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19737,8 +20718,619 @@
         </is>
       </c>
     </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Design app interfaces, systems and growth assets at an AI-focused consumer-app team. Full-time internship. Amount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Design student-editor and faculty-dashboard experiences. Employer lists a 2–4 month internship with flexible start. Amount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Prototype and improve a spatial-design product, including interface components and usability testing. Amount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Research and improve donor journeys, interface consistency and a component library. Six-month, full-time office internship. Amount unconfirmed.</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>RevRag AI</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Original employer advert already researched today; stipend and intake terms remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>NeuralPath Technologies</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Original employer advert already researched today; stipend and intake terms remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Zavio</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Original employer advert already researched today; stipend and intake terms remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Chiblu</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Existing researched role; stipend and renewed intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Coachingle</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Official product role requires3+ years, confirmed in the public role-description bundle. Company target only, not an intern/junior recommendation.</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coachingle.com/careers</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Cravv</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Employer advert:INR20,000/month, below the non-Gujarat target; not a current offer to the applicant.</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4716470-product-design-intern</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Figr</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.antler.co/companies/figr/jobs/48650001-product-design-intern</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Grexa AI</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="n"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>https://peerlist.io/company/grexa_ai/careers/product-design-intern/jobhlknq7lkradbbdc7dbmeg9ne98p</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Globalli</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Current official linked Greenhouse API exposes13 jobs and no designer role. Mirrored junior descriptions remain unverified; no active card added.</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying current stipend established unless explicitly stated in role evidence.</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>https://globalli.io/company/careers</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M124"/>
+  <autoFilter ref="A1:M137"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Dream,Workable,Possible"</formula1>
@@ -19886,6 +21478,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19897,7 +21502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -27579,8 +29184,775 @@
         </is>
       </c>
     </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Consumer-app publishing and product growth</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Education software and coding-lab interfaces</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Ahmedabad-based product team, India</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>AI design software for architecture and interiors</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Remote Global / Singapore; confirm India contracting and hours</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Donation and crowdfunding product software</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>RevRag AI</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>AI agents for financial workflows</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Original employer advert already researched today; stipend and intake terms remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>NeuralPath Technologies</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Privacy-first consumer applications</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Original employer advert already researched today; stipend and intake terms remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Zavio</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Financial education software</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Original employer advert already researched today; stipend and intake terms remain unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Chiblu</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace software for independent makers</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India; Bengaluru preferred</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Existing researched role; stipend and renewed intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Coachingle</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>AI learning software</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Official product role requires3+ years, confirmed in the public role-description bundle. Company target only, not an intern/junior recommendation.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coachingle.com/careers</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coachingle.com/careers</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Cravv</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>AI cooking device and companion app</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, office; six months</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4716470-product-design-intern</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4716470-product-design-intern</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Figr</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>AI product-design tools</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru / remote historical description</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.antler.co/companies/figr/jobs/48650001-product-design-intern</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.antler.co/companies/figr/jobs/48650001-product-design-intern</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Grexa AI</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>AI marketing software</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai, office</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>https://peerlist.io/company/grexa_ai/careers/product-design-intern/jobhlknq7lkradbbdc7dbmeg9ne98p</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>https://peerlist.io/company/grexa_ai/careers/product-design-intern/jobhlknq7lkradbbdc7dbmeg9ne98p</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Globalli</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Workforce-management software</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Indexed remote India/Pakistan; current intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Current official linked Greenhouse API exposes13 jobs and no designer role. Mirrored junior descriptions remain unverified; no active card added.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer; Interaction Designer</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>https://globalli.io/company/careers</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>https://globalli.io/company/careers</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Published careers/application route</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M124"/>
+  <autoFilter ref="A1:M137"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -27810,6 +30182,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId254"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27821,7 +30219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36568,8 +38966,997 @@
       </c>
       <c r="I203" s="2" t="inlineStr"/>
     </row>
+    <row r="204" ht="42" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio; student or personal projects accepted</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205" ht="42" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Figma components, responsive layouts and design systems</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206" ht="42" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Practical AI-assisted design and an interest in funnel analysis</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207" ht="42" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Rendered official detail verified, including interface work and AI-assisted iteration. Stipend, duration and start dates are unstated. This is not a confirmed paid-stipend match.</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Android/Material conventions and ability to iterate quickly</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208" ht="42" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Ahmedabad-based product team, India</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Figma, prototyping, user research and design-system skills named</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209" ht="42" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Ahmedabad-based product team, India</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Interest in student-editor and faculty-dashboard usability</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210" ht="42" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Remote; Ahmedabad-based product team, India</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Official careers section advertises a stipend without an amount. It names Figma, prototypes, research and design systems; no formal degree or experience requirement is stated. Hours and intake need confirmation.</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Clarify hours and duration before proceeding</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211" ht="42" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Remote Global / Singapore; confirm India contracting and hours</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Design/HCI/interaction-design student or recent graduate</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212" ht="42" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Remote Global / Singapore; confirm India contracting and hours</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Figma familiarity and interface-design fundamentals</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213" ht="42" customHeight="1">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Remote Global / Singapore; confirm India contracting and hours</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Specific internship detail says Remote Global / Singapore and allows full-time or part-time work. Current design/HCI students or recent graduates are eligible in the advert. Pay, duration and local engagement terms are unstated.</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Prototyping, component-library work and usability-test support</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214" ht="42" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Figma comfort and user-journey thinking</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215" ht="42" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Explain design decisions and work with engineering</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216" ht="42" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Research, prototyping and usability testing</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217" ht="42" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Product &amp; UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Official careers page names the role, location, duration and HR contact. Stipend and exact start window are not stated; do not infer a paid offer from internship benefits.</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Design for trust and conversion; six-month office commitment</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218" ht="42" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>RevRag AI</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Original company role is accessible and lists Bengaluru on-site. Third-party ₹40k claims are not confirmed by this page.</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219" ht="42" customHeight="1">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>NeuralPath Technologies</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Company careers page explicitly lists a remote Product Design Intern opportunity and year-round applications. Duration and stipend are discussed individually.</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220" ht="42" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Zavio</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Company careers page lists this as an open internship, remote anywhere in India. Stipend and posting date are not stated.</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221" ht="42" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Chiblu</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern (UX &amp; UI)</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Remote, India; Bengaluru preferred</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Company still exposes the role page and links it from careers. It is an older May posting; current hiring and stipend require confirmation. Recheck25 October: employer page remains accessible; linked Wellfound4209561 now returns410 Gone. The employer page alone does not establish a renewed intake.</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222" ht="42" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Coachingle</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Experienced; 3+ years</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coachingle.com/careers</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Official product role requires3+ years, confirmed in the public role-description bundle. Company target only, not an intern/junior recommendation.</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223" ht="42" customHeight="1">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Cravv</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Internship; below pay target</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, office; six months</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4716470-product-design-intern</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224" ht="42" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Figr</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Closed internship evidence</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru / remote historical description</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.antler.co/companies/figr/jobs/48650001-product-design-intern</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225" ht="42" customHeight="1">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Grexa AI</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Archived internship evidence</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai, office</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>https://peerlist.io/company/grexa_ai/careers/product-design-intern/jobhlknq7lkradbbdc7dbmeg9ne98p</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226" ht="42" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Globalli</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Junior Product Designer</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Indexed historical lead</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Indexed remote India/Pakistan; current intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>https://globalli.io/company/careers</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Current official linked Greenhouse API exposes13 jobs and no designer role. Mirrored junior descriptions remain unverified; no active card added.</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I203"/>
+  <autoFilter ref="A1:I226"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Unassessed,Met,Partly met,Gap"</formula1>
@@ -36778,6 +40165,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId225"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36789,7 +40199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37672,6 +41082,138 @@
         </is>
       </c>
     </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Superteams.ai</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Original role explicitly closed despite its listing on the general careers index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Leap</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Original ATS host/detail returns a site-not-found page; indexed internship not confirmed current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>LeelaRam Technologies</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Original stipend10–15k/month in Mumbai, below target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GoPratle</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Original header2–5k and final-year/fresher restriction; not a qualifying stipend match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Original410 Gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>frover</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Original410 Gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Mowka</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Original410 Gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>eLeoRex Technologies</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Original1October2026 deadline passed; not a current internship recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Figr</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Grexa AI</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Cravv</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$325</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$418</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$321</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z62"/>
+  <dimension ref="A1:Z66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -6422,8 +6422,388 @@
       </c>
       <c r="Z62" s="2" t="inlineStr"/>
     </row>
+    <row r="63" ht="95" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; on-site for six months</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Confirm current intake, monthly stipend, exact joining window and six-month full-time availability; prepare one flow with user-feedback evidence.</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>Published employer/board application route; manual review</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>Design/HCI student or recent graduate, or a strong self-taught portfolio; Strong Figma and a design used by someone who supplied feedback; Six months full time on-site in Hyderabad; Prototype and test flows; contribute components and edge states; usability research, data visualisation and frontend are bonuses</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>24August2026 displayed on original employer WR021 page</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="95" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Internship</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Kochi, Kerala, India; work arrangement to confirm</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Confirm that this specific intake remains open, fixed monthly stipend, duration, full-time/office requirements and joining window.</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Job board</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>careers@alignminds.com</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment email explicitly published in the institutional job advert; no email sent</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Infoparks Kerala detail names a Kochi UI/UX internship and published recruitment inbox. No numeric pay, duration, hours, original date or start deadline. Employer careers page corroborates the company, but does not independently establish this intake.</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>Basic understanding of UI/UX principles; Familiarity with Figma, Adobe XD, Sketch or similar tools; Attention to detail, creativity and openness to feedback</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>Original publication date unstated; newly researched does not mean newly posted</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="95" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India; work mode not stated</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Confirm fixed stipend, active intake, student eligibility, implementation stack, hours, duration, office/remote arrangement and joining window.</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>Published employer/board application route; manual review</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>Employer-authored LinkedIn detail asks for website redesign, Figma wireframes/mockups and implementation on the live site. Pay, duration, weekly hours, degree criteria and work mode are absent. Relative five-day label is not a verified original posting date. Official company website corroborates marketplace context only.</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>Create website wireframes and mockups in Figma; Improve website appearance, usability and flows; Implement design changes on the live website; exact technology stack unstated</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>Original publication date unstated; newly researched does not mean newly posted</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="95" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer (0–1 years) — junior alternative</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India; on-site</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the experience threshold, student/full-time eligibility, salary in its original units and joining date; demonstrate components and a design case study without assuming frontend work counts as product-design tenure.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>Published employer/board application route; manual review</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>Body asks1+years in product/UI-UX, including internships; title says0–1years: clarify; Portfolio may contain academic/personal projects or strong case studies; Figma Auto Layout, components and prototyping; typography and colour fundamentals; iOS/Android/web interfaces, mentored HIG/Material Design, micro-interactions and developer collaboration</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Original publication date unstated; newly researched does not mean newly posted</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z62"/>
+  <autoFilter ref="A1:Z66"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
@@ -6552,6 +6932,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6563,7 +6951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16862,8 +17250,2984 @@
         </is>
       </c>
     </row>
+    <row r="326" ht="42" customHeight="1">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="42" customHeight="1">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Infoparks Kerala detail names a Kochi UI/UX internship and published recruitment inbox. No numeric pay, duration, hours, original date or start deadline. Employer careers page corroborates the company, but does not independently establish this intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Employer-authored LinkedIn detail asks for website redesign, Figma wireframes/mockups and implementation on the live site. Pay, duration, weekly hours, degree criteria and work mode are absent. Relative five-day label is not a verified original posting date. Official company website corroborates marketplace context only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="42" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="42" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/sparksupport-infotech-pvt-ltd/ui-ux-designer-intern-1</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Infoparks Kerala advert describes a six-month on-site design internship with Company Standard stipend. Original employer careers page explicitly says no job openings. Current intake is unresolved; no active feed card and no claim the advert itself was definitively closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="42" customHeight="1">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>https://sparksupport.com/careers/</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Original careers says no job openings; conflict retained with institutional internship advert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="42" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/nuvento-systems-private-limited/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Institutional employer advert explicitly specifies three months unpaid; a possible later salary does not make the internship paid. Excluded from active recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="42" customHeight="1">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Indexed original employer detail states15,000INR/month gross for2–3months, plus discretionary performance incentives. Direct detail timed out during this pass; evidence is indexed official text. Lower stipend and mainly social/visual/video scope exclude it from the active UX shortlist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="42" customHeight="1">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Original posted7October2026. Despite Junior title, body explicitly asks2–6years and B.Tech/B.E with CS/IT/ECE preferred. Not an internship/fresher recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="42" customHeight="1">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="42" customHeight="1">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="42" customHeight="1">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="42" customHeight="1">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>BThree Design Agency</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-bthree-design-agency-4473077505</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="42" customHeight="1">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Wint Wealth</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sruthisivakumar_product-design-intern-wint-wealth-activity-7515659430051426304-tqUQ</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="42" customHeight="1">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Hevo Data</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/hevodata/433ffdef-3125-48ed-a131-52c697c321ee</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="42" customHeight="1">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>RevRag AI</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="42" customHeight="1">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Chiblu</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="42" customHeight="1">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>NeuralPath Technologies</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="42" customHeight="1">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>KRMR Solutions</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>https://krmrsolutions.com/careers/design-intern</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="42" customHeight="1">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Zavio</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="42" customHeight="1">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Gnixar Academy</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jobleads.com/in/job/product-design-intern--india--e24abd61a6654a91f9a3af3bab3db8da5</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="42" customHeight="1">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="42" customHeight="1">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Techolution</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="42" customHeight="1">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="42" customHeight="1">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Green Ping Solutions</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=157d2635900933e2</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="42" customHeight="1">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="42" customHeight="1">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; role body is empty/JavaScript-only. Current intake unresolved; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="42" customHeight="1">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="42" customHeight="1">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="42" customHeight="1">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>project44</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="42" customHeight="1">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Frappe</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>https://frappe.io/careers/open-positions/designer</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="42" customHeight="1">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Juno</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="42" customHeight="1">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="42" customHeight="1">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Ungrammary</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="42" customHeight="1">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Nonlinear</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>https://nonlinear.in/careers</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="42" customHeight="1">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Octet Design Studio</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>https://octet.design/careers/</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="42" customHeight="1">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Octet Design Studio</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>https://octet.design/careers/</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="42" customHeight="1">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>SuperKalam</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="42" customHeight="1">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Coulomb AI</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="42" customHeight="1">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Icogz</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="42" customHeight="1">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>VictorFlow</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="42" customHeight="1">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Gunadhya Software Solutions</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="42" customHeight="1">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Qoruz</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="42" customHeight="1">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Energise.pro</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="42" customHeight="1">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="42" customHeight="1">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; role body is empty/JavaScript-only. Current intake unresolved; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="42" customHeight="1">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="42" customHeight="1">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="42" customHeight="1">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="42" customHeight="1">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="42" customHeight="1">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; role body is empty/JavaScript-only. Current intake unresolved; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="42" customHeight="1">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="42" customHeight="1">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="42" customHeight="1">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="42" customHeight="1">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Payzoplus</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.payzoplus.com/company/careers/design</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="42" customHeight="1">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>DECTIFY</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.dectify.in/careers/details/DTCI-S191348/ui-ux-designer/</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="42" customHeight="1">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>CollabOP</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.collabop.com/careers/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="42" customHeight="1">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/lokal-app/j/CB2EDD7186</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; role body is empty/JavaScript-only. Current intake unresolved; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="42" customHeight="1">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Aeron Systems</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeronsystems.com/careers/design-intern-visuals-ui-ux/</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="42" customHeight="1">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Androcid</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>https://androcid.freshteam.com/jobs/_KvFSyux1O8C/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="42" customHeight="1">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>SutharTech</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>https://suthartech.com/internships/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="42" customHeight="1">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Nihar / Creuto</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.niharrout.com/work-with-me/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="42" customHeight="1">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>ATRISI</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>https://atrisi.org/collaborate/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="42" customHeight="1">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Toddle</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>https://toddle.keka.com/careers/jobdetails/36030</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="42" customHeight="1">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Toddle</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>https://toddle.keka.com/careers/jobdetails/85790</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="42" customHeight="1">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Mojro</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ux-design-research-intern-at-mojro-4477515785</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="42" customHeight="1">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>LeadSquared</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=af19b01b18d49a36</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="42" customHeight="1">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Krevok</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>https://krevok.com/careers</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched. Fetch does not independently establish current intake or revalidate all terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="42" customHeight="1">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="42" customHeight="1">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="42" customHeight="1">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="42" customHeight="1">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="42" customHeight="1">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="42" customHeight="1">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="42" customHeight="1">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Qoruz</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Role body reviewed; existing pay units, requirements and stable record retained. Current cohort/start date still needs employer confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="42" customHeight="1">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>https://gravity.jobs.growhire.com/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Same requisition on Growhire ATS; enrich existing Gravity record without duplicate. Unknown pay/duration and strong ownership expectations remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="42" customHeight="1">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Travel On Tips</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=ffeba8fc64341436</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Exact Indeed Ahmedabad six-month internship advert5–10kINR/month; below Gujarat floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="42" customHeight="1">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Picktime</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=d85a0138a8f9dfdd</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Exact Indeed Hyderabad in-person UI/UX internship12–15kINR/month; below target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="42" customHeight="1">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Aiva Technology</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=f269a751c3d3ad87</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Exact Indeed Bengaluru interaction/Figma/React internship15–18kINR/month; below target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="42" customHeight="1">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>YS Innovations</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=4f3cbca2acaedf92</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Indexed Indeed Coimbatore internship8–10kINR/month; below target. Original detail not separately opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="42" customHeight="1">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>WebEarl</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=0bd3b6429ce89f4a</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Indexed Indeed Ahmedabad up-to8kINR/month; below target; not independently reviewed detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="42" customHeight="1">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/nuvento-systems-private-limited/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Institutional advert explicitly unpaid for three months; later salary not current internship pay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="42" customHeight="1">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>0110 Design</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-frontend-development-intern-at-0110-design-4478994398</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="42" customHeight="1">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>UNMANND</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-unmannd-4476265566</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern is mechanical UAV CAD/FEA role with mechanical-engineering background; outside UX/product interface scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="42" customHeight="1">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Junior title conflicts with original2–6years requirement; not a fresher internship alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="42" customHeight="1">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official15kINR/month gross2–3months visual/media design internship; below remote target. Direct role timed out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="42" customHeight="1">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>MailerMen</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mailermen.com/jobs/ux-writing-and-interface-design-intern-remote-india-291</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Original detail explicitly unpaid;4September posting and27October update remain different dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="42" customHeight="1">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Sensor Equation</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4079234-ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>Indexed relevant remote listing original returned410Gone; not an active lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="42" customHeight="1">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>IQnext</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4475568-ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Indexed internship original returned410Gone; current intake not inferred from snippet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="42" customHeight="1">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Triptych Technologies</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.triptych-technologies.com/jobs/design-intern</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Original design internship is social graphics/pitch decks/internal branding; no core UX/product responsibilities established.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="42" customHeight="1">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Seloriz</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seloriz.com/jobs/product-design-industrial-design-intern</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Original remote India six-month internship is physical/industrial product design with CAD and immediate start; not a core UX/product-interface lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="42" customHeight="1">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Future Interns</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/uiux-design-intern-at-future-interns-4480685128</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Indexed October2026 cohort explicitly unpaid for one month; not a paid internship match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="42" customHeight="1">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/sparksupport-infotech-pvt-ltd/ui-ux-designer-intern-1</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T01:42:05+00:00</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Institutional internship advert conflicts with official careers no openings. Company-only unresolved evidence, not a confirmed current vacancy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F325"/>
+  <autoFilter ref="A1:F418"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16874,7 +20238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16936,22 +20300,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Targeted public design/India search and retained URL checks</t>
+          <t>Accessible category and sample search</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Public design board opened, India internship search run, existing SuperKalam/Coulomb originals fetched. No additional suitable current YC-primary lead.2024 original dates/older-listing/on_hold and pay conflicts preserved.</t>
+          <t>YC design category opened and India internship query searched. Cityfurnish indexed UI/UX internship is Gurugram with anomalous10–15INR/month header, not a qualifying role. No new suitable employer-verified YC internship added.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Directories, US-only and senior roles are not inferred eligible vacancies; zero new qualifying source result is preserved.</t>
+          <t>Category date October2026 does not date individual roles. Existing SuperKalam/Coulomb2024 origins and compensation-unit conflicts retained; no renewed intake inferred.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -16969,22 +20333,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Public route opened; extraction limited</t>
+          <t>Inaccessible tool route / indexed sample</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Public design jobs route again extracted no readable job body; targeted indexed searches yielded no additional verified suitable original detail.</t>
+          <t>Explicit Work at a Startup India-design search attempted; jobs?roles=designer original inaccessible through research tool. No new suitable role verified.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>No account/session assumed. Older YC leads are retained with actual original dates.</t>
+          <t>No logged-in access implied, no source quota and no duplicate YC card.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -17002,22 +20366,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Public API scan and selected matching posts</t>
+          <t>Public HN API top-level scan</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Current Algolia snapshot393 comments including replies,263 top-level posts,25 normalized designer/UX/UI matches. Previous26October snapshot had266 top-level posts; API count change is not proof roles closed. Selected matches still yielded no verified India-eligible junior paid design lead.</t>
+          <t>October2026 thread49922569 public API:319top-level records fetched;21 raw-text designer/UX/UI-term matches. Reviewed matching headings/geography/seniority; no independently verified suitable new India junior/intern vacancy. Earlier266top-level figure belongs to a prior snapshot.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Term matches include engineering/product-manager false positives. US/Europe/onsite/senior and volunteer examples excluded; not every matching employer career page audited.</t>
+          <t>Term filter is a screening aid, not every linked employer JD. Raw-text counts differ from previous normalized-text method; no direct trend inferred. Trustworthy part-time pay/India eligibility unspecified; US/BayArea roles and senior postings unsuitable.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -17068,27 +20432,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Accessible originals plus sample discovery</t>
+          <t>Accessible exact details and targeted search</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Seven prior active Indeed primaries fetched. LeadSquared Job_444 upgraded from directory-only index to one on-hold role via exact detail:0–1years, Bengaluru, no full JD/pay. Arihant genuine cross-post added to same ID. PV Labs3–5k visuals excluded. Microsoft detail found directly, but original employer/current eligible city or remote intake unresolved:company-only evidence.</t>
+          <t>Three new exact Indeed details reviewed: Travel On Tips5–10k/month, Picktime12–15k/month, Aiva15–18k/month; all below target. Existing active Indeed primaries fetched. No new suitable Indeed card; salary minima are not replaced by upper endpoints.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Some tool/redirect routes unavailable while direct public HTTPS details worked.21October LeadSquared field is Updated Date, not original posting date. No duplicate source-quota cards.</t>
+          <t>Sample search/detail checks, not every Indeed job. Indexed YS/WebEarl low-pay examples are labelled indexed, not newly verified originals.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Kixar: INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.; Melento: Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.; Redliner: Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.; BiCSoM: Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.; We-intern: Direct Indeed detail INR10,000–20,000/month remote, below target.; Balusen Technologies: Original expiry banner; retained archived ID.; PV Labs: Exact Indeed detail3–5k stipend/up-to5k per month; four-week product-image/e-commerce-visual role, below pay and outside core UX.</t>
+          <t>Kixar: INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.; Melento: Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.; Redliner: Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.; BiCSoM: Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.; We-intern: Direct Indeed detail INR10,000–20,000/month remote, below target.; Balusen Technologies: Original expiry banner; retained archived ID.; PV Labs: Exact Indeed detail3–5k stipend/up-to5k per month; four-week product-image/e-commerce-visual role, below pay and outside core UX.; Travel On Tips: Exact Indeed Ahmedabad six-month internship advert5–10kINR/month; below Gujarat floor.; Picktime: Exact Indeed Hyderabad in-person UI/UX internship12–15kINR/month; below target.; Aiva Technology: Exact Indeed Bengaluru interaction/Figma/React internship15–18kINR/month; below target.; YS Innovations: Indexed Indeed Coimbatore internship8–10kINR/month; below target. Original detail not separately opened.; WebEarl: Indexed Indeed Ahmedabad up-to8kINR/month; below target; not independently reviewed detail.</t>
         </is>
       </c>
     </row>
@@ -17105,22 +20469,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Blocked by robots; existing shell response unresolved</t>
+          <t>Blocked by robots.txt</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Explicit Naukri-domain UX/internship remote/India queries attempted; research tool reports non-retryable robots block. Earlier primary URL check returned no readable body. No new original Naukri vacancy verified.</t>
+          <t>Explicit Naukri-domain discovery returned non-retryable robots restriction; original UI/UX intern search inaccessible. Retained Keyideas primary responded with an empty body, not a verified vacancy.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>No linked account, original freshness claim, alternate identity or CAPTCHA bypass. Prior mirror/older route limits retained.</t>
+          <t>No authenticated account, CAPTCHA bypass or repeated restricted-domain attempts. Indexed Naukri-associated Miko mirror says unpaid, while another mirror10–12k has unclear period; no pay or vacancy promoted from these conflicts.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17142,22 +20506,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Targeted public search and existing salary-unit checks</t>
+          <t>Accessible retained detail and indexed search</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Existing Qoruz original fetched; annual4–6lakh and1–3years retained. Search sample includes3–5k/month internships and older Ungrammary10–12k/month. No additional qualifying Cutshort-primary role.</t>
+          <t>Cutshort junior/UIUX search repeated; retained Qoruz detail still lists1–3years and4–6lakhINR/year. No new suitable internship found in sample.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Minimum pay matters; annual full-time salary is not monthly internship stipend. Prior negative pay evidence retained.</t>
+          <t>Annual salary stays annual. Ungrammary10–12k/month fellowship caveat retained, not a qualifying match. Search category counts are not an inventory review.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -17179,22 +20543,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Targeted indexed search; public search route unavailable</t>
+          <t>JavaScript / cookie-limited route</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>UI/UX internship/November targeted search attempted; public search route unavailable. No additional suitable original detail verified.</t>
+          <t>Explicit Unstop internship/UIUX search attempted. Original internships page returns Please Wait / Cookies Disabled without readable role inventory. No new role verified.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Mirror deadlines/start windows do not establish renewed employer intake; prior expired examples retained.</t>
+          <t>No cookie/access-control bypass; generic search results and other-board mirrors do not establish an Unstop original.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -17216,22 +20580,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Restricted original route; targeted indexed discovery</t>
+          <t>Restricted / robots-blocked</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>UI/UX/product-design stipend query run; original route restricted. No new verified suitable employer intake accepted from mirrors.</t>
+          <t>Explicit Internshala product-design30k query and original UI/UX internship route attempted; original restricted. Mirrored low-pay/unpaid examples did not produce a qualifying new role.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>No authenticated inventory or bypass. Deadline, original date and mirror age remain distinct.</t>
+          <t>No authenticated session implied. Original posting/start dates cannot be established from fresh mirror crawl labels.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -17249,22 +20613,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Explicit early-career query; public route unavailable</t>
+          <t>520 error / limited indexed discovery</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Internship/fresher UI/UX search performed and public UX route attempted; unavailable. No new suitable role detail verified.</t>
+          <t>Explicit Instahyre design-intern query searched; original home returned520 through research tool. No exact suitable new role verified.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Salary guide/category counts are not open vacancies or current listing compensation.</t>
+          <t>Do not equate public search with signed-in access or complete job inventory.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -17282,27 +20646,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Selected exact original detail and startup search</t>
+          <t>Indexed discovery; exact samples gone</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>NoobSync original checked:3months,20hours/week,India remote but explicitly no fixed stipend/performance-only. Company-only caveated record, no guaranteed-pay recommendation. Targeted other design-intern India search yielded no new accepted Wellfound-primary role.</t>
+          <t>Wellfound search found IQnext and Sensor Equation; both exact original details410Gone. Autumn Tech Worx indexed10–15k and other unconfirmed snippets not promoted.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>No fixed stipend is distinct from merely undisclosed amount. Platform relative age not original date.</t>
+          <t>Fresh crawl of a search snippet does not override410 original. No new qualifying Wellfound vacancy.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid; BetterStory: INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.; Rootcode: Original Wellfound detail returned410 Gone.; NoobSync Innovations: Explicit no fixed stipend, performance-only compensation and20hours/week; no guaranteed monthly floor.</t>
+          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid; BetterStory: INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.; Rootcode: Original Wellfound detail returned410 Gone.; NoobSync Innovations: Explicit no fixed stipend, performance-only compensation and20hours/week; no guaranteed monthly floor.; IQnext: Indexed internship original returned410Gone; current intake not inferred from snippet.; Sensor Equation: Indexed relevant remote listing original returned410Gone; not an active lead.</t>
         </is>
       </c>
     </row>
@@ -17319,22 +20683,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>India-UX category and exact internship review</t>
+          <t>Accessible public category / targeted search</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Public India UX category sampled and retained Energise.pro fetched. Exact Metasys remote internship explicitly unpaid initially; excluded despite25October board date. No newly qualifying paid internship found.</t>
+          <t>India entry-level design and UX/intern categories searched/opened. Entry-level India page showed descriptive/sign-up content without readable qualifying cards in reviewed extract. Existing Energise detail remains accessible.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Job expired? control is a reporting button, not closure evidence. Category and board dates are not independently employer-confirmed dates.</t>
+          <t>Global intern examples may be Poland/other-country-only. Energise Job expired? is a report button, not a closure notice. No new India-eligible internship independently verified.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -17356,22 +20720,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Public design-category sample and junior query</t>
+          <t>Accessible public category sample</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Design category opened and junior/product-designer search run. Sample did not verify another India-eligible early-career product/UX detail.</t>
+          <t>We Work Remotely design category opened and junior-product query searched. Reviewed public extract did not establish an India-eligible junior/intern role.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Category membership/Anywhere wording alone does not verify role-level legal geography, experience or current intake.</t>
+          <t>Category/sample only; senior Poland/Europe or generic global labels do not establish India eligibility.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -17393,22 +20757,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Public design-category sample and intern query</t>
+          <t>Accessible public category sample</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Public design route and intern-design indexed query inspected; no suitable new original role independently verified.</t>
+          <t>Remote OK design category opened and India-intern query searched. No suitable exact internship/junior role established from reviewed sample.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Best-effort sample only; no all-inventory or linked-account claim.</t>
+          <t>Location filters and generic page taxonomy are not a vacancy or India permission. No claim of full inventory scraping.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -17430,22 +20794,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Public category and targeted India query</t>
+          <t>Accessible public category / limited sample</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Design category opened and UX/intern India query run. No additional qualifying verified role; existing Unitedover shell and mirror limits retained.</t>
+          <t>Remotive design category opened and India-UX-intern query searched. No suitable exact new role verified.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Paid/unavailable inventory not accessed; search ages and category totals are not reviewed vacancy counts.</t>
+          <t>Public category and sign-in/unlock boundaries limit coverage; no paid-access bypass and no complete-inventory claim.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17467,22 +20831,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Public design sample and junior India query</t>
+          <t>Accessible category / sample search</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Design route and junior UX India search checked; visible senior/restricted/non-core design sample produced no new suitable verified detail.</t>
+          <t>Remote.co design category and India-junior search checked; reviewed sample includes senior graphic design, not a suitable new internship.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Remote work is not automatically remote India. No source-quota vacancy inferred.</t>
+          <t>Remote generally does not imply India eligibility. No new role from landing-page or generic descriptions alone.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17504,22 +20868,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Entry-level public route; readable jobs limited</t>
+          <t>Accessible descriptive entry-level page</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Entry-level design page and intern-design search checked. Route exposed navigation/descriptive text without readable cards; indexed Pinterest research example is USA-only.</t>
+          <t>Working Nomads entry-level design page opened and design-intern search attempted. Page exposed descriptive content/navigation without readable qualifying job cards in this extract.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>No claim to have checked every listing, paid feed or signed-in inventory.</t>
+          <t>No claim that the site has zero jobs; only this sample yielded no independently verified role.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -17537,22 +20901,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Public map/city discovery sample</t>
+          <t>Accessible directory; city route unavailable</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Homepage and eligible-city routes sampled. Additional Bangalore Startup Map Toddle detail led to current employer feed and role verification; directory membership alone not used as vacancy proof.</t>
+          <t>StartupMap.in home opened:startup counts and city/sector/hiring filters visible. Hyderabad city route inaccessible via research tool.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Best-effort discovery sample. Each accepted vacancy needs separate employer or exact advert evidence.</t>
+          <t>Directory presence, funding or hiring filter is employer discovery only. No vacancy inferred and no map-derived personal-fit claim.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -17570,22 +20934,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Public India directory sample</t>
+          <t>Indexed public directory sample</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>India ranking/directory opened for employer discovery; no role inferred from funding, rank or traffic.</t>
+          <t>StartupBlink India explicit discovery query returned October2026 company ranking/context, including pharmacy/product companies. No eligible exact UX internship established from ranking.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Best-effort discovery sample. Each accepted vacancy needs separate employer or exact advert evidence.</t>
+          <t>Funding/traffic/employee rank is not an opening. Existing researched product targets retained; no new role claimed from directory alone.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -17603,22 +20967,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Public map/register sample</t>
+          <t>Indexed directory and methodology sample</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Map/register page opened; dynamic map not exhaustively inspected. Registration and scheme records are employer discovery only.</t>
+          <t>Indian Startup Map India/design pages examined in search extracts:August2026 government-register snapshot, with explicit dormant-company and location-precision limits.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Best-effort discovery sample. Each accepted vacancy needs separate employer or exact advert evidence.</t>
+          <t>Registration/funding is not current operation or hiring. Paid reports not accessed; no vacancy derived from directory counts.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -17636,22 +21000,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Direct homepage timeout; indexed sample</t>
+          <t>Indexed public directory sample</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Direct homepage timed out; indexed directory context limited. No hiring inference from membership.</t>
+          <t>IndianStartupsMap home/about/rules surfaced in discovery search;648companies and16cities reported by site snapshot.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Best-effort discovery sample. Each accepted vacancy needs separate employer or exact advert evidence.</t>
+          <t>User submissions/map positions are company context only, not independently verified employer roles. No exhaustive employer checks claimed.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -17669,25 +21033,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Primary-source maintenance and selected deeper employer checks</t>
+          <t>Original role review and whole-board URL maintenance</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>All51 prior active primary URLs attempted:47 fetched,4 collector robots blocks. Four responses are shells/metadata. Eight new role records:seven internships and one junior alternative. SutharTech explicit December cohort/24November deadline; no new numeric stipend. Toddle legacy redirect resolved through current public active feed/detail URLs. No newly confirmed closed existing role.</t>
+          <t>New WATER WR021 six-month Hyderabad UX internship and Pixster Ahmedabad junior product role: pay absent, both held. Menstrupedia25–30k/month and existing annual Moonfire pay rechecked; Gravity ATS cross-post deduplicated. All59 active primary URLs attempted:52 public responses,7 robots/access blocks; four fetched bodies were shells.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>A successful fetch is not renewed intake. Dates remain original versus discovery/updated fields. No private browser data accessible; no form submissions or messages.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>A fetched page is not renewed intake. Two blocked LinkedIn primaries separately readable through public research. Nine original-primary body checks remain unresolved (five blocked plus four shells). No reliable new closure established; two archived records retained.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems: Institutional advert explicitly unpaid for three months; later salary not current internship pay.; Jio: Junior title conflicts with original2–6years requirement; not a fresher internship alternative.; Neurai Technologies: Indexed official15kINR/month gross2–3months visual/media design internship; below remote target. Direct role timed out.; 0110 Design: Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -17702,22 +21070,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Explicit public search; original access limited</t>
+          <t>403 Forbidden / indexed sample</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Explicit India/remote design-intern and junior hiring searches performed, including domain restriction. Original public search remains inaccessible/403; no verified new original hiring post or card.</t>
+          <t>Explicit X design-intern India search and original search URL attempted; original403. Indexed results did not establish a suitable new original UX hiring post.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>No signed-in feed or bypass. Existing mirrored cross-post evidence and derived-date labels retained.</t>
+          <t>No original post freshness verified and no claim of authenticated access. Art Deco visual/motion mirror is not a verified UX vacancy; existing Wint/BThree evidence retained.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -17735,25 +21103,29 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>One new employer-authored internship; retained source rechecks</t>
+          <t>Accessible employer-authored sample</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Mojro employer-authored exact internship added on hold:onsite Bengaluru,3–6months,students preferred,amount unstated. ShramikSathi, More Retail, BThree and Wint descriptions reviewed; existing pay/timing/office terms retained. ATRISI employer-linked job redirects generically and is not treated as a verified cross-post.</t>
+          <t>One new on-hold NueFind website UX/implementation internship, Bengaluru. ShramikSathi30k/month remote India and More Retail35k/month Bengaluru descriptions remain readable. 0110 deferred/equity and UNMANND mechanical CAD roles excluded.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Relative ages not converted into original posting dates. No signed-in application session, contact or submission.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>Pay/start/hours absent on NueFind; relative age is not original publication date. No sign-in, application or employer contact.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0110 Design: Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.; UNMANND: Product Design Intern is mechanical UAV CAD/FEA role with mechanical-engineering background; outside UX/product interface scope.; Future Interns: Indexed October2026 cohort explicitly unpaid for one month; not a paid internship match.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -17768,22 +21140,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Product-first discovery and employer corroboration</t>
+          <t>Targeted startup/company role checks</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Toddle active feed yielded internship and junior alternative. Mojro employer internship added. SutharTech remote December cohort, Creuto/Nihar remote, ATRISI platform work and Krevok studio broaden new targets. No new numeric stipend; NoobSync performance-only and Lyzr experienced role kept company-only.</t>
+          <t>Product/startup sample includes WATER, NueFind and existing Gravity. Gravity matching Growhire requisition added as additionalSources, not another card. Neurai indexed15k and 0110 deferred/equity excluded.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Startup stage/funding not independently audited. Published scope and tools do not establish personal fit or commercial shipping experience.</t>
+          <t>Startup status alone does not establish compensation, active intake or India permission; generic hiring signals remain separate from vacancies.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -17862,8 +21234,45 @@
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Infoparks Kerala</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Accessible institutional employer job details</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Kochi UI/UX internship added on hold: stipend/duration/mode/intake unconfirmed. SparkSupport advert six-month on-site Company Standard stipend conflicts with original careers no openings:company-only. Nuvento explicitly unpaid three months:excluded.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No absolute posting, closing or cohort date found on these institutional details. Institutional job evidence is distinct from original-company intake confirmation.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems: Institutional advert explicitly unpaid for three months; later salary not current internship pay.; SparkSupport Infotech: Institutional internship advert conflicts with official careers no openings. Company-only unresolved evidence, not a confirmed current vacancy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17874,7 +21283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25256,8 +28665,400 @@
         </is>
       </c>
     </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Suggested Workable target for biophysical intelligence and adaptive-product application ux. Editable preference/fit suggestion; not hiring probability or an offer.</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="2" t="n"/>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Current listing compensation undisclosed; no reliable role-specific benchmark added. Confirm the actual offer terms.</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Suggested Workable target for design-led product engineering. Editable preference/fit suggestion; not hiring probability or an offer.</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Current listing compensation undisclosed; no reliable role-specific benchmark added. Confirm the actual offer terms.</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alignminds.com/careers/</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Suggested Possible target for indian-brand discovery marketplace. Editable preference/fit suggestion; not hiring probability or an offer.</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="2" t="n"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Current listing compensation undisclosed; no reliable role-specific benchmark added. Confirm the actual offer terms.</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Suggested Workable target for consumer mobile applications and design systems. Editable preference/fit suggestion; not hiring probability or an offer.</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Current listing compensation undisclosed; no reliable role-specific benchmark added. Confirm the actual offer terms.</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Company watchlist only; current evidence does not establish a suitable paid early-career role. Editable suggestion, not hiring odds.</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="2" t="n"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Amount unstated; Company Standard is not a numerical monthly stipend.</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>https://sparksupport.com/careers/</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Company watchlist only; current evidence does not establish a suitable paid early-career role. Editable suggestion, not hiring odds.</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="n"/>
+      <c r="G160" s="2" t="n"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly unpaid for three months; below stipend target.</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>https://nuvento.com/</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Company watchlist only; current evidence does not establish a suitable paid early-career role. Editable suggestion, not hiring odds.</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Employer-listed stipend</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Limited: indexed official detail; direct fetch timeout</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>Indexed employer15,000INR/month gross; incentives do not raise a guaranteed floor.</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Company watchlist only; current evidence does not establish a suitable paid early-career role. Editable suggestion, not hiring odds.</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="n"/>
+      <c r="G162" s="2" t="n"/>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>Salary not disclosed; no senior or generic company pay substituted.</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M154"/>
+  <autoFilter ref="A1:M162"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Dream,Workable,Possible"</formula1>
@@ -25436,6 +29237,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId181"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25447,7 +29257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34915,8 +38725,492 @@
         </is>
       </c>
     </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Biophysical intelligence and adaptive-product application UX</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; on-site for six months</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Public careers/application route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Services / technology team</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Design-led product engineering</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Kochi, Kerala, India; work arrangement to confirm</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Infoparks Kerala detail names a Kochi UI/UX internship and published recruitment inbox. No numeric pay, duration, hours, original date or start deadline. Employer careers page corroborates the company, but does not independently establish this intake.</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alignminds.com/careers/</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>careers@alignminds.com</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment inbox explicitly published for this internship; no message sent</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Indian-brand discovery marketplace</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India; work mode not stated</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Employer-authored LinkedIn detail asks for website redesign, Figma wireframes/mockups and implementation on the live site. Pay, duration, weekly hours, degree criteria and work mode are absent. Relative five-day label is not a verified original posting date. Official company website corroborates marketplace context only.</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Public careers/application route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Consumer mobile applications and design systems</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India; on-site</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Public careers/application route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Services / technology team</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Managed IT and software development</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Infopark Kochi; on-site six months</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Infoparks Kerala advert describes a six-month on-site design internship with Company Standard stipend. Original employer careers page explicitly says no job openings. Current intake is unresolved; no active feed card and no claim the advert itself was definitively closed.</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>https://sparksupport.com/careers/</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>careers@sparksupport.com</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>https://sparksupport.com/careers/</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Published recruitment route; confirm conflicting intake before applying</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Services / technology team</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Digital product and software services</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Kochi; hybrid</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Institutional employer advert explicitly specifies three months unpaid; a possible later salary does not make the internship paid. Excluded from active recommendations.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>https://nuvento.com/</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>anindita.ghosal@nuvento.com</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/nuvento-systems-private-limited/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Application inbox published in this role body; not a salary enquiry already sent</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Creator tools and media products</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India primary focus</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Indexed original employer detail states15,000INR/month gross for2–3months, plus discretionary performance incentives. Direct detail timed out during this pass; evidence is indexed official text. Lower stipend and mainly social/visual/video scope exclude it from the active UX shortlist.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>Public careers/context route; no recruitment email guessed</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Telecommunications and digital products</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka; employer office location</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Original posted7October2026. Despite Junior title, body explicitly asks2–6years and B.Tech/B.E with CS/IT/ECE preferred. Not an internship/fresher recommendation.</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Public careers/context route; no recruitment email guessed</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M154"/>
+  <autoFilter ref="A1:M162"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -35206,6 +39500,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId304"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35217,7 +39527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I295"/>
+  <dimension ref="A1:I321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -47920,8 +52230,1126 @@
       </c>
       <c r="I295" s="2" t="inlineStr"/>
     </row>
+    <row r="296" ht="42" customHeight="1">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; on-site for six months</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Design/HCI student or recent graduate, or a strong self-taught portfolio</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297" ht="42" customHeight="1">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; on-site for six months</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>Strong Figma and a design used by someone who supplied feedback</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298" ht="42" customHeight="1">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; on-site for six months</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>Six months full time on-site in Hyderabad</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299" ht="42" customHeight="1">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; on-site for six months</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Original WR021 application page specifies Hyderabad on-site, six months and application UX/Figma/user testing. Employer displays24August2026. Stipend, deadline and cohort start are unstated; a live form alone does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>Prototype and test flows; contribute components and edge states; usability research, data visualisation and frontend are bonuses</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300" ht="42" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Internship</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Kochi, Kerala, India; work arrangement to confirm</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Infoparks Kerala detail names a Kochi UI/UX internship and published recruitment inbox. No numeric pay, duration, hours, original date or start deadline. Employer careers page corroborates the company, but does not independently establish this intake.</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>Basic understanding of UI/UX principles</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301" ht="42" customHeight="1">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Internship</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Kochi, Kerala, India; work arrangement to confirm</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Infoparks Kerala detail names a Kochi UI/UX internship and published recruitment inbox. No numeric pay, duration, hours, original date or start deadline. Employer careers page corroborates the company, but does not independently establish this intake.</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>Familiarity with Figma, Adobe XD, Sketch or similar tools</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302" ht="42" customHeight="1">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Internship</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Kochi, Kerala, India; work arrangement to confirm</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Infoparks Kerala detail names a Kochi UI/UX internship and published recruitment inbox. No numeric pay, duration, hours, original date or start deadline. Employer careers page corroborates the company, but does not independently establish this intake.</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>Attention to detail, creativity and openness to feedback</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303" ht="42" customHeight="1">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India; work mode not stated</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Employer-authored LinkedIn detail asks for website redesign, Figma wireframes/mockups and implementation on the live site. Pay, duration, weekly hours, degree criteria and work mode are absent. Relative five-day label is not a verified original posting date. Official company website corroborates marketplace context only.</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>Create website wireframes and mockups in Figma</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304" ht="42" customHeight="1">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India; work mode not stated</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Employer-authored LinkedIn detail asks for website redesign, Figma wireframes/mockups and implementation on the live site. Pay, duration, weekly hours, degree criteria and work mode are absent. Relative five-day label is not a verified original posting date. Official company website corroborates marketplace context only.</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>Improve website appearance, usability and flows</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305" ht="42" customHeight="1">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Internship; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India; work mode not stated</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Employer-authored LinkedIn detail asks for website redesign, Figma wireframes/mockups and implementation on the live site. Pay, duration, weekly hours, degree criteria and work mode are absent. Relative five-day label is not a verified original posting date. Official company website corroborates marketplace context only.</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Implement design changes on the live website; exact technology stack unstated</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306" ht="42" customHeight="1">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer (0–1 years) — junior alternative</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India; on-site</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Body asks1+years in product/UI-UX, including internships; title says0–1years: clarify</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307" ht="42" customHeight="1">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer (0–1 years) — junior alternative</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India; on-site</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio may contain academic/personal projects or strong case studies</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308" ht="42" customHeight="1">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer (0–1 years) — junior alternative</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India; on-site</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Figma Auto Layout, components and prototyping; typography and colour fundamentals</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309" ht="42" customHeight="1">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer (0–1 years) — junior alternative</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher; pay/eligibility to confirm</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India; on-site</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail advertises two on-site Ahmedabad openings. Title says0–1years, while body asks1+years of product/UI-UX experience and counts internships; academic/personal portfolio projects accepted. Neither pay nor original posting date is stated. This experience conflict needs clarification.</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>iOS/Android/web interfaces, mentored HIG/Material Design, micro-interactions and developer collaboration</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310" ht="42" customHeight="1">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Intern — conflicting intake evidence</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Infopark Kochi; on-site six months</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/sparksupport-infotech-pvt-ltd/ui-ux-designer-intern-1</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Infoparks Kerala advert describes a six-month on-site design internship with Company Standard stipend. Original employer careers page explicitly says no job openings. Current intake is unresolved; no active feed card and no claim the advert itself was definitively closed.</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Figma wireframes/prototypes; Photoshop/Illustrator visual assets</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311" ht="42" customHeight="1">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Intern — conflicting intake evidence</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Infopark Kochi; on-site six months</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/sparksupport-infotech-pvt-ltd/ui-ux-designer-intern-1</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Infoparks Kerala advert describes a six-month on-site design internship with Company Standard stipend. Original employer careers page explicitly says no job openings. Current intake is unresolved; no active feed card and no claim the advert itself was definitively closed.</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Completed UI/UX certification preferred</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312" ht="42" customHeight="1">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer Intern — conflicting intake evidence</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Infopark Kochi; on-site six months</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/sparksupport-infotech-pvt-ltd/ui-ux-designer-intern-1</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Infoparks Kerala advert describes a six-month on-site design internship with Company Standard stipend. Original employer careers page explicitly says no job openings. Current intake is unresolved; no active feed card and no claim the advert itself was definitively closed.</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Six months on-site in Kochi</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313" ht="42" customHeight="1">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern — explicitly unpaid</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Kochi; hybrid</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/nuvento-systems-private-limited/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Institutional employer advert explicitly specifies three months unpaid; a possible later salary does not make the internship paid. Excluded from active recommendations.</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Relevant study and design portfolio</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314" ht="42" customHeight="1">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern — explicitly unpaid</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Kochi; hybrid</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/nuvento-systems-private-limited/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Institutional employer advert explicitly specifies three months unpaid; a possible later salary does not make the internship paid. Excluded from active recommendations.</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Figma, Adobe XD or Sketch</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315" ht="42" customHeight="1">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern — explicitly unpaid</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Kochi; hybrid</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/nuvento-systems-private-limited/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Institutional employer advert explicitly specifies three months unpaid; a possible later salary does not make the internship paid. Excluded from active recommendations.</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Three-month unpaid internship</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316" ht="42" customHeight="1">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern — below-target stipend</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India primary focus</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Indexed original employer detail states15,000INR/month gross for2–3months, plus discretionary performance incentives. Direct detail timed out during this pass; evidence is indexed official text. Lower stipend and mainly social/visual/video scope exclude it from the active UX shortlist.</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>College students; no full-time experience required</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317" ht="42" customHeight="1">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern — below-target stipend</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India primary focus</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Indexed original employer detail states15,000INR/month gross for2–3months, plus discretionary performance incentives. Direct detail timed out during this pass; evidence is indexed official text. Lower stipend and mainly social/visual/video scope exclude it from the active UX shortlist.</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Social creatives, simple layouts and short video edits</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318" ht="42" customHeight="1">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Design Intern — below-target stipend</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India primary focus</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>https://neuraitech.com/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Indexed original employer detail states15,000INR/month gross for2–3months, plus discretionary performance incentives. Direct detail timed out during this pass; evidence is indexed official text. Lower stipend and mainly social/visual/video scope exclude it from the active UX shortlist.</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Two-to-three-month remote internship</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319" ht="42" customHeight="1">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Junior UI/UX Designer87241396 — experienced requirement</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka; employer office location</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Original posted7October2026. Despite Junior title, body explicitly asks2–6years and B.Tech/B.E with CS/IT/ECE preferred. Not an internship/fresher recommendation.</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Two-to-six years experience</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320" ht="42" customHeight="1">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Junior UI/UX Designer87241396 — experienced requirement</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka; employer office location</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Original posted7October2026. Despite Junior title, body explicitly asks2–6years and B.Tech/B.E with CS/IT/ECE preferred. Not an internship/fresher recommendation.</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>B.Tech/B.E; CS, IT or ECE preferable</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321" ht="42" customHeight="1">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Junior UI/UX Designer87241396 — experienced requirement</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>Company evidence only; not an active internship recommendation</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka; employer office location</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.jio.com/frmjobdescription.aspx?JBTITLE=LXU8057xFyosevktt8ag2w%3D%3D&amp;funcCode=ni4dknKJ6TY%3D&amp;jbID=cpYnSfK8AcND9rzlh25Ugw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Original posted7October2026. Despite Junior title, body explicitly asks2–6years and B.Tech/B.E with CS/IT/ECE preferred. Not an internship/fresher recommendation.</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>Wireframes, user research, responsive interfaces and usability testing</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I295"/>
+  <autoFilter ref="A1:I321"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Unassessed,Met,Partly met,Gap"</formula1>
@@ -48222,6 +53650,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId320"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48233,7 +53687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -48248,7 +53702,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Research snapshot: 2026-10-27</t>
+          <t>Research snapshot: 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -49473,6 +54927,210 @@
       <c r="B103" s="2" t="inlineStr">
         <is>
           <t>2–4 years shipped-product requirement; watchlist-only experienced role, not internship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Travel On Tips</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Exact Indeed Ahmedabad six-month internship advert5–10kINR/month; below Gujarat floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Picktime</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Exact Indeed Hyderabad in-person UI/UX internship12–15kINR/month; below target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Aiva Technology</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Exact Indeed Bengaluru interaction/Figma/React internship15–18kINR/month; below target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>YS Innovations</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Indexed Indeed Coimbatore internship8–10kINR/month; below target. Original detail not separately opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>WebEarl</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Indexed Indeed Ahmedabad up-to8kINR/month; below target; not independently reviewed detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Nuvento Systems</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Institutional advert explicitly unpaid for three months; later salary not current internship pay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>0110 Design</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>UNMANND</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern is mechanical UAV CAD/FEA role with mechanical-engineering background; outside UX/product interface scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Jio</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Junior title conflicts with original2–6years requirement; not a fresher internship alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Neurai Technologies</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official15kINR/month gross2–3months visual/media design internship; below remote target. Direct role timed out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>MailerMen</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Original detail explicitly unpaid;4September posting and27October update remain different dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Sensor Equation</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Indexed relevant remote listing original returned410Gone; not an active lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>IQnext</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Indexed internship original returned410Gone; current intake not inferred from snippet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Triptych Technologies</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Original design internship is social graphics/pitch decks/internal branding; no core UX/product responsibilities established.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Seloriz</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Original remote India six-month internship is physical/industrial product design with CAD and immediate start; not a core UX/product-interface lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Future Interns</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Indexed October2026 cohort explicitly unpaid for one month; not a paid internship match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SparkSupport Infotech</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Institutional internship advert conflicts with official careers no openings. Company-only unresolved evidence, not a confirmed current vacancy.</t>
         </is>
       </c>
     </row>

--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$418</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$512</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$162</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$162</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$343</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z66"/>
+  <dimension ref="A1:Z68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Confirm current intake, stipend, work arrangement and eligibility with employer before applying.</t>
+          <t>Confirm current intake,1–3year experience requirement, joining eligibility, office arrangement and INR4–6lakh annual salary. Current board date display may be a repost, not a new original vacancy.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
@@ -6802,8 +6802,200 @@
       </c>
       <c r="Z66" s="2" t="inlineStr"/>
     </row>
+    <row r="67" ht="95" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Fuworx Innovations</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer — Intern</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; hybrid</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Obtain the exact job description and active application route; confirm fixed monthly paid stipend, duration, hours, student eligibility and joining window.</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>Published employer route; manual review</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>Original Open Position list explicitly names UI/UX Designer, Intern and Hybrid (Hyderabad). No numeric stipend, duration, hours, degree criteria or publication/start date. Apply controls do not expose a separate job-detail URL in the reviewed page; a general resume form is available. General info inbox is not a verified recruiting address.</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid Hyderabad internship as listed; detailed skills and degree criteria not published</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>Original publication date unstated; newly researched is not necessarily newly posted</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="95" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — older advert; intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru, Karnataka, India; full-time office</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Confirm a renewed intake and current monthly stipend in writing; verify three-month duration, start window and application contact before preparing an application.</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Job board</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>abeljohnsunil@gmail.com</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>Email explicitly published by the YDI advert author; confirm current intake before use</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>UX research, data analysis and independent task ownership; Strong Figma and design-system execution; AI/prompting awareness and some frontend understanding; Graphic or motion interest; Claude Code and Adobe Creative Suite are bonuses</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>13March2026 on YDI advert; employer original posting date not independently established</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z66"/>
+  <autoFilter ref="A1:Z68"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
@@ -6940,6 +7132,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6951,7 +7147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F418"/>
+  <dimension ref="A1:F512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20226,8 +20422,3016 @@
         </is>
       </c>
     </row>
+    <row r="419" ht="42" customHeight="1">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>Fuworx Innovations</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Original Open Position list explicitly names UI/UX Designer, Intern and Hybrid (Hyderabad). No numeric stipend, duration, hours, degree criteria or publication/start date. Apply controls do not expose a separate job-detail URL in the reviewed page; a general resume form is available. General info inbox is not a verified recruiting address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="42" customHeight="1">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="42" customHeight="1">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="42" customHeight="1">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="42" customHeight="1">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="42" customHeight="1">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>BThree Design Agency</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-bthree-design-agency-4473077505</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="42" customHeight="1">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Wint Wealth</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sruthisivakumar_product-design-intern-wint-wealth-activity-7515659430051426304-tqUQ</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="42" customHeight="1">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>Hevo Data</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/hevodata/433ffdef-3125-48ed-a131-52c697c321ee</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="42" customHeight="1">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>RevRag AI</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="42" customHeight="1">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Chiblu</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="42" customHeight="1">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>NeuralPath Technologies</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="42" customHeight="1">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>KRMR Solutions</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>https://krmrsolutions.com/careers/design-intern</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="42" customHeight="1">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Zavio</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="42" customHeight="1">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Gnixar Academy</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jobleads.com/in/job/product-design-intern--india--e24abd61a6654a91f9a3af3bab3db8da5</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="42" customHeight="1">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="42" customHeight="1">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Techolution</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="42" customHeight="1">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="42" customHeight="1">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>Green Ping Solutions</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=157d2635900933e2</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="42" customHeight="1">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="42" customHeight="1">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Fetched response is empty/JavaScript-only; current role body/intake unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="42" customHeight="1">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="42" customHeight="1">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="42" customHeight="1">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>project44</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="42" customHeight="1">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Frappe</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>https://frappe.io/careers/open-positions/designer</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="42" customHeight="1">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Juno</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="42" customHeight="1">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="42" customHeight="1">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Ungrammary</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="42" customHeight="1">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Nonlinear</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>https://nonlinear.in/careers</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="42" customHeight="1">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Octet Design Studio</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>https://octet.design/careers/</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="42" customHeight="1">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Octet Design Studio</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>https://octet.design/careers/</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="42" customHeight="1">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>SuperKalam</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="42" customHeight="1">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Coulomb AI</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="42" customHeight="1">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Icogz</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="42" customHeight="1">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>VictorFlow</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="42" customHeight="1">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Gunadhya Software Solutions</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="42" customHeight="1">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Qoruz</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="42" customHeight="1">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>Energise.pro</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="42" customHeight="1">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="42" customHeight="1">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Fetched response is empty/JavaScript-only; current role body/intake unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="42" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="42" customHeight="1">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="42" customHeight="1">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="42" customHeight="1">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="42" customHeight="1">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Fetched response is empty/JavaScript-only; current role body/intake unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="42" customHeight="1">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="42" customHeight="1">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="42" customHeight="1">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="42" customHeight="1">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Payzoplus</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.payzoplus.com/company/careers/design</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="42" customHeight="1">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>DECTIFY</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.dectify.in/careers/details/DTCI-S191348/ui-ux-designer/</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="42" customHeight="1">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>CollabOP</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.collabop.com/careers/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="42" customHeight="1">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/lokal-app/j/CB2EDD7186</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>shell</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Fetched response is empty/JavaScript-only; current role body/intake unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="42" customHeight="1">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Aeron Systems</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeronsystems.com/careers/design-intern-visuals-ui-ux/</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="42" customHeight="1">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Androcid</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>https://androcid.freshteam.com/jobs/_KvFSyux1O8C/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="42" customHeight="1">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>SutharTech</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>https://suthartech.com/internships/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="42" customHeight="1">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Nihar / Creuto</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.niharrout.com/work-with-me/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="42" customHeight="1">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>ATRISI</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>https://atrisi.org/collaborate/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="42" customHeight="1">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Toddle</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>https://toddle.keka.com/careers/jobdetails/36030</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="42" customHeight="1">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Toddle</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>https://toddle.keka.com/careers/jobdetails/85790</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="42" customHeight="1">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Mojro</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ux-design-research-intern-at-mojro-4477515785</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="42" customHeight="1">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>LeadSquared</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=af19b01b18d49a36</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="42" customHeight="1">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Krevok</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>https://krevok.com/careers</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="42" customHeight="1">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="42" customHeight="1">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="42" customHeight="1">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="42" customHeight="1">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>Public primary fetched; fetch alone does not reconfirm every requirement or current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="42" customHeight="1">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="42" customHeight="1">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="42" customHeight="1">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>BThree Design Agency</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-bthree-design-agency-4473077505</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="42" customHeight="1">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="42" customHeight="1">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>SutharTech</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>https://suthartech.com/internships/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="42" customHeight="1">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="42" customHeight="1">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="42" customHeight="1">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>project44</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="42" customHeight="1">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>Qoruz</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Role terms reviewed; prior pay units, requirements and original dates retained. Current intake/joining eligibility still requires confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="42" customHeight="1">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>project44</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.project44.com/company/careers/open-roles/job/?detail=8101750</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>Original employer detail matches tracked Greenhouse requisition8101750; six-month Bengaluru role. Genuine additionalSource without duplicate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="42" customHeight="1">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs/8483276-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="42" customHeight="1">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs/8495367-ui-design-intern</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>Original UI Design Intern8495367 explicitly inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="42" customHeight="1">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLScLOwa6O_McDXujdHTrDAmGE-MTUgyVhcUMI2_1h3BVWyhTDA/viewform</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="42" customHeight="1">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-specific2028 graduation and returning-enrollment requirement; original detail unavailable, indexed official evidence only. Not a general internship recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="42" customHeight="1">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Arventiq Labs</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>https://arventiqlabs.com/careers</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="42" customHeight="1">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>3Di Systems</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3disystems.com/careers-at-3di/</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>Careers landing page has a Junior Product Designer/Mumbai teaser and placeholder apply# link. Linked Current Job Openings has six other roles, no design detail. Placeholder content is not a confirmed new junior vacancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="42" customHeight="1">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>Unosecur</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.workable.com/view/hi44WzLeFfNqDRnyDhXD2R/product-design-intern-in-bengaluru-at-unosecur</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>Specific indexed Workable Product Design Intern detail returns410Gone. Official careers corroborates identity-security company; linked public ATS is a blank JavaScript response. No renewed design intake established; no claim all company hiring closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="42" customHeight="1">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="42" customHeight="1">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>Grovyn</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/3834773-ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>Exact original Wellfound detail410Gone; index freshness does not establish current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="42" customHeight="1">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>Feelin’s App</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4045278-product-designer-intern</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>Exact original Wellfound detail410Gone; not a new active role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="42" customHeight="1">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>Metapercept Technology Services</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/q-internship-ux-designer-l-pune%2C-maharashtra-jobs.html</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>Indeed category/detail extract5–7.5k/month header,7.5k body; below target. September category date/cached extract is not fresh employer publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="42" customHeight="1">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>SOR Group</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Graphic-Design-UI-UX-Intern-Hyderabad-SOR-Group-rToBMsWw</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>Indexed matching Cutshort advert11.5–12k/month Hyderabad below target; exact opened extract did not independently re-establish salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="42" customHeight="1">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Raptee.HV</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.weekday.works/raptee-energy-ui%2Fux-designer---intern</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>excluded-or-unresolved</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>Indexed mirror1.8lakh/year, another mirror15k/month; no employer-current stipend confirmed and both below target. Keep units/source limits; do not convert annual header to a verified stipend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="42" customHeight="1">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>Arventiq Labs</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>https://arventiq-reviews-api.arventiqlabs.com/v1/jobs</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="42" customHeight="1">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>Original index has three other roles; exact design role closure checked separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="42" customHeight="1">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>Original role body/careers index says open but linked form explicitly closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="42" customHeight="1">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>3Di Systems</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3disystems.com/current-job-openings/</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>Current jobs list six other roles, no design detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="42" customHeight="1">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>Unosecur</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unosecur.com/careers</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>Official company identity-security careers context; current design intake not confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="42" customHeight="1">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Young Designers India</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:42:32+00:00</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F418"/>
+  <autoFilter ref="A1:F512"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20300,22 +23504,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Accessible category and sample search</t>
+          <t>Accessible category and targeted query</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>YC design category opened and India internship query searched. Cityfurnish indexed UI/UX internship is Gurugram with anomalous10–15INR/month header, not a qualifying role. No new suitable employer-verified YC internship added.</t>
+          <t>YC design category and India intern queries checked. Cityfurnish Gurugram/low-or-anomalous pay and US-only Flick motion/graphic role do not meet this shortlist. No new suitable exact YC role verified.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Category date October2026 does not date individual roles. Existing SuperKalam/Coulomb2024 origins and compensation-unit conflicts retained; no renewed intake inferred.</t>
+          <t>October category label is not a date on each job. SuperKalam/Coulomb2024 originals and compensation conflicts retained on hold.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -20333,22 +23537,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Inaccessible tool route / indexed sample</t>
+          <t>Inaccessible original route / search sample</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Explicit Work at a Startup India-design search attempted; jobs?roles=designer original inaccessible through research tool. No new suitable role verified.</t>
+          <t>Work at a Startup design-intern India search attempted; jobs?roles=designer inaccessible through tool. No suitable new original verified.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>No logged-in access implied, no source quota and no duplicate YC card.</t>
+          <t>No logged-in access or complete inventory claim; YC duplicates are not counted as additional roles.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -20366,22 +23570,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Public HN API top-level scan</t>
+          <t>Public API top-level scan</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>October2026 thread49922569 public API:319top-level records fetched;21 raw-text designer/UX/UI-term matches. Reviewed matching headings/geography/seniority; no independently verified suitable new India junior/intern vacancy. Earlier266top-level figure belongs to a prior snapshot.</t>
+          <t>October2026 HN thread49922569:319top-level records fetched,21raw-text designer/UX/UI matches screened by company heading/geography/seniority; no independently verified suitable new India junior/intern role. Previous266 snapshot retained historically.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Term filter is a screening aid, not every linked employer JD. Raw-text counts differ from previous normalized-text method; no direct trend inferred. Trustworthy part-time pay/India eligibility unspecified; US/BayArea roles and senior postings unsuitable.</t>
+          <t>Same raw-term method as28October, not every linked employer JD. Engineering/senior/US/Europe posts and unspecified part-time engagement not promoted. No no-hiring conclusion for entire platform.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -20432,27 +23636,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Accessible exact details and targeted search</t>
+          <t>Accessible retained originals / cached category sample</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Three new exact Indeed details reviewed: Travel On Tips5–10k/month, Picktime12–15k/month, Aiva15–18k/month; all below target. Existing active Indeed primaries fetched. No new suitable Indeed card; salary minima are not replaced by upper endpoints.</t>
+          <t>All prior Indeed primary URLs attempted; public category searches across Gujarat/Pune/Hyderabad and fresher design. Metapercept5–7.5k/month below target; retained Techolution same role, no duplicate new card.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Sample search/detail checks, not every Indeed job. Indexed YS/WebEarl low-pay examples are labelled indexed, not newly verified originals.</t>
+          <t>Indeed category URLs returned older September extracts despite newer search snippets; do not claim current inventory or employer publication from category dates. No new suitable Indeed-primary lead.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Kixar: INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.; Melento: Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.; Redliner: Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.; BiCSoM: Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.; We-intern: Direct Indeed detail INR10,000–20,000/month remote, below target.; Balusen Technologies: Original expiry banner; retained archived ID.; PV Labs: Exact Indeed detail3–5k stipend/up-to5k per month; four-week product-image/e-commerce-visual role, below pay and outside core UX.; Travel On Tips: Exact Indeed Ahmedabad six-month internship advert5–10kINR/month; below Gujarat floor.; Picktime: Exact Indeed Hyderabad in-person UI/UX internship12–15kINR/month; below target.; Aiva Technology: Exact Indeed Bengaluru interaction/Figma/React internship15–18kINR/month; below target.; YS Innovations: Indexed Indeed Coimbatore internship8–10kINR/month; below target. Original detail not separately opened.; WebEarl: Indexed Indeed Ahmedabad up-to8kINR/month; below target; not independently reviewed detail.</t>
+          <t>Kixar: INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.; Melento: Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.; Redliner: Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.; BiCSoM: Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.; We-intern: Direct Indeed detail INR10,000–20,000/month remote, below target.; Balusen Technologies: Original expiry banner; retained archived ID.; PV Labs: Exact Indeed detail3–5k stipend/up-to5k per month; four-week product-image/e-commerce-visual role, below pay and outside core UX.; Travel On Tips: Exact Indeed Ahmedabad six-month internship advert5–10kINR/month; below Gujarat floor.; Picktime: Exact Indeed Hyderabad in-person UI/UX internship12–15kINR/month; below target.; Aiva Technology: Exact Indeed Bengaluru interaction/Figma/React internship15–18kINR/month; below target.; YS Innovations: Indexed Indeed Coimbatore internship8–10kINR/month; below target. Original detail not separately opened.; WebEarl: Indexed Indeed Ahmedabad up-to8kINR/month; below target; not independently reviewed detail.; Metapercept Technology Services: Indeed category/detail extract5–7.5k/month header,7.5k body; below target. September category date/cached extract is not fresh employer publication.</t>
         </is>
       </c>
     </row>
@@ -20469,22 +23673,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Blocked by robots.txt</t>
+          <t>Restricted route / prior robots limits</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Explicit Naukri-domain discovery returned non-retryable robots restriction; original UI/UX intern search inaccessible. Retained Keyideas primary responded with an empty body, not a verified vacancy.</t>
+          <t>Explicit Naukri UI/UX-intern queries attempted. Direct search route unavailable; retained Keyideas primary body empty. No independently verified new Naukri job.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>No authenticated account, CAPTCHA bypass or repeated restricted-domain attempts. Indexed Naukri-associated Miko mirror says unpaid, while another mirror10–12k has unclear period; no pay or vacancy promoted from these conflicts.</t>
+          <t>Prior robots restrictions remain caveated; current empty response is not verified vacancy content. No account access, CAPTCHA bypass or authenticated session implied.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -20506,27 +23710,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Accessible retained detail and indexed search</t>
+          <t>Accessible retained detail / sample discovery</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Cutshort junior/UIUX search repeated; retained Qoruz detail still lists1–3years and4–6lakhINR/year. No new suitable internship found in sample.</t>
+          <t>Qoruz current detail still1–3years and4–6lakhINR/year. Current board shows28October, while prior record observed16October/index7October; original date fields preserved, date observation labelled separately. SOR indexed11.5–12k/month below target.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Annual salary stays annual. Ungrammary10–12k/month fellowship caveat retained, not a qualifying match. Search category counts are not an inventory review.</t>
+          <t>Changing board/repost dates are not verified employer original publication. Ungrammary10–12k/month below-target fellowship and annual conflict retained.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>AMPM Network: ₹10–15k/mo, belowtarget; recruiterinactive; SDS softwares: ₹7–15k/mo; no current full-time students; immediatejoiners; Synorus: Original Cutshort range INR0–5,000/month, dated29November2025; below target, potentially unpaid lower end.</t>
+          <t>AMPM Network: ₹10–15k/mo, belowtarget; recruiterinactive; SDS softwares: ₹7–15k/mo; no current full-time students; immediatejoiners; Synorus: Original Cutshort range INR0–5,000/month, dated29November2025; below target, potentially unpaid lower end.; SOR Group: Indexed matching Cutshort advert11.5–12k/month Hyderabad below target; exact opened extract did not independently re-establish salary.</t>
         </is>
       </c>
     </row>
@@ -20543,22 +23747,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>JavaScript / cookie-limited route</t>
+          <t>Cookie/JavaScript-limited route</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Explicit Unstop internship/UIUX search attempted. Original internships page returns Please Wait / Cookies Disabled without readable role inventory. No new role verified.</t>
+          <t>Unstop UX-intern search attempted; original internships page returns Please Wait/Cookies Disabled and no readable inventory. No suitable new role verified.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>No cookie/access-control bypass; generic search results and other-board mirrors do not establish an Unstop original.</t>
+          <t>No access bypass. Non-Unstop results from broad search are not claimed as original Unstop postings.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -20580,22 +23784,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Restricted / robots-blocked</t>
+          <t>Restricted original route</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Explicit Internshala product-design30k query and original UI/UX internship route attempted; original restricted. Mirrored low-pay/unpaid examples did not produce a qualifying new role.</t>
+          <t>Explicit Internshala30k design queries and original UI/UX-internships page attempted; direct page restricted. Sample mirrors show low pay or start windows ending in November; no new employer-corroborated qualifying role.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>No authenticated session implied. Original posting/start dates cannot be established from fresh mirror crawl labels.</t>
+          <t>No signed-in account implied. Mirror ages and closing/start windows are labelled mirror evidence, not independently original employer dates.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -20613,22 +23817,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>520 error / limited indexed discovery</t>
+          <t>520 error / indexed sample search</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Explicit Instahyre design-intern query searched; original home returned520 through research tool. No exact suitable new role verified.</t>
+          <t>Explicit Instahyre UX-intern query attempted; original home520. No exact suitable new role verified.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Do not equate public search with signed-in access or complete job inventory.</t>
+          <t>Tool access does not establish a linked account or complete inventory. No bypass or source quota.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -20646,27 +23850,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Indexed discovery; exact samples gone</t>
+          <t>Indexed discovery / exact detail410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Wellfound search found IQnext and Sensor Equation; both exact original details410Gone. Autumn Tech Worx indexed10–15k and other unconfirmed snippets not promoted.</t>
+          <t>Wellfound India design-intern searches found Grovyn and Feelin’s App; both exact details410Gone. Cravv indexed20k/month remains below target.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Fresh crawl of a search snippet does not override410 original. No new qualifying Wellfound vacancy.</t>
+          <t>Fresh snippet/crawl dates do not revive removed details. Prior closed/excluded records retained without duplicates.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid; BetterStory: INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.; Rootcode: Original Wellfound detail returned410 Gone.; NoobSync Innovations: Explicit no fixed stipend, performance-only compensation and20hours/week; no guaranteed monthly floor.; IQnext: Indexed internship original returned410Gone; current intake not inferred from snippet.; Sensor Equation: Indexed relevant remote listing original returned410Gone; not an active lead.</t>
+          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid; BetterStory: INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.; Rootcode: Original Wellfound detail returned410 Gone.; NoobSync Innovations: Explicit no fixed stipend, performance-only compensation and20hours/week; no guaranteed monthly floor.; IQnext: Indexed internship original returned410Gone; current intake not inferred from snippet.; Sensor Equation: Indexed relevant remote listing original returned410Gone; not an active lead.; Grovyn: Exact original Wellfound detail410Gone; index freshness does not establish current intake.; Feelin’s App: Exact original Wellfound detail410Gone; not a new active role.</t>
         </is>
       </c>
     </row>
@@ -20683,22 +23887,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Accessible public category / targeted search</t>
+          <t>Accessible descriptive category / discovery sample</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>India entry-level design and UX/intern categories searched/opened. Entry-level India page showed descriptive/sign-up content without readable qualifying cards in reviewed extract. Existing Energise detail remains accessible.</t>
+          <t>Himalayas India UX and intern-design searches surfaced listings; original intern category extract contained descriptive/sign-up content rather than readable qualifying cards. Cloud Counselage indexed junior role restricts Kerala/Tamil Nadu candidates; no suitable exact original verified.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Global intern examples may be Poland/other-country-only. Energise Job expired? is a report button, not a closure notice. No new India-eligible internship independently verified.</t>
+          <t>No claim site has zero roles. Existing Energise Job expired? remains a reporting button, not a closure notice. Pay/start/location eligibility not inferred from remote labels.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -20720,22 +23924,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Accessible public category sample</t>
+          <t>Accessible category / targeted search</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>We Work Remotely design category opened and junior-product query searched. Reviewed public extract did not establish an India-eligible junior/intern role.</t>
+          <t>WWR design category and India-junior queries checked; listing index surfaced LooseGrip part-time junior contract with worldwide label, but no exact UX scope, current pay unit and India engagement verified. No new recommended role.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Category/sample only; senior Poland/Europe or generic global labels do not establish India eligibility.</t>
+          <t>Category/index sample only; world-wide label alone does not establish applicant or contract eligibility.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -20757,22 +23961,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Accessible public category sample</t>
+          <t>Accessible category / sample query</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Remote OK design category opened and India-intern query searched. No suitable exact internship/junior role established from reviewed sample.</t>
+          <t>Remote OK design category and India-design-intern search attempted. No suitable new exact UX internship or junior vacancy verified in reviewed sample.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Location filters and generic page taxonomy are not a vacancy or India permission. No claim of full inventory scraping.</t>
+          <t>Country filters and category taxonomy are not vacancy/eligibility evidence; no full-inventory scraping claimed.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -20794,22 +23998,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Accessible public category / limited sample</t>
+          <t>Accessible category / limited public sample</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Remotive design category opened and India-UX-intern query searched. No suitable exact new role verified.</t>
+          <t>Remotive design page and India-UX-junior queries checked; no suitable new exact original verified.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Public category and sign-in/unlock boundaries limit coverage; no paid-access bypass and no complete-inventory claim.</t>
+          <t>Public samples and unlock/sign-in boundaries limit coverage; paid access not bypassed.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -20831,22 +24035,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Accessible category / sample search</t>
+          <t>Accessible category / sample query</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Remote.co design category and India-junior search checked; reviewed sample includes senior graphic design, not a suitable new internship.</t>
+          <t>Remote.co design category and India-junior queries checked; no suitable new exact India junior/intern UX role verified.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Remote generally does not imply India eligibility. No new role from landing-page or generic descriptions alone.</t>
+          <t>Generic remote descriptions and senior/graphic roles are not active India internship evidence.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -20868,7 +24072,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -20878,12 +24082,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Working Nomads entry-level design page opened and design-intern search attempted. Page exposed descriptive content/navigation without readable qualifying job cards in this extract.</t>
+          <t>Working Nomads entry-level design category and design-intern India query checked. Extract contained descriptive navigation without readable qualifying cards.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>No claim that the site has zero jobs; only this sample yielded no independently verified role.</t>
+          <t>Not a claim board has zero jobs; no complete inventory or current employer intake established.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -20901,22 +24105,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Accessible directory; city route unavailable</t>
+          <t>Accessible directory; deeper route unresolved</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>StartupMap.in home opened:startup counts and city/sector/hiring filters visible. Hyderabad city route inaccessible via research tool.</t>
+          <t>StartupMap.in public home provides city/sector/hiring filters and3070startup directory context. Attempted Chennai link did not resolve reliably through research tool; no company/role derived from that click.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Directory presence, funding or hiring filter is employer discovery only. No vacancy inferred and no map-derived personal-fit claim.</t>
+          <t>Directory/filter counts are discovery only, not active vacancies. Deeper city/company discovery remained unverified in this sample.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -20934,22 +24138,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Indexed public directory sample</t>
+          <t>Original page timeout</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>StartupBlink India explicit discovery query returned October2026 company ranking/context, including pharmacy/product companies. No eligible exact UX internship established from ranking.</t>
+          <t>StartupBlink India original directory opened but timed out in this pass; no newly verified company or role derived.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Funding/traffic/employee rank is not an opening. Existing researched product targets retained; no new role claimed from directory alone.</t>
+          <t>Previous indexed directory evidence retained in history; no claim current ranking or full directory accessed today.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -20967,22 +24171,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Indexed directory and methodology sample</t>
+          <t>Accessible directory map/context</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Indian Startup Map India/design pages examined in search extracts:August2026 government-register snapshot, with explicit dormant-company and location-precision limits.</t>
+          <t>Indian Startup Map public map opened:funding/scheme register context with JavaScript map and location/methodology limits. No exact current internship verified from register.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Registration/funding is not current operation or hiring. Paid reports not accessed; no vacancy derived from directory counts.</t>
+          <t>Registration/funding/location signal is not hiring or continued operation. No paid report or private data accessed.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -21000,22 +24204,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Indexed public directory sample</t>
+          <t>Accessible public directory shell</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>IndianStartupsMap home/about/rules surfaced in discovery search;648companies and16cities reported by site snapshot.</t>
+          <t>IndianStartupsMap home opened with648-company snapshot and client-rendered map/grid. No exact current hiring derived.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>User submissions/map positions are company context only, not independently verified employer roles. No exhaustive employer checks claimed.</t>
+          <t>Submitted company profiles and generic hiring filters are not vacancy evidence; no exhaustive company inventory review.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -21033,27 +24237,27 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Original role review and whole-board URL maintenance</t>
+          <t>Original details, application routes and primary maintenance</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>New WATER WR021 six-month Hyderabad UX internship and Pixster Ahmedabad junior product role: pay absent, both held. Menstrupedia25–30k/month and existing annual Moonfire pay rechecked; Gravity ATS cross-post deduplicated. All59 active primary URLs attempted:52 public responses,7 robots/access blocks; four fetched bodies were shells.</t>
+          <t>Fuworx explicitly lists hybrid Hyderabad UI/UX internship; pay/JD absent, held. Original HugoHub UX/UI inactive; Nngtw open index conflicts with closed application form. Arventiq normal public feed has four non-design roles;3Di current index six other roles versus placeholder design teaser. project44 exact8101750 official cross-post added.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>A fetched page is not renewed intake. Two blocked LinkedIn primaries separately readable through public research. Nine original-primary body checks remain unresolved (five blocked plus four shells). No reliable new closure established; two archived records retained.</t>
+          <t>All63 active primary URLs attempted:55 responses/eight collector blocks/four shells. Three blocked LinkedIn bodies separately readable; nine original-primary body checks remain unresolved. No existing active lead newly closed by reliable evidence. Application forms inspected read-only; none submitted.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Nuvento Systems: Institutional advert explicitly unpaid for three months; later salary not current internship pay.; Jio: Junior title conflicts with original2–6years requirement; not a fresher internship alternative.; Neurai Technologies: Indexed official15kINR/month gross2–3months visual/media design internship; below remote target. Direct role timed out.; 0110 Design: Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.</t>
+          <t>Nuvento Systems: Institutional advert explicitly unpaid for three months; later salary not current internship pay.; Jio: Junior title conflicts with original2–6years requirement; not a fresher internship alternative.; Neurai Technologies: Indexed official15kINR/month gross2–3months visual/media design internship; below remote target. Direct role timed out.; 0110 Design: Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.; HugoHub: Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.; Nngtw Studio: Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.; Arventiq Labs: Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.; 3Di Systems: Careers landing page has a Junior Product Designer/Mumbai teaser and placeholder apply# link. Linked Current Job Openings has six other roles, no design detail. Placeholder content is not a confirmed new junior vacancy.</t>
         </is>
       </c>
     </row>
@@ -21070,22 +24274,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>403 Forbidden / indexed sample</t>
+          <t>403 Forbidden / limited public search</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Explicit X design-intern India search and original search URL attempted; original403. Indexed results did not establish a suitable new original UX hiring post.</t>
+          <t>Explicit X product-design-intern and design-internship India/remote queries searched; original X search inaccessible403. No suitable original social hiring post newly verified.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>No original post freshness verified and no claim of authenticated access. Art Deco visual/motion mirror is not a verified UX vacancy; existing Wint/BThree evidence retained.</t>
+          <t>Search snippets are not verified original access or freshness. Existing X source histories preserved; no quota vacancy invented.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -21103,22 +24307,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Accessible employer-authored sample</t>
+          <t>Retained employer-authored terms / sampled discovery</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>One new on-hold NueFind website UX/implementation internship, Bengaluru. ShramikSathi30k/month remote India and More Retail35k/month Bengaluru descriptions remain readable. 0110 deferred/equity and UNMANND mechanical CAD roles excluded.</t>
+          <t>ShramikSathi30k/month remote,More Retail35k/month Bengaluru and BThree20–25k/month/immediate descriptions rechecked. Antropi exact old URL redirects to generic industrial-design results; no current role inferred.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Pay/start/hours absent on NueFind; relative age is not original publication date. No sign-in, application or employer contact.</t>
+          <t>Google/YouTube2028-cohort and closed/older/low-pay discoveries are not new eligible cards. Relative ages do not establish original publication or start eligibility.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -21140,27 +24344,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Targeted startup/company role checks</t>
+          <t>Targeted startup/company and live route checks</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Product/startup sample includes WATER, NueFind and existing Gravity. Gravity matching Growhire requisition added as additionalSources, not another card. Neurai indexed15k and 0110 deferred/equity excluded.</t>
+          <t>Fuworx and older Paradigm are newly researched on hold. HugoHub35k anonymous-board copy rejected after original inactive. Nngtw open label rejected for active recommendation after linked form explicitly closed. Strom original unpaid; Unosecur exact board410.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Startup status alone does not establish compensation, active intake or India permission; generic hiring signals remain separate from vacancies.</t>
+          <t>Company discovery, funding and startup reputation do not establish salary or eligibility. Existing SutharTech December cohort rechecked; no new guaranteed monthly-pay match.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Superteams.ai: Original role explicitly closed despite its listing on the general careers index.; Leap: Original ATS host/detail returns a site-not-found page; indexed internship not confirmed current.; LeelaRam Technologies: Original stipend10–15k/month in Mumbai, below target.; GoPratle: Original header2–5k and final-year/fresher restriction; not a qualifying stipend match.; FLIP: Original410 Gone.; frover: Original410 Gone.; Mowka: Original410 Gone.; eLeoRex Technologies: Original1October2026 deadline passed; not a current internship recommendation.; Figr: Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.; Grexa AI: Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.; Cravv: Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.</t>
+          <t>Superteams.ai: Original role explicitly closed despite its listing on the general careers index.; Leap: Original ATS host/detail returns a site-not-found page; indexed internship not confirmed current.; LeelaRam Technologies: Original stipend10–15k/month in Mumbai, below target.; GoPratle: Original header2–5k and final-year/fresher restriction; not a qualifying stipend match.; FLIP: Original410 Gone.; frover: Original410 Gone.; Mowka: Original410 Gone.; eLeoRex Technologies: Original1October2026 deadline passed; not a current internship recommendation.; Figr: Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.; Grexa AI: Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.; Cravv: Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.; Nngtw Studio: Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.; Strom Bot: Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.; Unosecur: Specific indexed Workable Product Design Intern detail returns410Gone. Official careers corroborates identity-security company; linked public ATS is a blank JavaScript response. No renewed design intake established; no claim all company hiring closed.</t>
         </is>
       </c>
     </row>
@@ -21177,22 +24381,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Selected public design-board detail and employer corroboration</t>
+          <t>Accessible dated advert / employer inaccessible</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Sola dated4August2026 six-month Bengaluru advert checked. Header30–50k and body up-to50k do not establish a guaranteed minimum. Current official careers has only two engineering jobs; company-only indexed lead, no active feed card.</t>
+          <t>Paradigm YDI13March2026 advert researched as older on-hold lead:three months office Bengaluru,body30–35k/month versus header30–50k. Historical range recorded only in payBenchmark; listing monthly pay fields null.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Selected details only; board range is not a current employer offer or renewed intake. Application shortlink unavailable through research tool.</t>
+          <t>Employer site inaccessible, current intake/pay unknown; board publication date is not independently verified employer original date. Old advert must not be called freshly posted.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -21283,7 +24487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -29057,8 +32261,447 @@
         </is>
       </c>
     </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Fuworx Innovations</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Editable Possible preference/fit suggestion for digital engineering and transformation. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="2" t="n"/>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>Current fixed stipend not stated; do not infer from company reputation.</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Editable Possible preference/fit suggestion for sports motion-analysis software. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Historical advertised stipend on job board</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Low for current intake/pay</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Historical YDI body30–35k/month versus header30–50k; no current employer-confirmed compensation.</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>https://paradigmsports.app/</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub / Atlas Consolidated</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Editable Workable preference/fit suggestion for modular banking platform. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>No verified current stipend. Anonymous board35k/month claim cannot establish a current employer offer.</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Editable Possible preference/fit suggestion for games and interactive applications. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="n"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>No stipend stated. Certificate/mentorship are not evidence of pay.</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/careers</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Editable Dream preference/fit suggestion for video platforms and creator experiences. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="n"/>
+      <c r="G167" s="2" t="n"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Salary undisclosed; no current or historical numeric range inferred.</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Arventiq Labs</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Editable Possible preference/fit suggestion for education platforms and cybersecurity tools. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX stipend/fees unknown. Do not conflate a separate fee-based SOC programme with design employment.</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>https://arventiqlabs.com/careers</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>3Di Systems</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Editable Workable preference/fit suggestion for civic technology and community software. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>No design-role salary verified.</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.3disystems.com/current-job-openings/</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Unosecur</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Editable Workable preference/fit suggestion for identity security for human and ai identities. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="2" t="n"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>No current stipend verified; mirror salary/experience metadata not promoted.</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.unosecur.com/careers</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Editable Possible preference/fit suggestion for discord management dashboards and community tools. Not a hiring probability, confirmed vacancy or offer.</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="n"/>
+      <c r="G171" s="2" t="n"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Explicit unpaid/volunteer header; conditional body wording is not a guaranteed stipend.</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M162"/>
+  <autoFilter ref="A1:M171"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Dream,Workable,Possible"</formula1>
@@ -29246,6 +32889,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId191"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29257,7 +32910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39209,8 +42862,555 @@
         </is>
       </c>
     </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Fuworx Innovations</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Services / technology team</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Digital engineering and transformation</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; hybrid</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Original Open Position list explicitly names UI/UX Designer, Intern and Hybrid (Hyderabad). No numeric stipend, duration, hours, degree criteria or publication/start date. Apply controls do not expose a separate job-detail URL in the reviewed page; a general resume form is available. General info inbox is not a verified recruiting address.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>info@fuworx.com</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Published general resume form; email is general company contact, not a stated recruitment inbox</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Sports motion-analysis software</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru, Karnataka, India; full-time office</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>https://paradigmsports.app/</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>abeljohnsunil@gmail.com</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Application email explicitly published by dated advert author; current recruitment activity unconfirmed</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub / Atlas Consolidated</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Modular banking platform</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad; historical internships on-site for six months</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Public careers route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Games and interactive applications</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>India remote for advertised internship</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/careers</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>hello@nngtw.studio</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>General business/partnership contact on official home, not verified recruitment email</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Video platforms and creator experiences</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; specific summer2027 cohort</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official YouTube summer2027 internship specifies graduation in2028 and returning full-time enrollment. Application window27October–4November2026. Direct employer detail unavailable through research tool; recorded as cohort-specific directory evidence, not a generally eligible internship recommendation.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Public careers route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Arventiq Labs</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Education platforms and cybersecurity tools</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; on-site/hybrid varies by role</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>https://arventiqlabs.com/careers</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>info@arventiqlabs.com</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>https://arventiqlabs.com/careers</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>General company contact; not a verified UI/UX recruitment route</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>3Di Systems</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Civic technology and community software</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai/Navi Mumbai and Pune; role-specific work arrangement required</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Careers landing page has a Junior Product Designer/Mumbai teaser and placeholder apply# link. Linked Current Job Openings has six other roles, no design detail. Placeholder content is not a confirmed new junior vacancy.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.3disystems.com/current-job-openings/</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.3disystems.com/current-job-openings/</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Public careers route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Unosecur</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Identity security for human and AI identities</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Historical internship Bengaluru office; current arrangement unverified</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Specific indexed Workable Product Design Intern detail returns410Gone. Official careers corroborates identity-security company; linked public ATS is a blank JavaScript response. No renewed design intake established; no claim all company hiring closed.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.unosecur.com/careers</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.unosecur.com/careers</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Public careers route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Discord management dashboards and community tools</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Remote; published2025/2026 computer-stream graduate restriction</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Public careers route; no recruitment email inferred</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M162"/>
+  <autoFilter ref="A1:M171"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -39516,6 +43716,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId303"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId322"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39527,7 +43745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I321"/>
+  <dimension ref="A1:I343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -53348,8 +57566,954 @@
       </c>
       <c r="I321" s="2" t="inlineStr"/>
     </row>
+    <row r="322" ht="42" customHeight="1">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Fuworx Innovations</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Designer — Intern</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>Internship; current terms/intake need confirmation</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India; hybrid</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Original Open Position list explicitly names UI/UX Designer, Intern and Hybrid (Hyderabad). No numeric stipend, duration, hours, degree criteria or publication/start date. Apply controls do not expose a separate job-detail URL in the reviewed page; a general resume form is available. General info inbox is not a verified recruiting address.</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid Hyderabad internship as listed; detailed skills and degree criteria not published</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323" ht="42" customHeight="1">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — older advert; intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>Internship; current terms/intake need confirmation</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru, Karnataka, India; full-time office</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>UX research, data analysis and independent task ownership</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324" ht="42" customHeight="1">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — older advert; intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Internship; current terms/intake need confirmation</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru, Karnataka, India; full-time office</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>Strong Figma and design-system execution</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325" ht="42" customHeight="1">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — older advert; intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>Internship; current terms/intake need confirmation</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru, Karnataka, India; full-time office</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>AI/prompting awareness and some frontend understanding</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326" ht="42" customHeight="1">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — older advert; intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>Internship; current terms/intake need confirmation</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru, Karnataka, India; full-time office</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>YDI advert dated13March2026 lists full-time Bengaluru office and three months. Body stipend30–35kINR/month differs from header30–50k. Employer site inaccessible in this pass; neither range is a verified current offer. Keep older-listing/on_hold until renewed intake and current pay confirmed.</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Graphic or motion interest; Claude Code and Adobe Creative Suite are bonuses</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327" ht="42" customHeight="1">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub / Atlas Consolidated</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern8483276 — inactive</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>Closed original internship; historical evidence only</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad; historical six-month on-site role</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs/8483276-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>Historical mirror: Figma, user research and interaction/IA foundations</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub / Atlas Consolidated</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern8483276 — inactive</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>Closed original internship; historical evidence only</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad; historical six-month on-site role</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs/8483276-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Historical mirror: ongoing/recent Design or HCI study preferred</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329" ht="42" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub / Atlas Consolidated</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern8483276 — inactive</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>Closed original internship; historical evidence only</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad; historical six-month on-site role</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs/8483276-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>Historical mirror: six-month Hyderabad office commitment</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330" ht="42" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub / Atlas Consolidated</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Intern8495367 — inactive</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>Closed original internship; no active recommendation</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>https://atlasconsolidatedpteltd.teamtailor.com/jobs/8495367-ui-design-intern</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Original exact page explicitly no longer active.</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331" ht="42" customHeight="1">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — application route closed</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>Conflicting current-intake evidence; not active recommendation</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Basic Figma and UI/UX principles</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr"/>
+    </row>
+    <row r="332" ht="42" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — application route closed</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>Conflicting current-intake evidence; not active recommendation</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>Attention to detail, feedback and iteration</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333" ht="42" customHeight="1">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — application route closed</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>Conflicting current-intake evidence; not active recommendation</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nngtw.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio/personal work, responsive design and AI tools are nice to have</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334" ht="42" customHeight="1">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern, Summer2027, YouTube —2028 cohort</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-specific internship; indexed official evidence</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official YouTube summer2027 internship specifies graduation in2028 and returning full-time enrollment. Application window27October–4November2026. Direct employer detail unavailable through research tool; recorded as cohort-specific directory evidence, not a generally eligible internship recommendation.</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>Graduating in2028 from relevant B.Des/M.Des/B.Tech/M.Tech degree</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335" ht="42" customHeight="1">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern, Summer2027, YouTube —2028 cohort</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-specific internship; indexed official evidence</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official YouTube summer2027 internship specifies graduation in2028 and returning full-time enrollment. Application window27October–4November2026. Direct employer detail unavailable through research tool; recorded as cohort-specific directory evidence, not a generally eligible internship recommendation.</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Full-time enrollment and return to study after internship</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr"/>
+    </row>
+    <row r="336" ht="42" customHeight="1">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern, Summer2027, YouTube —2028 cohort</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-specific internship; indexed official evidence</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official YouTube summer2027 internship specifies graduation in2028 and returning full-time enrollment. Application window27October–4November2026. Direct employer detail unavailable through research tool; recorded as cohort-specific directory evidence, not a generally eligible internship recommendation.</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>User interviews/surveys, user-centred design work and portfolio</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337" ht="42" customHeight="1">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern, Summer2027, YouTube —2028 cohort</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-specific internship; indexed official evidence</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/results/78252225691820742-user-experience-design-intern-summer-2027-youtube-ux?sort_by=date</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Indexed official YouTube summer2027 internship specifies graduation in2028 and returning full-time enrollment. Application window27October–4November2026. Direct employer detail unavailable through research tool; recorded as cohort-specific directory evidence, not a generally eligible internship recommendation.</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Figma, Framer or similar design tools</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr"/>
+    </row>
+    <row r="338" ht="42" customHeight="1">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Arventiq Labs</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX internship — index only; not in current public roles feed</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>Indexed lead; no current design vacancy confirmed</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; role-specific mode unverified</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>https://arventiqlabs.com/careers</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339" ht="42" customHeight="1">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>3Di Systems</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Junior Product Designer — unverified landing-page teaser</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>Unverified teaser; no active junior recommendation</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai on teaser; current role location unverified</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>https://www.3disystems.com/careers-at-3di/</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Careers landing page has a Junior Product Designer/Mumbai teaser and placeholder apply# link. Linked Current Job Openings has six other roles, no design detail. Placeholder content is not a confirmed new junior vacancy.</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340" ht="42" customHeight="1">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Unosecur</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — gone indexed detail</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>Older/gone board detail; no active recommendation</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru; historical on-site listing</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.workable.com/view/hi44WzLeFfNqDRnyDhXD2R/product-design-intern-in-bengaluru-at-unosecur</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Specific indexed Workable Product Design Intern detail returns410Gone. Official careers corroborates identity-security company; linked public ATS is a blank JavaScript response. No renewed design intake established; no claim all company hiring closed.</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Indexed advert: complex B2B SaaS UX and product design</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341" ht="42" customHeight="1">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — unpaid/volunteer</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>Unpaid internship; excluded from paid shortlist</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India eligibility not separately verified</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026 Computer Science, IT or related graduate</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr"/>
+    </row>
+    <row r="342" ht="42" customHeight="1">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — unpaid/volunteer</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>Unpaid internship; excluded from paid shortlist</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India eligibility not separately verified</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>Figma, responsive design and design portfolio/coursework</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343" ht="42" customHeight="1">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Design Intern — unpaid/volunteer</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>Unpaid internship; excluded from paid shortlist</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Remote; India eligibility not separately verified</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>https://www.strombot.com/careers/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Full-time remote availability</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I321"/>
+  <autoFilter ref="A1:I343"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Unassessed,Met,Partly met,Gap"</formula1>
@@ -53676,6 +58840,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId319"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId342"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53687,7 +58873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -53702,7 +58888,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Research snapshot: 2026-10-28</t>
+          <t>Research snapshot: 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55131,6 +60317,162 @@
       <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Institutional internship advert conflicts with official careers no openings. Company-only unresolved evidence, not a confirmed current vacancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>HugoHub</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Original UI Design Intern8495367 explicitly inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Nngtw Studio</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Google / YouTube</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-specific2028 graduation and returning-enrollment requirement; original detail unavailable, indexed official evidence only. Not a general internship recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Arventiq Labs</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>3Di Systems</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Careers landing page has a Junior Product Designer/Mumbai teaser and placeholder apply# link. Linked Current Job Openings has six other roles, no design detail. Placeholder content is not a confirmed new junior vacancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Unosecur</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Specific indexed Workable Product Design Intern detail returns410Gone. Official careers corroborates identity-security company; linked public ATS is a blank JavaScript response. No renewed design intake established; no claim all company hiring closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Strom Bot</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Grovyn</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Exact original Wellfound detail410Gone; index freshness does not establish current intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Feelin’s App</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Exact original Wellfound detail410Gone; not a new active role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Metapercept Technology Services</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Indeed category/detail extract5–7.5k/month header,7.5k body; below target. September category date/cached extract is not fresh employer publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SOR Group</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Indexed matching Cutshort advert11.5–12k/month Hyderabad below target; exact opened extract did not independently re-establish salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Raptee.HV</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Indexed mirror1.8lakh/year, another mirror15k/month; no employer-current stipend confirmed and both below target. Keep units/source limits; do not convert annual header to a verified stipend.</t>
         </is>
       </c>
     </row>

--- a/topics/job-search-agent/app/public/data/internships.xlsx
+++ b/topics/job-search-agent/app/public/data/internships.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$512</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internships'!$A$1:$Z$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$F$606</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source coverage'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Company watchlist'!$A$1:$M$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Company directory'!$A$1:$M$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Role requirements'!$A$1:$I$362</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -4450,12 +4450,12 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Confirm stipend, duration, office location and start date with the official listing; complete both required steps only after review.</t>
+          <t>Archived removed original. Reopen only if employer confirms a renewed/replacement requisition; prior browser-local application history remains available.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline. Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
@@ -6994,8 +6994,278 @@
       </c>
       <c r="Z68" s="2" t="inlineStr"/>
     </row>
+    <row r="69" ht="95" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — UX/UI and Accessibility</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Hyderabad hybrid/office optional</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Confirm monthly stipend/currency,12-week dates and20–40hour schedule, evening overlap, written overseas contract and college internship-letter acceptance before applying.</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>Original200 detail: paid, approximately12weeks,20–40hours/week,November/December2026 start. Remote India or optional Hyderabad office;2–3hours evening IST overlap. Direct contract with TheInterviews Inc.(Delaware), no Indian subsidiary. Stipend depends on hours/experience and is not numerically stated. Intake/start and college acceptance still need confirmation.</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>Students/recent graduates welcome; portfolio should explain process and iteration; Figma and visual/interaction foundations; feedback and weekly iteration; Accessibility checks for keyboard, screen reader, contrast and mobile; component/token work mapped to Tailwind; Research/analytics and developer handoff; HTML/CSS/React are bonuses</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>Original posting date not stated; first observed30October2026 is not a posting date</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="95" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India; work mode unstated</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Confirm monthly stipend, office/hybrid expectations,3–6month intake and current application access; verify current-student eligibility.</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>https://recruitcrm.io/apply/17301815425210068169ldp</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>Original role: Mumbai,3–6months,0–1years. Student/personal work and self-taught candidates welcome. Pay, posting date, start/cohort and work mode absent. Linked RecruitCRM application could not be read through research tool; no form submitted.</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio including student or personal design work;0–1years; Research/data/behaviour synthesis into problem statements, journeys and prototypes; Strong aesthetics, attention to detail, collaboration and presenting design decisions; Motion, illustration and advanced prototyping are bonuses</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Original posting date not stated; first observed30October2026 is not a posting date</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="95" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer — junior/stretch,1–2years required</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai header / Bengaluru body; employer location conflict</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Confirm experience and current-student eligibility, Mumbai versus Bengaluru, joining window, work mode and annual salary in original units.</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Company careers</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-designer-1</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>https://recruitcrm.io/apply/17283921567990068169CeZ</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>Original full-time role requires1–2years; junior/stretch alternative, not an internship or assured fresher eligibility. Header says Mumbai, body says Bengaluru. Pay/start/work mode unstated. Linked RecruitCRM application restricted to research tool.</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>1–2years required; do not assume zero-experience or student eligibility; Develop ideas into prototypes, including no-code/lightweight code; Synthesize research/data into product problems and vision; Present product stories and work with technical teams</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>Original posting date not stated; first observed30October2026 is not a posting date</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z68"/>
+  <autoFilter ref="A1:Z71"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"discovered,shortlisted,on_hold,applied,assessment,interview,offer,closed"</formula1>
@@ -7136,6 +7406,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7147,7 +7423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F512"/>
+  <dimension ref="A1:F606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23430,8 +23706,3016 @@
         </is>
       </c>
     </row>
+    <row r="513" ht="42" customHeight="1">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>Original200 detail: paid, approximately12weeks,20–40hours/week,November/December2026 start. Remote India or optional Hyderabad office;2–3hours evening IST overlap. Direct contract with TheInterviews Inc.(Delaware), no Indian subsidiary. Stipend depends on hours/experience and is not numerically stated. Intake/start and college acceptance still need confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="42" customHeight="1">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/join-the-team</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>Official team index links Product Design Intern and Product Designer1–2years. talent@humanx.io is general recruitment/speculative-interest contact, not contacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="42" customHeight="1">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>Original role: Mumbai,3–6months,0–1years. Student/personal work and self-taught candidates welcome. Pay, posting date, start/cohort and work mode absent. Linked RecruitCRM application could not be read through research tool; no form submitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="42" customHeight="1">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-designer-1</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>Original full-time role requires1–2years; junior/stretch alternative, not an internship or assured fresher eligibility. Header says Mumbai, body says Bengaluru. Pay/start/work mode unstated. Linked RecruitCRM application restricted to research tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="42" customHeight="1">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=5e25dd89f059fecc</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>Indeed exact detail still readable: PDI282506,body Posted22August2026,Hyderabad office6months,0–1years; no pay. Original employer detail410; not verified active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="42" customHeight="1">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>https://tensorgo.com/job-type/pdi282506/</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>Repeated fresh originalHTTP410Gone. Current careers page is JavaScript shell; site migration possible, so no company-wide closure inferred. Accessible Indeed advert does not establish renewed intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="42" customHeight="1">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tensorgo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>Fresh careers200 response is a JavaScript shell; current product-design intake not established.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="42" customHeight="1">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/TensorGo-Technologies-UX-Product-Designer-Intern-Salaries-E4412050_DAO.htm?filter.jobTitleExact=UX%2FProduct+Designer+Intern</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>Role-specific public Glassdoor table: one report1June2023,Hyderabad0–1years,23–27kINR/month. Low-confidence historical benchmark; modeled header differs, not current listing pay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="42" customHeight="1">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk/61239b0fde0a6e4a69cf151f?source=careers</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>ATS detail KL-85UMEFA9 remains readable:3months,0–1years, pay/date unknown. Linked application explicitly says not accepting applications; not an active feed recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="42" customHeight="1">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk/61239b0fde0a6e4a69cf151f/apply?source=careers</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>Original application says currently not accepting applications. CAPTCHA not entered/bypassed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="42" customHeight="1">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4639779-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>Original Wellfound detail readable, relative age2months not an absolute publication date. Header5–10kINR lacks period; fetched JSON-LD baseSalary specifies YEAR. Do not silently reinterpret as monthly. Pay/error needs employer clarification; not stipend match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="42" customHeight="1">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>https://archinza.com</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>Official product website linked from employer job description; product context only, not additional vacancy evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="42" customHeight="1">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>Growth Gravy</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.growthgravy.com/</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>Public research extract lists UI/UX Designer; pay/seniority/detailed current internship not established. Normal HTTP request encountered CAPTCHA redirect shell; no bypass. Work-from-home FAQ is role-dependent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="42" customHeight="1">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>Growth Gravy</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>https://startupgoa.org/job/growth-gravy-goa-internship-internships-in-goa-multiple-positions/</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>StartupGoa broad multi-position internship advert includes UI/UX Intern; no original date, pay, UX-specific requirements or current cohort verified. Company-only discovery, not an inferred active internship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="42" customHeight="1">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="42" customHeight="1">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4298 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="42" customHeight="1">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="42" customHeight="1">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>BThree Design Agency</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-bthree-design-agency-4473077505</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="42" customHeight="1">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>Wint Wealth</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sruthisivakumar_product-design-intern-wint-wealth-activity-7515659430051426304-tqUQ</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="42" customHeight="1">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Hevo Data</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/hevodata/433ffdef-3125-48ed-a131-52c697c321ee</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3675 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="42" customHeight="1">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>RevRag AI</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.revrag.ai/careers/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4775 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="42" customHeight="1">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Chiblu</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>https://chiblu.com/careers/product-design-intern-ux-ui</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3953 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="42" customHeight="1">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>NeuralPath Technologies</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neuralpath.app/careers/</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 6178 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="42" customHeight="1">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>KRMR Solutions</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>https://krmrsolutions.com/careers/design-intern</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 1082 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="42" customHeight="1">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Zavio</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gozavio.com/careers</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2591 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="42" customHeight="1">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>Gnixar Academy</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jobleads.com/in/job/product-design-intern--india--e24abd61a6654a91f9a3af3bab3db8da5</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4423 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="42" customHeight="1">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/glance/jobs/7916115</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3892 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="42" customHeight="1">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Techolution</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e1a25a765d7c4fd7</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4704 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="42" customHeight="1">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>F1studioz</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fef929ca634359c7</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4281 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="42" customHeight="1">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Green Ping Solutions</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=157d2635900933e2</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2702 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="42" customHeight="1">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Moon Technolabs</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=45ad3491be217187</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2894 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="42" customHeight="1">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Keyideas Infotech</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-ui-ux-internship-figma-graphics-research-keyideas-infotech-gurgaon-gurugram-0-to-1-years-181120004352</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 0 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="42" customHeight="1">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-design-intern-pune</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 10760 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="42" customHeight="1">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Zunderdog</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zunderdog.com/careers/ui-ux-designer-fresher-pune</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 11135 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="42" customHeight="1">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>project44</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/project44/jobs/8101750</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 9016 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="42" customHeight="1">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Frappe</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>https://frappe.io/careers/open-positions/designer</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2219 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="42" customHeight="1">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>Juno</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.kula.ai/juno/446-product-design-intern</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2078 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="42" customHeight="1">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gravity.fast/jobs/cmqdlet8309n1b5p6q8lbi6im</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2445 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="42" customHeight="1">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Ungrammary</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>https://club.ungrammary.com/jobs/ux%2Fui-trainee-designer</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3776 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="42" customHeight="1">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Nonlinear</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>https://nonlinear.in/careers</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 8427 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="42" customHeight="1">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>Octet Design Studio</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>https://octet.design/careers/</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3153 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="42" customHeight="1">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Octet Design Studio</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>https://octet.design/careers/</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3153 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="42" customHeight="1">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>SuperKalam</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/superkalam/jobs/MW7xgR6-product-designer-internship</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4888 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="42" customHeight="1">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Coulomb AI</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/coulomb-ai/jobs/Qtbm3xO-ux-designer</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4615 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="42" customHeight="1">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>Icogz</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=3d84294c02b4aced</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 7523 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="42" customHeight="1">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>VictorFlow</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=32e693c20b142dbf</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3508 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="42" customHeight="1">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>Gunadhya Software Solutions</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=e4310669941f4c75</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 4456 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="42" customHeight="1">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Qoruz</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 41654 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="42" customHeight="1">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>Energise.pro</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/energise-pro/jobs/ui-ux-designer</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 11862 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="42" customHeight="1">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Arihant AI</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>https://arihantai.com/jobs/uiux-product-design-internship-web-mobile-ai-systems-85</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 16714 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="42" customHeight="1">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Unitedover</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>https://app.dover.com/apply/unitedover/04e656b6-31ce-4f66-aee2-45bf80085c3b</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 5 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="42" customHeight="1">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Atlabs</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>https://join.atlabs.ai/roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 5498 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="42" customHeight="1">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: missing. HTTP 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="42" customHeight="1">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: error. HTTP 503</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="42" customHeight="1">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 6549 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="42" customHeight="1">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Propel</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>https://gopropel.in/careers/design-intern/</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 22 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="42" customHeight="1">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Kodin / Autometa Labs</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getkodin.com/#careers</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 22171 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="42" customHeight="1">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>FORMAS.AI</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.formas.ai/careers</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 52040 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="42" customHeight="1">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Daankart</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>https://daankart.com/about/careers#open-roles</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 13173 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="42" customHeight="1">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>Payzoplus</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.payzoplus.com/company/careers/design</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 5063 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="42" customHeight="1">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>DECTIFY</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.dectify.in/careers/details/DTCI-S191348/ui-ux-designer/</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2448 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="42" customHeight="1">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>CollabOP</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.collabop.com/careers/ui-ux-intern</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2106 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="42" customHeight="1">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/lokal-app/j/CB2EDD7186</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 35 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="42" customHeight="1">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Aeron Systems</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeronsystems.com/careers/design-intern-visuals-ui-ux/</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 6251 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="42" customHeight="1">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Androcid</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>https://androcid.freshteam.com/jobs/_KvFSyux1O8C/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2735 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="42" customHeight="1">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>SutharTech</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>https://suthartech.com/internships/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 1927 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="42" customHeight="1">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Nihar / Creuto</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.niharrout.com/work-with-me/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 12807 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="42" customHeight="1">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>ATRISI</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>https://atrisi.org/collaborate/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2866 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="42" customHeight="1">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Toddle</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>https://toddle.keka.com/careers/jobdetails/36030</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="42" customHeight="1">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Toddle</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>https://toddle.keka.com/careers/jobdetails/85790</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="42" customHeight="1">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>Mojro</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ux-design-research-intern-at-mojro-4477515785</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="42" customHeight="1">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>LeadSquared</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=af19b01b18d49a36</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2668 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="42" customHeight="1">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Krevok</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>https://krevok.com/careers</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2522 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="42" customHeight="1">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>WATER / Water Robotics</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.water.bio/careers/WR021</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 1923 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="42" customHeight="1">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>AlignMinds Technologies</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>https://infopark.in/jobs/alignminds-technologies/ui-ux-designer-internship-3</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 1803 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="42" customHeight="1">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>NueFind</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-intern-at-nuefind-4481147403</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: blocked. Robots unavailable or disallows collector; no closure inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="42" customHeight="1">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>Pixster Studio</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pixsterstudio.com/jobs-opening/jr-product-designer</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 6369 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="42" customHeight="1">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>Fuworx Innovations</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fuworx.com/careers/</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 2275 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="42" customHeight="1">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youngdesignersindia.com/Jobs/ui-ux-design-internparadigmbengaluru-ydijobs</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>fetched</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>Primary URL check: fetched. Public response extracted 3254 characters; successful fetch alone does not revalidate intake, pay or deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="42" customHeight="1">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>ShramikSathi</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ui-ux-design-intern-at-shramiksathi-4469701295</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>terms-reviewed</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>Original listing terms separately reviewed30October; retained pay/units, experience, start and location caveats. Current intake and written offer not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="42" customHeight="1">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Menstrupedia</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.menstrupedia.com/careers/ux-intern</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>terms-reviewed</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>Original listing terms separately reviewed30October; retained pay/units, experience, start and location caveats. Current intake and written offer not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="42" customHeight="1">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/product-design-intern-at-more-retail-private-limited-4477072502</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>terms-reviewed</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>Original listing terms separately reviewed30October; retained pay/units, experience, start and location caveats. Current intake and written offer not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="42" customHeight="1">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>Qoruz</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/job/Junior-UX-Designer-Bengaluru-Bangalore-Qoruz-c5rfKlTo</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>terms-reviewed</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>Original listing terms separately reviewed30October; retained pay/units, experience, start and location caveats. Current intake and written offer not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="42" customHeight="1">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Bot</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/enterprisebot/16830986-ui-designer-0-1-years-experience</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>terms-reviewed</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>Original listing terms separately reviewed30October; retained pay/units, experience, start and location caveats. Current intake and written offer not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="42" customHeight="1">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>SutharTech</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>https://suthartech.com/internships/ui-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>terms-reviewed</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>Original listing terms separately reviewed30October; retained pay/units, experience, start and location caveats. Current intake and written offer not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="42" customHeight="1">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>removed-original</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="42" customHeight="1">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/search-jobs/JR-045767/</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>Fresh official search returned200 and0results for exact requisition. Together with repeated original404 supports original removal; not proof position filled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="42" customHeight="1">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>https://revvity.wd103.myworkdayjobs.com/wday/cxs/revvity/External/job/Mumbai/UX-Intern_JR-045767</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>Normal public detail request403 permission denied; no retry/bypass, no current replacement intake established.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="42" customHeight="1">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.moonfiregroup.com/jobs/ui-ux-design-trainee-fresher</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>unresolved-maintenance</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>Repeated original503 with explicit maintenance page. Not closure; prior annual advertised pay retained, not freshly revalidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="42" customHeight="1">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.revvity.com/job/thane/ux-intern/20539/102245859808</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="42" customHeight="1">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk/61239b0fde0a6e4a69cf151f/apply?source=careers</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>Original application explicitly not accepting despite live detail; company-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604" ht="42" customHeight="1">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4639779-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>Header5–10kINR without period; original JSON-LD YEAR. Low/anomalous as written, not converted to monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605" ht="42" customHeight="1">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>HYV</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.livehyv.com/careers/roles/design-intern</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>HYV-INT-01 explicitly Delhi NCR/Gurugram onsite, outside eligible office geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" ht="42" customHeight="1">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>Eduminatti</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>https://jobsii.com/job/eduminatti-ui-ux-design-internship-wfh-october-2026/</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:49:34+00:00</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>Mirror-reported5–10k/month,2months part-time; below target. Original Internshala restricted; dates not independently verified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F512"/>
+  <autoFilter ref="A1:F606"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23442,7 +26726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23504,25 +26788,29 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Accessible category and targeted query</t>
+          <t>Targeted category and exact-role checks</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>YC design category and India intern queries checked. Cityfurnish Gurugram/low-or-anomalous pay and US-only Flick motion/graphic role do not meet this shortlist. No new suitable exact YC role verified.</t>
+          <t>YC design/India intern search and originals reviewed; Deep24 remote US/visa-only20–30USD/hour excluded, Cityfurnish Gurugram/low-or-anomalous pay excluded. No suitable new YC-primary role.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>October category label is not a date on each job. SuperKalam/Coulomb2024 originals and compensation conflicts retained on hold.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Existing SuperKalam/Coulomb2024 original dates and compensation conflicts remain on hold. Category label is not an individual posting date.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Deep24 US-only; Cityfurnish outside geography</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -23537,22 +26825,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Inaccessible original route / search sample</t>
+          <t>Inaccessible original / indexed sample</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Work at a Startup design-intern India search attempted; jobs?roles=designer inaccessible through tool. No suitable new original verified.</t>
+          <t>India design internship search attempted; original designer route inaccessible. No additional suitable verified role.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>No logged-in access or complete inventory claim; YC duplicates are not counted as additional roles.</t>
+          <t>No signed-in access or full inventory; YC crossposts not counted twice.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -23570,22 +26858,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Public API top-level scan</t>
+          <t>Public API top-level sample scan</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>October2026 HN thread49922569:319top-level records fetched,21raw-text designer/UX/UI matches screened by company heading/geography/seniority; no independently verified suitable new India junior/intern role. Previous266 snapshot retained historically.</t>
+          <t>October thread49922569:319top-level records fetched,21raw designer/UX/UI matches screened by heading/geography/seniority. No suitable new independently verified role. Prior266 snapshot remains historical.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Same raw-term method as28October, not every linked employer JD. Engineering/senior/US/Europe posts and unspecified part-time engagement not promoted. No no-hiring conclusion for entire platform.</t>
+          <t>Not every linked job detail reviewed; engineering/senior/US-Europe and volunteer posts are not matching vacancies.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -23636,27 +26924,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Accessible retained originals / cached category sample</t>
+          <t>Accessible details and targeted search</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>All prior Indeed primary URLs attempted; public category searches across Gujarat/Pune/Hyderabad and fresher design. Metapercept5–7.5k/month below target; retained Techolution same role, no duplicate new card.</t>
+          <t>Indeed exact TensorGo PDI282506 readable, but employer original410. Matching xCube category advert conflicts with original application not accepting. No new active Indeed-primary card.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Indeed category URLs returned older September extracts despite newer search snippets; do not claim current inventory or employer publication from category dates. No new suitable Indeed-primary lead.</t>
+          <t>Search/mirror freshness does not renew original vacancy. Indeed category date is not an employer posting date.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Kixar: INR30–35k/month internship copy explicitly expired; page says8 May2026 and no longer accepting. Fresh mirror ages do not revive it.; Melento: Indeed internship lists INR11,000–150,000/month, a very wide anomalous range with below-target minimum; not a confirmed stipend match.; Redliner: Indexed up-to-INR30k listing is expired; upper limit is not a guaranteed minimum.; BiCSoM: Historical2022 role with a still-accessible form, but LinkedIn crosspost closed; watchlist only pending a new intake.; We-intern: Direct Indeed detail INR10,000–20,000/month remote, below target.; Balusen Technologies: Original expiry banner; retained archived ID.; PV Labs: Exact Indeed detail3–5k stipend/up-to5k per month; four-week product-image/e-commerce-visual role, below pay and outside core UX.; Travel On Tips: Exact Indeed Ahmedabad six-month internship advert5–10kINR/month; below Gujarat floor.; Picktime: Exact Indeed Hyderabad in-person UI/UX internship12–15kINR/month; below target.; Aiva Technology: Exact Indeed Bengaluru interaction/Figma/React internship15–18kINR/month; below target.; YS Innovations: Indexed Indeed Coimbatore internship8–10kINR/month; below target. Original detail not separately opened.; WebEarl: Indexed Indeed Ahmedabad up-to8kINR/month; below target; not independently reviewed detail.; Metapercept Technology Services: Indeed category/detail extract5–7.5k/month header,7.5k body; below target. September category date/cached extract is not fresh employer publication.</t>
+          <t>TensorGo removed original; YS Innovations8–10k header; training pay unclear, up-to10k only performance-linked project phase; ZeonAI up-to15k/month; Calibium up-to8k/month; remote/hybrid conflict</t>
         </is>
       </c>
     </row>
@@ -23673,29 +26961,25 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Restricted route / prior robots limits</t>
+          <t>Original robots-blocked / indexed sample</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Explicit Naukri UI/UX-intern queries attempted. Direct search route unavailable; retained Keyideas primary body empty. No independently verified new Naukri job.</t>
+          <t>Explicit Naukri domain search attempted; non-retryable robots restriction. Indexed corporate/campus pages did not establish a suitable new current design internship.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Prior robots restrictions remain caveated; current empty response is not verified vacancy content. No account access, CAPTCHA bypass or authenticated session implied.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Arcitech: Naukri-associated indexed mirror reports INR15,000/month Mumbai, below target. Original Naukri detail and original pay not verified; mirror30September date is not a verified employer posting date.</t>
-        </is>
-      </c>
+          <t>No account/session inferred, CAPTCHA bypass or original vacancy freshness claimed; existing source IDs preserved.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -23710,29 +26994,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Accessible retained detail / sample discovery</t>
+          <t>Targeted public detail/search sample</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Qoruz current detail still1–3years and4–6lakhINR/year. Current board shows28October, while prior record observed16October/index7October; original date fields preserved, date observation labelled separately. SOR indexed11.5–12k/month below target.</t>
+          <t>India UX/product internship searches checked. Integra Magna3–5k/month and HouseAI0/month unsuitable; no new qualifying original. Existing Qoruz4–6lakh/year reviewed without changing original-date observations.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Changing board/repost dates are not verified employer original publication. Ungrammary10–12k/month below-target fellowship and annual conflict retained.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>AMPM Network: ₹10–15k/mo, belowtarget; recruiterinactive; SDS softwares: ₹7–15k/mo; no current full-time students; immediatejoiners; Synorus: Original Cutshort range INR0–5,000/month, dated29November2025; below target, potentially unpaid lower end.; SOR Group: Indexed matching Cutshort advert11.5–12k/month Hyderabad below target; exact opened extract did not independently re-establish salary.</t>
-        </is>
-      </c>
+          <t>Annual junior pay is not monthly stipend. Ungrammary10–12k/month negative evidence and company annual conflict preserved.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -23747,29 +27027,25 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Cookie/JavaScript-limited route</t>
+          <t>Cookie / JavaScript shell and indexed search</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Unstop UX-intern search attempted; original internships page returns Please Wait/Cookies Disabled and no readable inventory. No suitable new role verified.</t>
+          <t>Unstop internship original route opened but cookie/JS extraction limited; indexed targeted sample yielded no additional suitable verified detail.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>No access bypass. Non-Unstop results from broad search are not claimed as original Unstop postings.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Pixel Paranoia UI/UX hackathon: Competitionprize30k, notinternstipend</t>
-        </is>
-      </c>
+          <t>No full original inventory or renewal of old/closed internships claimed.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -23784,25 +27060,29 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Restricted original route</t>
+          <t>Restricted original / mirror-only sample</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Explicit Internshala30k design queries and original UI/UX-internships page attempted; direct page restricted. Sample mirrors show low pay or start windows ending in November; no new employer-corroborated qualifying role.</t>
+          <t>Explicit Internshala query and original route attempted; restricted. Eduminatti Jobsii mirror reports5–10k/month,2months part-time,29October date and28November deadline; below target.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>No signed-in account implied. Mirror ages and closing/start windows are labelled mirror evidence, not independently original employer dates.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>Those dates/pay are mirror-reported, not verified direct Internshala access or freshness; no bypass.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Eduminatti mirror below target and short duration</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -23817,22 +27097,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>520 error / indexed sample search</t>
+          <t>Original520 / indexed sample</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Explicit Instahyre UX-intern query attempted; original home520. No exact suitable new role verified.</t>
+          <t>Explicit Instahyre search and original route attempted;520 response. No suitable new current exact detail verified.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Tool access does not establish a linked account or complete inventory. No bypass or source quota.</t>
+          <t>No authenticated access or closure inferred from error.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -23850,27 +27130,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Indexed discovery / exact detail410</t>
+          <t>Targeted search and exact details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Wellfound India design-intern searches found Grovyn and Feelin’s App; both exact details410Gone. Cravv indexed20k/month remains below target.</t>
+          <t>Archinza UX intern remote Everywhere;5–10kINR header lacks period, original JSON-LD YEAR. Company-only low/unit-conflict evidence. Timbre original410. No suitable new active Wellfound role.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Fresh snippet/crawl dates do not revive removed details. Prior closed/excluded records retained without duplicates.</t>
+          <t>Do not convert Archinza annual metadata to monthly or treat relative2months as absolute original date.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Snaptrude: Direct HTTP 410Gone; search index stale; Renan: Opened detail explicitly₹5k/month; MAVR: Body explicitly unpaid; BetterStory: INR25k/month remote India visual-design internship explicitly says it is not a product/UX role; outside requested discipline.; Rootcode: Original Wellfound detail returned410 Gone.; NoobSync Innovations: Explicit no fixed stipend, performance-only compensation and20hours/week; no guaranteed monthly floor.; IQnext: Indexed internship original returned410Gone; current intake not inferred from snippet.; Sensor Equation: Indexed relevant remote listing original returned410Gone; not an active lead.; Grovyn: Exact original Wellfound detail410Gone; index freshness does not establish current intake.; Feelin’s App: Exact original Wellfound detail410Gone; not a new active role.</t>
+          <t>Timbre original410; Archinza compensation units/low amount</t>
         </is>
       </c>
     </row>
@@ -23887,29 +27167,25 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Accessible descriptive category / discovery sample</t>
+          <t>Targeted public category/search sample</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Himalayas India UX and intern-design searches surfaced listings; original intern category extract contained descriptive/sign-up content rather than readable qualifying cards. Cloud Counselage indexed junior role restricts Kerala/Tamil Nadu candidates; no suitable exact original verified.</t>
+          <t>Himalayas design-intern/junior remote India search and public category opened. No suitable new exact employer-backed India-eligible internship verified.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>No claim site has zero roles. Existing Energise Job expired? remains a reporting button, not a closure notice. Pay/start/location eligibility not inferred from remote labels.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>GWEN: Applicant-paid training, no salary or job offer; Cloud Counselage: 2+years andKerala/TamilNadu residency; not a fresher role; GitLab: Explicit future talent pool, not current vacancy; Metasys: Specific remote internship explicitly unpaid initially for first-quarter evaluation; possible later paid extension is not current paid work.25October/24December are Himalayas posting/deadline dates, not independently employer-verified dates.</t>
-        </is>
-      </c>
+          <t>Category/filter extracts may be limited, signup-gated or descriptive; global/remote label alone does not establish India eligibility. No comprehensive inventory claim.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -23924,29 +27200,25 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Accessible category / targeted search</t>
+          <t>Targeted public category/search sample</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>WWR design category and India-junior queries checked; listing index surfaced LooseGrip part-time junior contract with worldwide label, but no exact UX scope, current pay unit and India engagement verified. No new recommended role.</t>
+          <t>We Work Remotely design-intern/junior remote India search and public category opened. No suitable new exact employer-backed India-eligible internship verified.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Category/index sample only; world-wide label alone does not establish applicant or contract eligibility.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Workiva: Principal designer, UnitedStates; Cribl: Senior UX, UnitedStates</t>
-        </is>
-      </c>
+          <t>Category/filter extracts may be limited, signup-gated or descriptive; global/remote label alone does not establish India eligibility. No comprehensive inventory claim.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -23961,29 +27233,25 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Accessible category / sample query</t>
+          <t>Targeted public category/search sample</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Remote OK design category and India-design-intern search attempted. No suitable new exact UX internship or junior vacancy verified in reviewed sample.</t>
+          <t>Remote OK design-intern/junior remote India search and public category opened. No suitable new exact employer-backed India-eligible internship verified.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Country filters and category taxonomy are not vacancy/eligibility evidence; no full-inventory scraping claimed.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Twine: Canada-only brand role; Twine: Graphic brand work; outside requested UX/product roles</t>
-        </is>
-      </c>
+          <t>Category/filter extracts may be limited, signup-gated or descriptive; global/remote label alone does not establish India eligibility. No comprehensive inventory claim.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -23998,29 +27266,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Accessible category / limited public sample</t>
+          <t>Targeted public category/search sample</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Remotive design page and India-UX-junior queries checked; no suitable new exact original verified.</t>
+          <t>Remotive design-intern/junior remote India search and public category opened. No suitable new exact employer-backed India-eligible internship verified.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Public samples and unlock/sign-in boundaries limit coverage; paid access not bypassed.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Blueprint Technologies: UX/CX roleArgentina; seniorexamplePhilippines; HOPn UG: GraphicinternGermany</t>
-        </is>
-      </c>
+          <t>Category/filter extracts may be limited, signup-gated or descriptive; global/remote label alone does not establish India eligibility. No comprehensive inventory claim.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -24035,29 +27299,25 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Accessible category / sample query</t>
+          <t>Targeted public category/search sample</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Remote.co design category and India-junior queries checked; no suitable new exact India junior/intern UX role verified.</t>
+          <t>Remote.co design-intern/junior remote India search and public category opened. No suitable new exact employer-backed India-eligible internship verified.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Generic remote descriptions and senior/graphic roles are not active India internship evidence.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Databento: VisualDesignerUSnational; Discovery Education: ProductDesignerUSnational</t>
-        </is>
-      </c>
+          <t>Category/filter extracts may be limited, signup-gated or descriptive; global/remote label alone does not establish India eligibility. No comprehensive inventory claim.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -24072,22 +27332,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Accessible descriptive entry-level page</t>
+          <t>Targeted public category/search sample</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Working Nomads entry-level design category and design-intern India query checked. Extract contained descriptive navigation without readable qualifying cards.</t>
+          <t>Working Nomads design-intern/junior remote India search and public category opened. No suitable new exact employer-backed India-eligible internship verified.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Not a claim board has zero jobs; no complete inventory or current employer intake established.</t>
+          <t>Category/filter extracts may be limited, signup-gated or descriptive; global/remote label alone does not establish India eligibility. No comprehensive inventory claim.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -24105,22 +27365,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Accessible directory; deeper route unresolved</t>
+          <t>Public directory discovery sample</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>StartupMap.in public home provides city/sector/hiring filters and3070startup directory context. Attempted Chennai link did not resolve reliably through research tool; no company/role derived from that click.</t>
+          <t>StartupMap.in public map/home opened for employer discovery. No vacancy inferred from map entry, funding, counts or generic hiring filter.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Directory/filter counts are discovery only, not active vacancies. Deeper city/company discovery remained unverified in this sample.</t>
+          <t>Interactive/dynamic directory extraction limited; employer role/application evidence required before active recommendation.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -24138,22 +27398,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Original page timeout</t>
+          <t>Public directory discovery sample</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>StartupBlink India original directory opened but timed out in this pass; no newly verified company or role derived.</t>
+          <t>StartupBlink India public map/home opened for employer discovery. No vacancy inferred from map entry, funding, counts or generic hiring filter.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Previous indexed directory evidence retained in history; no claim current ranking or full directory accessed today.</t>
+          <t>Interactive/dynamic directory extraction limited; employer role/application evidence required before active recommendation.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -24171,22 +27431,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Accessible directory map/context</t>
+          <t>Public directory discovery sample</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Indian Startup Map public map opened:funding/scheme register context with JavaScript map and location/methodology limits. No exact current internship verified from register.</t>
+          <t>Indian Startup Map public map/home opened for employer discovery. No vacancy inferred from map entry, funding, counts or generic hiring filter.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Registration/funding/location signal is not hiring or continued operation. No paid report or private data accessed.</t>
+          <t>Interactive/dynamic directory extraction limited; employer role/application evidence required before active recommendation.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -24204,22 +27464,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Accessible public directory shell</t>
+          <t>Public directory discovery sample</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>IndianStartupsMap home opened with648-company snapshot and client-rendered map/grid. No exact current hiring derived.</t>
+          <t>IndianStartupsMap public map/home opened for employer discovery. No vacancy inferred from map entry, funding, counts or generic hiring filter.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Submitted company profiles and generic hiring filters are not vacancy evidence; no exhaustive company inventory review.</t>
+          <t>Interactive/dynamic directory extraction limited; employer role/application evidence required before active recommendation.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -24237,29 +27497,25 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Original details, application routes and primary maintenance</t>
+          <t>Whole-board URL check and original/apply review</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Fuworx explicitly lists hybrid Hyderabad UI/UX internship; pay/JD absent, held. Original HugoHub UX/UI inactive; Nngtw open index conflicts with closed application form. Arventiq normal public feed has four non-design roles;3Di current index six other roles versus placeholder design teaser. project44 exact8101750 official cross-post added.</t>
+          <t>All65previous active primaries attempted:55responses,8collector blocks,1missing original,1error;4responses shells. Three blocked LinkedIn details separately readable. New TheInterviews/HumanX originals support3held records. Revvity original retired after404+official0results. Moonfire maintenance503 stays unresolved.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>All63 active primary URLs attempted:55 responses/eight collector blocks/four shells. Three blocked LinkedIn bodies separately readable; nine original-primary body checks remain unresolved. No existing active lead newly closed by reliable evidence. Application forms inspected read-only; none submitted.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Nuvento Systems: Institutional advert explicitly unpaid for three months; later salary not current internship pay.; Jio: Junior title conflicts with original2–6years requirement; not a fresher internship alternative.; Neurai Technologies: Indexed official15kINR/month gross2–3months visual/media design internship; below remote target. Direct role timed out.; 0110 Design: Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.; HugoHub: Exact original UX8483276 and UI8495367 pages explicitly say no longer active. Current employer job index lists three other roles, not design internships. Fresh mirror ages and an anonymous35k/month board copy do not revive these vacancies.; Nngtw Studio: Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.; Arventiq Labs: Careers index/search mentions UI/UX internships, but normal public site jobs feed currently contains four non-design roles and no UI/UX role. No specific current design opening established. One separate SOC programme has3999INR fee; this does not establish UI/UX fees or compensation.; 3Di Systems: Careers landing page has a Junior Product Designer/Mumbai teaser and placeholder apply# link. Linked Current Job Openings has six other roles, no design detail. Placeholder content is not a confirmed new junior vacancy.</t>
-        </is>
-      </c>
+          <t>A fetch is not fresh intake confirmation. Ten retained active primary-body checks remain unresolved after Revvity retirement; no closure inferred from errors, robots or shells.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -24274,22 +27530,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>403 Forbidden / limited public search</t>
+          <t>Original403 / indexed search sample</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Explicit X product-design-intern and design-internship India/remote queries searched; original X search inaccessible403. No suitable original social hiring post newly verified.</t>
+          <t>Explicit UX/product design internship India X search attempted; original search403. No suitable new original social vacancy established.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Search snippets are not verified original access or freshness. Existing X source histories preserved; no quota vacancy invented.</t>
+          <t>No authenticated session, exhaustive social scan or current original access claimed; prior Wint/BThree evidence retained.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -24307,29 +27563,25 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Retained employer-authored terms / sampled discovery</t>
+          <t>Targeted public search and retained-role review</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ShramikSathi30k/month remote,More Retail35k/month Bengaluru and BThree20–25k/month/immediate descriptions rechecked. Antropi exact old URL redirects to generic industrial-design results; no current role inferred.</t>
+          <t>HumanX and India design internship queries; original employer evidence used for new cards. Retained ShramikSathi,More Retail,BThree terms separately readable.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Google/YouTube2028-cohort and closed/older/low-pay discoveries are not new eligible cards. Relative ages do not establish original publication or start eligibility.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0110 Design: Exact employer-authored detail compensation is equity/sweat equity with deferred-salary roadmap; no present fixed monthly stipend, excluded.; UNMANND: Product Design Intern is mechanical UAV CAD/FEA role with mechanical-engineering background; outside UX/product interface scope.; Future Interns: Indexed October2026 cohort explicitly unpaid for one month; not a paid internship match.</t>
-        </is>
-      </c>
+          <t>No new LinkedIn-primary duplicate; role current intake/start still requires confirmation.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -24344,29 +27596,25 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Targeted startup/company and live route checks</t>
+          <t>Targeted original and startup discovery checks</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Fuworx and older Paradigm are newly researched on hold. HugoHub35k anonymous-board copy rejected after original inactive. Nngtw open label rejected for active recommendation after linked form explicitly closed. Strom original unpaid; Unosecur exact board410.</t>
+          <t>TheInterviews paid remote India November/December role added, amount unknown. HumanX studio intern and1–2year junior/stretch added. TensorGo old/removed and xCube not-accepting retained directory-only.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Company discovery, funding and startup reputation do not establish salary or eligibility. Existing SutharTech December cohort rechecked; no new guaranteed monthly-pay match.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Superteams.ai: Original role explicitly closed despite its listing on the general careers index.; Leap: Original ATS host/detail returns a site-not-found page; indexed internship not confirmed current.; LeelaRam Technologies: Original stipend10–15k/month in Mumbai, below target.; GoPratle: Original header2–5k and final-year/fresher restriction; not a qualifying stipend match.; FLIP: Original410 Gone.; frover: Original410 Gone.; Mowka: Original410 Gone.; eLeoRex Technologies: Original1October2026 deadline passed; not a current internship recommendation.; Figr: Antler original detail explicitly says no longer accepting. Current opening not inferred from a stale search snippet.; Grexa AI: Original Peerlist employer post is archived; watch for a renewed role rather than treating it as current.; Cravv: Employer Wellfound detail lists20k/month and digital/device work. Below the non-Gujarat target; retain as a watchlist-only company, not a qualifying new job.; Nngtw Studio: Advertised India-remote UI/UX internship conflicts with its linked Google form, which redirects to closedform and explicitly no longer accepts responses. Keep company-only pending a working renewed intake; no pay or duration verified.; Strom Bot: Original role header explicitly Volunteer and Unpaid, posted27June2026. Body mentions skill/output-based stipend without guaranteed amount, which conflicts with unpaid header. Not a qualifying paid internship.; Unosecur: Specific indexed Workable Product Design Intern detail returns410Gone. Official careers corroborates identity-security company; linked public ATS is a blank JavaScript response. No renewed design intake established; no claim all company hiring closed.</t>
-        </is>
-      </c>
+          <t>No numerical stipend matches invented; no applicant-specific fit claims or hiring probability.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -24475,8 +27723,41 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>StartupGoa</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://startupgoa.org/job/growth-gravy-goa-internship-internships-in-goa-multiple-positions/</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Public regional discovery and employer corroboration</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Growth Gravy broad internship advert includes UI/UX Intern in Panjim. Official careers extract lists UI/UX Designer, but exact internship/current cohort/pay not verified. Added company-only.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Undated multi-role board programme is not a current individual vacancy; normal employer HTTP encountered CAPTCHA redirect, no bypass.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
+  <autoFilter ref="A1:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24487,7 +27768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30159,7 +33440,7 @@
       <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -32700,8 +35981,306 @@
         </is>
       </c>
     </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Suggested preference/fit tier based on published product or UX work and location; no hiring probability or offer implied.</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="n"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Paid internship; numeric stipend not published and set at offer.</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Suggested preference/fit tier based on published product or UX work and location; no hiring probability or offer implied.</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="2" t="n"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>No numerical pay in either original role.</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/join-the-team</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Suggested preference/fit tier based on published product or UX work and location; no hiring probability or offer implied.</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Historical self-reported salary</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>UX/Product Designer Intern</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Current stipend undisclosed. Historical role-specific report is below30k target and not current pay.</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tensorgo.com/careers/</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Salary/TensorGo-Technologies-UX-Product-Designer-Intern-Salaries-E4412050_DAO.htm?filter.jobTitleExact=UX%2FProduct+Designer+Intern</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Suggested preference/fit tier based on published product or UX work and location; no hiring probability or offer implied.</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="n"/>
+      <c r="G175" s="2" t="n"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Internship pay unstated; no qualifying numerical stipend established.</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk?department=design&amp;source=google_jobs</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Suggested preference/fit tier based on published product or UX work and location; no hiring probability or offer implied.</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="2" t="n"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Visible5–10kINR header omits period; structured metadata explicitly YEAR. Anomalous and below target as written, not monthly stipend.</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4639779-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Growth Gravy</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Suggested preference/fit tier based on published product or UX work and location; no hiring probability or offer implied.</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="2" t="n"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>No UI/UX stipend or salary confirmed.</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.growthgravy.com/</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M171"/>
+  <autoFilter ref="A1:M177"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Dream,Workable,Possible"</formula1>
@@ -32899,6 +36478,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32910,7 +36496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -40231,7 +43817,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Advertised role; eligibility, pay and intake need review</t>
+          <t>Retained UX internship original removed; replacement unverified</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -40258,7 +43844,7 @@
       <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -43409,8 +46995,346 @@
         </is>
       </c>
     </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Voice AI interviews and hiring software</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Hyderabad hybrid/office optional</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Current employer role; pay, engagement and exact start require confirmation</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Published role application form / optional AI-interview route; not initiated</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UX/product studio</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Behaviour-led digital product design consultancy</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai internship; junior header Mumbai/body Bengaluru conflict. Work mode unstated.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Two advertised early-career roles; pay/start/locations require confirmation</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/join-the-team</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>talent@humanx.io</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>General recruitment / speculative interest</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>AI and computer-vision platform</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad; historical design internship work from office</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Historical Indeed advert conflicts with410 original; renewed intake unverified</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tensorgo.com/careers/</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Services / product engineering</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Digital product engineering and UX services</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad; no remote permission established</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Internship detail retained, but linked application explicitly not accepting</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk?department=design&amp;source=google_jobs</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>alphateam@xcubelabs.com</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Published careers questions contact</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Product company</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>AI search and business tools for design industry</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Remote Everywhere on Wellfound; company New Delhi</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Advertised UX intern; pay-unit conflict/low amount excludes qualifying recommendation</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4639779-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Growth Gravy</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Services / digital agency</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Digital marketing, websites and UI/UX</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Panjim/Goa; work-from-home depends on role, not established for UX</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Generic employer UI/UX Designer opening; broad board internship intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>UX Designer; Product Designer</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.growthgravy.com/</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>hr@growthgravy.com</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Published general/speculative recruitment for unmatched positions</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M171"/>
+  <autoFilter ref="A1:M177"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -43734,6 +47658,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId321"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId329"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43745,7 +47676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I343"/>
+  <dimension ref="A1:I362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -51961,7 +55892,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline. Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -52004,7 +55935,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline. Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -52047,7 +55978,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline. Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -52090,7 +56021,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline.</t>
+          <t>Official careers detail lists JR-045767 and links the Workday application plus a mandatory Microsoft questionnaire. Both steps are required. Workday was not accessible through the research tool; no submission flow tested. Unstop lists 5 November while another mirror gives 7 December; neither is an employer-confirmed deadline. Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -58512,8 +62443,825 @@
       </c>
       <c r="I343" s="2" t="inlineStr"/>
     </row>
+    <row r="344" ht="42" customHeight="1">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — UX/UI and Accessibility</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Hyderabad hybrid/office optional</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Original200 detail: paid, approximately12weeks,20–40hours/week,November/December2026 start. Remote India or optional Hyderabad office;2–3hours evening IST overlap. Direct contract with TheInterviews Inc.(Delaware), no Indian subsidiary. Stipend depends on hours/experience and is not numerically stated. Intake/start and college acceptance still need confirmation.</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Students/recent graduates welcome; portfolio should explain process and iteration</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr"/>
+    </row>
+    <row r="345" ht="42" customHeight="1">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — UX/UI and Accessibility</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Hyderabad hybrid/office optional</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Original200 detail: paid, approximately12weeks,20–40hours/week,November/December2026 start. Remote India or optional Hyderabad office;2–3hours evening IST overlap. Direct contract with TheInterviews Inc.(Delaware), no Indian subsidiary. Stipend depends on hours/experience and is not numerically stated. Intake/start and college acceptance still need confirmation.</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Figma and visual/interaction foundations; feedback and weekly iteration</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346" ht="42" customHeight="1">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — UX/UI and Accessibility</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Hyderabad hybrid/office optional</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Original200 detail: paid, approximately12weeks,20–40hours/week,November/December2026 start. Remote India or optional Hyderabad office;2–3hours evening IST overlap. Direct contract with TheInterviews Inc.(Delaware), no Indian subsidiary. Stipend depends on hours/experience and is not numerically stated. Intake/start and college acceptance still need confirmation.</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility checks for keyboard, screen reader, contrast and mobile; component/token work mapped to Tailwind</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347" ht="42" customHeight="1">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>TheInterviews</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — UX/UI and Accessibility</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Remote within India; Hyderabad hybrid/office optional</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theinterviews.ai/careers/product-design-intern-ux-accessibility-india</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Original200 detail: paid, approximately12weeks,20–40hours/week,November/December2026 start. Remote India or optional Hyderabad office;2–3hours evening IST overlap. Direct contract with TheInterviews Inc.(Delaware), no Indian subsidiary. Stipend depends on hours/experience and is not numerically stated. Intake/start and college acceptance still need confirmation.</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>Research/analytics and developer handoff; HTML/CSS/React are bonuses</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348" ht="42" customHeight="1">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India; work mode unstated</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Original role: Mumbai,3–6months,0–1years. Student/personal work and self-taught candidates welcome. Pay, posting date, start/cohort and work mode absent. Linked RecruitCRM application could not be read through research tool; no form submitted.</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio including student or personal design work;0–1years</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349" ht="42" customHeight="1">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India; work mode unstated</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Original role: Mumbai,3–6months,0–1years. Student/personal work and self-taught candidates welcome. Pay, posting date, start/cohort and work mode absent. Linked RecruitCRM application could not be read through research tool; no form submitted.</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>Research/data/behaviour synthesis into problem statements, journeys and prototypes</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr"/>
+    </row>
+    <row r="350" ht="42" customHeight="1">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India; work mode unstated</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Original role: Mumbai,3–6months,0–1years. Student/personal work and self-taught candidates welcome. Pay, posting date, start/cohort and work mode absent. Linked RecruitCRM application could not be read through research tool; no form submitted.</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>Strong aesthetics, attention to detail, collaboration and presenting design decisions</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351" ht="42" customHeight="1">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India; work mode unstated</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-design-intern</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Original role: Mumbai,3–6months,0–1years. Student/personal work and self-taught candidates welcome. Pay, posting date, start/cohort and work mode absent. Linked RecruitCRM application could not be read through research tool; no form submitted.</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Motion, illustration and advanced prototyping are bonuses</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352" ht="42" customHeight="1">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer — junior/stretch,1–2years required</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai header / Bengaluru body; employer location conflict</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-designer-1</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Original full-time role requires1–2years; junior/stretch alternative, not an internship or assured fresher eligibility. Header says Mumbai, body says Bengaluru. Pay/start/work mode unstated. Linked RecruitCRM application restricted to research tool.</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>1–2years required; do not assume zero-experience or student eligibility</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353" ht="42" customHeight="1">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer — junior/stretch,1–2years required</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai header / Bengaluru body; employer location conflict</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-designer-1</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Original full-time role requires1–2years; junior/stretch alternative, not an internship or assured fresher eligibility. Header says Mumbai, body says Bengaluru. Pay/start/work mode unstated. Linked RecruitCRM application restricted to research tool.</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>Develop ideas into prototypes, including no-code/lightweight code</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354" ht="42" customHeight="1">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer — junior/stretch,1–2years required</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai header / Bengaluru body; employer location conflict</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-designer-1</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Original full-time role requires1–2years; junior/stretch alternative, not an internship or assured fresher eligibility. Header says Mumbai, body says Bengaluru. Pay/start/work mode unstated. Linked RecruitCRM application restricted to research tool.</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>Synthesize research/data into product problems and vision</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355" ht="42" customHeight="1">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>HumanX</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Product Designer — junior/stretch,1–2years required</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>Junior / fresher</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai header / Bengaluru body; employer location conflict</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="inlineStr">
+        <is>
+          <t>https://www.humanx.io/job-roles/product-designer-1</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Original full-time role requires1–2years; junior/stretch alternative, not an internship or assured fresher eligibility. Header says Mumbai, body says Bengaluru. Pay/start/work mode unstated. Linked RecruitCRM application restricted to research tool.</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Present product stories and work with technical teams</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356" ht="42" customHeight="1">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — original removed</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Historical / original removed</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana; office</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="inlineStr">
+        <is>
+          <t>https://tensorgo.com/job-type/pdi282506/</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Repeated fresh originalHTTP410Gone. Current careers page is JavaScript shell; site migration possible, so no company-wide closure inferred. Accessible Indeed advert does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Historical advert:0–1years and six-month office availability</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr"/>
+    </row>
+    <row r="357" ht="42" customHeight="1">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>TensorGo</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Product Design Intern — original removed</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>Historical / original removed</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana; office</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="inlineStr">
+        <is>
+          <t>https://tensorgo.com/job-type/pdi282506/</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Repeated fresh originalHTTP410Gone. Current careers page is JavaScript shell; site migration possible, so no company-wide closure inferred. Accessible Indeed advert does not establish renewed intake.</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Historical advert: user flows, wireframes, UI and developer handoff</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358" ht="42" customHeight="1">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Intern — UI/UX, applications not accepting</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>Internship — application closed</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk/61239b0fde0a6e4a69cf151f?source=careers</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>ATS detail KL-85UMEFA9 remains readable:3months,0–1years, pay/date unknown. Linked application explicitly says not accepting applications; not an active feed recommendation.</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>0–1years; any graduation/PG/doctorate listed, current-student eligibility unconfirmed</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359" ht="42" customHeight="1">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Intern — UI/UX, applications not accepting</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>Internship — application closed</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk/61239b0fde0a6e4a69cf151f?source=careers</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>ATS detail KL-85UMEFA9 remains readable:3months,0–1years, pay/date unknown. Linked application explicitly says not accepting applications; not an active feed recommendation.</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>Figma/XD/Sketch, research, wireframes, prototypes and design systems</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360" ht="42" customHeight="1">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS / PurpleTalk</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Intern — UI/UX, applications not accepting</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Internship — application closed</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.klimb.io/purpletalk/61239b0fde0a6e4a69cf151f?source=careers</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>ATS detail KL-85UMEFA9 remains readable:3months,0–1years, pay/date unknown. Linked application explicitly says not accepting applications; not an active feed recommendation.</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>Photoshop, Illustrator and After Effects training a bonus</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361" ht="42" customHeight="1">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>UX Design Intern — compensation unit unresolved</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>Internship — below-target / unit conflict</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Remote Everywhere</t>
+        </is>
+      </c>
+      <c r="E361" s="3" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs/4639779-ux-design-intern</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Original Wellfound detail readable, relative age2months not an absolute publication date. Header5–10kINR lacks period; fetched JSON-LD baseSalary specifies YEAR. Do not silently reinterpret as monthly. Pay/error needs employer clarification; not stipend match.</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>No experience stated; Figma, research, prototyping and design systems</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362" ht="42" customHeight="1">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Growth Gravy</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX Intern — general programme/intake unconfirmed</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>Indexed / general internship programme</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Panjim, Goa</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>https://startupgoa.org/job/growth-gravy-goa-internship-internships-in-goa-multiple-positions/</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>StartupGoa broad multi-position internship advert includes UI/UX Intern; no original date, pay, UX-specific requirements or current cohort verified. Company-only discovery, not an inferred active internship.</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>No detailed requirements captured; open source</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>Unassessed</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I343"/>
+  <autoFilter ref="A1:I362"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Unassessed,Met,Partly met,Gap"</formula1>
@@ -58862,6 +63610,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId341"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId361"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58873,7 +63640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -58888,7 +63655,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Research snapshot: 2026-10-29</t>
+          <t>Research snapshot: 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -60473,6 +65240,66 @@
       <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Indexed mirror1.8lakh/year, another mirror15k/month; no employer-current stipend confirmed and both below target. Keep units/source limits; do not convert annual header to a verified stipend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Revvity</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Original detail repeatedlyHTTP404 and official requisition search JR-045767 returned0results30October. Retired as removed original, not claimed filled. Cached research extract still shows old JD. Workday public detail403 means replacement availability unresolved. History/IDs retained; browser-local saved stage overrides feed status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>[x]cube LABS</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Original application explicitly not accepting despite live detail; company-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Archinza</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Header5–10kINR without period; original JSON-LD YEAR. Low/anomalous as written, not converted to monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>HYV</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>HYV-INT-01 explicitly Delhi NCR/Gurugram onsite, outside eligible office geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Eduminatti</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Mirror-reported5–10k/month,2months part-time; below target. Original Internshala restricted; dates not independently verified.</t>
         </is>
       </c>
     </row>
